--- a/icyber/TRUST-Tracker-Pro.xlsx
+++ b/icyber/TRUST-Tracker-Pro.xlsx
@@ -19,7 +19,6 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="T · Time" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KEEP Dashboard" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly Review" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Lists" sheetId="13" state="hidden" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -35,7 +34,7 @@
     <numFmt numFmtId="167" formatCode="€#,##0.00;-€#,##0.00;&quot;–&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -202,6 +201,12 @@
       <color rgb="006E8180"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Georgia"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="17"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -267,7 +272,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
@@ -325,6 +330,9 @@
     <xf numFmtId="0" fontId="20" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -378,6 +386,9 @@
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -398,6 +409,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
@@ -410,39 +422,6 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="001A9E9E"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="00E8F4F2"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="00FFFFFF"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="001A9E9E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <b val="1"/>
-        <color rgb="009E1B5E"/>
-      </font>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -835,7 +814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:B49"/>
+  <dimension ref="A1:B49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -843,6 +822,7 @@
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="44" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -850,14 +830,15 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="41.4" customHeight="1">
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>You work hard for your money. But is it creating the life you're working so hard for?</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="79" customHeight="1">
+    <row r="4"/>
+    <row r="5" ht="86.90000000000001" customHeight="1">
       <c r="B5" s="3" t="inlineStr">
         <is>
           <t>I'm a full-time cybersecurity consultant at a Big Four firm, working in the financial sector. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €30,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I've experienced it myself.</t>
@@ -871,7 +852,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="36.2" customHeight="1">
       <c r="B7" s="5" t="inlineStr">
         <is>
           <t>How do I build a financially secure future without missing out on the people and moments that matter most today?</t>
@@ -885,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="19" customHeight="1">
       <c r="B10" s="6" t="inlineStr">
         <is>
@@ -899,7 +881,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="94" customHeight="1">
+    <row r="12" ht="100.5" customHeight="1">
       <c r="B12" s="4" t="inlineStr">
         <is>
           <t>Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a mum who needs them. I wish I'd had a clear, honest plan for the few hours I actually had left, when I wasn't already exhausted from work and every other responsibility around me. So I decided to build it for myself, step by step. You shouldn't need a wake-up call to start. Begin before yours comes, or before it's too late.</t>
@@ -913,6 +895,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="19" customHeight="1">
       <c r="B15" s="6" t="inlineStr">
         <is>
@@ -948,7 +931,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1">
+    <row r="20" ht="32.3" customHeight="1">
       <c r="B20" s="4" t="inlineStr">
         <is>
           <t>✓  You want financial independence for a reason: more choices and more time with the people you love.</t>
@@ -962,6 +945,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="19" customHeight="1">
       <c r="B23" s="6" t="inlineStr">
         <is>
@@ -1018,6 +1002,7 @@
         </is>
       </c>
     </row>
+    <row r="31"/>
     <row r="32" ht="19" customHeight="1">
       <c r="B32" s="6" t="inlineStr">
         <is>
@@ -1032,6 +1017,7 @@
         </is>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="19" customHeight="1">
       <c r="B35" s="6" t="inlineStr">
         <is>
@@ -1081,6 +1067,7 @@
         </is>
       </c>
     </row>
+    <row r="42"/>
     <row r="43" ht="19" customHeight="1">
       <c r="B43" s="6" t="inlineStr">
         <is>
@@ -1088,13 +1075,14 @@
         </is>
       </c>
     </row>
-    <row r="44" ht="34" customHeight="1">
+    <row r="44" ht="46" customHeight="1">
       <c r="B44" s="4" t="inlineStr">
         <is>
           <t>Head to the How to Use tab, then the 7 Stages tab. In about 20 minutes you'll have your first financial snapshot. You don't need everything figured out today. You just need somewhere meaningful to start.</t>
         </is>
       </c>
     </row>
+    <row r="45"/>
     <row r="46" ht="64" customHeight="1">
       <c r="B46" s="9" t="inlineStr">
         <is>
@@ -1102,7 +1090,7 @@
         </is>
       </c>
     </row>
-    <row r="47" ht="34" customHeight="1">
+    <row r="47" ht="46" customHeight="1">
       <c r="B47" s="10" t="inlineStr">
         <is>
           <t>Build your options without quitting your 9–5.  Know your money. Build your wealth. Reclaim your time.
@@ -1110,7 +1098,8 @@
         </is>
       </c>
     </row>
-    <row r="49" ht="34" customHeight="1">
+    <row r="48"/>
+    <row r="49" ht="38.1" customHeight="1">
       <c r="B49" s="11" t="inlineStr">
         <is>
           <t>Educational information only, not individualised financial or investment advice. TRUST Tracker Pro helps you organise and understand your finances; it doesn't guarantee financial outcomes. Your financial information stays in your own copy of the workbook unless you choose to share it.</t>
@@ -1129,16 +1118,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:E30"/>
+  <dimension ref="A1:E30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="30" customWidth="1" min="2" max="2"/>
+    <col width="39" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -1156,6 +1146,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -1179,260 +1170,264 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="C6" s="44" t="n">
+      <c r="C6" s="45" t="n">
         <v>49</v>
       </c>
-      <c r="D6" s="44" t="n">
+      <c r="D6" s="45" t="n">
         <v>52</v>
       </c>
-      <c r="E6" s="22" t="inlineStr">
+      <c r="E6" s="23" t="inlineStr">
         <is>
           <t>Phone out of the bedroom</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Paid work (incl. overtime)</t>
         </is>
       </c>
-      <c r="C7" s="44" t="n">
+      <c r="C7" s="45" t="n">
         <v>43</v>
       </c>
-      <c r="D7" s="44" t="n">
+      <c r="D7" s="45" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="22" t="inlineStr">
+      <c r="E7" s="23" t="inlineStr">
         <is>
           <t>Stop answering email after 7pm</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Commute</t>
         </is>
       </c>
-      <c r="C8" s="44" t="n">
+      <c r="C8" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="44" t="n">
+      <c r="D8" s="45" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="22" t="inlineStr"/>
+      <c r="E8" s="23" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Caregiving</t>
         </is>
       </c>
-      <c r="C9" s="44" t="n">
+      <c r="C9" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="44" t="n">
+      <c r="D9" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="22" t="inlineStr">
+      <c r="E9" s="23" t="inlineStr">
         <is>
           <t>Ask sibling for one fixed day</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t>Household &amp; admin</t>
         </is>
       </c>
-      <c r="C10" s="44" t="n">
+      <c r="C10" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="44" t="n">
+      <c r="D10" s="45" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="22" t="inlineStr">
+      <c r="E10" s="23" t="inlineStr">
         <is>
           <t>One big shop per week</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>Family &amp; friends time</t>
         </is>
       </c>
-      <c r="C11" s="44" t="n">
+      <c r="C11" s="45" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="44" t="n">
+      <c r="D11" s="45" t="n">
         <v>16</v>
       </c>
-      <c r="E11" s="22" t="inlineStr">
+      <c r="E11" s="23" t="inlineStr">
         <is>
           <t>Protected Sunday afternoon</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="22" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>Health &amp; movement</t>
         </is>
       </c>
-      <c r="C12" s="44" t="n">
+      <c r="C12" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="44" t="n">
+      <c r="D12" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="22" t="inlineStr">
+      <c r="E12" s="23" t="inlineStr">
         <is>
           <t>Walk at lunch</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>Building options (learning / side income)</t>
         </is>
       </c>
-      <c r="C13" s="44" t="n">
+      <c r="C13" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="44" t="n">
+      <c r="D13" s="45" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="22" t="inlineStr">
+      <c r="E13" s="23" t="inlineStr">
         <is>
           <t>Two 2-hour blocks, Tue &amp; Sat</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="22" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t>Rest &amp; yourself</t>
         </is>
       </c>
-      <c r="C14" s="44" t="n">
+      <c r="C14" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="44" t="n">
+      <c r="D14" s="45" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="22" t="inlineStr"/>
+      <c r="E14" s="23" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="44" t="n"/>
-      <c r="D15" s="44" t="n"/>
-      <c r="E15" s="22" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="45" t="n"/>
+      <c r="D15" s="45" t="n"/>
+      <c r="E15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="44" t="n"/>
-      <c r="D16" s="44" t="n"/>
-      <c r="E16" s="22" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="45" t="n"/>
+      <c r="D16" s="45" t="n"/>
+      <c r="E16" s="23" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="44" t="n"/>
-      <c r="D17" s="44" t="n"/>
-      <c r="E17" s="22" t="n"/>
-    </row>
-    <row r="19">
-      <c r="B19" s="45" t="inlineStr">
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="45" t="n"/>
+      <c r="D17" s="45" t="n"/>
+      <c r="E17" s="23" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19" ht="18" customHeight="1">
+      <c r="B19" s="46" t="inlineStr">
         <is>
           <t>Hours planned</t>
         </is>
       </c>
-      <c r="C19" s="57">
+      <c r="C19" s="58">
         <f>SUM(C6:C17)</f>
         <v/>
       </c>
-      <c r="D19" s="57">
+      <c r="D19" s="58">
         <f>SUM(D6:D17)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="33" t="inlineStr">
+    <row r="20" ht="18" customHeight="1">
+      <c r="B20" s="34" t="inlineStr">
         <is>
           <t>Unplanned hours (of 168)</t>
         </is>
       </c>
-      <c r="C20" s="58">
+      <c r="C20" s="59">
         <f>168-C19</f>
         <v/>
       </c>
-      <c r="D20" s="58">
+      <c r="D20" s="59">
         <f>168-D19</f>
         <v/>
       </c>
     </row>
-    <row r="22">
+    <row r="21"/>
+    <row r="22" ht="18" customHeight="1">
       <c r="B22" s="19" t="inlineStr">
         <is>
           <t>Family time gained / week</t>
         </is>
       </c>
-      <c r="C22" s="59">
+      <c r="C22" s="60">
         <f>SUMIF(B6:B17,"Family*",D6:D17)-SUMIF(B6:B17,"Family*",C6:C17)</f>
         <v/>
       </c>
     </row>
-    <row r="23">
+    <row r="23" ht="18" customHeight="1">
       <c r="B23" s="19" t="inlineStr">
         <is>
           <t>Family time gained / year</t>
         </is>
       </c>
-      <c r="C23" s="60">
+      <c r="C23" s="61">
         <f>C22*52</f>
         <v/>
       </c>
     </row>
+    <row r="24"/>
     <row r="25" ht="24" customHeight="1">
-      <c r="B25" s="24" t="inlineStr">
+      <c r="B25" s="25" t="inlineStr">
         <is>
           <t>Negative unplanned hours mean the week doesn't fit. Something has to go before anything new comes in. Never take side-project hours out of sleep or family first.</t>
         </is>
       </c>
     </row>
     <row r="26"/>
-    <row r="28">
-      <c r="B28" s="45" t="inlineStr">
+    <row r="27"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>Your hourly value at work</t>
         </is>
       </c>
-      <c r="C28" s="61">
+      <c r="C28" s="62">
         <f>'U · Understand'!C29</f>
         <v/>
       </c>
-      <c r="D28" s="24" t="inlineStr">
+      <c r="D28" s="25" t="inlineStr">
         <is>
           <t>This is roughly what extra income or savings would need to replace if you reduced your paid hours to your goal. A concrete target for the Income Streams tab.</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="45" t="inlineStr">
+    <row r="29" ht="31" customHeight="1">
+      <c r="B29" s="46" t="inlineStr">
         <is>
           <t>Value of the work hours you want back / year</t>
         </is>
       </c>
-      <c r="C29" s="28">
+      <c r="C29" s="29">
         <f>MAX(0,SUMIF(B6:B17,"Paid work*",C6:C17)-SUMIF(B6:B17,"Paid work*",D6:D17))*52*C28</f>
         <v/>
       </c>
@@ -1456,19 +1451,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F30"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="4" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="63" t="inlineStr">
         <is>
           <t>KEEP — Know your Earnings to Escape your Paycheck</t>
         </is>
@@ -1485,6 +1482,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="15" t="inlineStr">
         <is>
@@ -1493,11 +1491,11 @@
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="62">
-        <f>INDEX(Lists!$F$1:$F$7,C9+1)</f>
-        <v/>
-      </c>
-      <c r="E6" s="63">
+      <c r="B6" s="64">
+        <f>CHOOSE(C9+1,"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose")</f>
+        <v/>
+      </c>
+      <c r="E6" s="65">
         <f>CHOOSE(C9+1,"Next step: more goes out than comes in. Use R · Reclaim and cut wants until KEEP is at least €0.","Next step: build a starter buffer of one month of needs before anything else.","Next step: clear consumer debt, highest interest first (Priority 1 on U · Understand).","Next step: grow the buffer into your full emergency fund on S · Save.","Next step: you are secure. Stage 5: learn investing basics on the Invest tab, then start ONE income stream.","Next step: extra income covers 25%+ of needs. Keep investing; decide what time you want back.","You have choices. Extra income covers your baseline. Decide on your terms how much you want to work.")</f>
         <v/>
       </c>
@@ -1505,36 +1503,38 @@
     <row r="7" ht="28" customHeight="1">
       <c r="C7" s="13" t="n"/>
     </row>
-    <row r="9">
+    <row r="8"/>
+    <row r="9" ht="18" customHeight="1">
       <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Level number</t>
         </is>
       </c>
-      <c r="C9" s="64">
+      <c r="C9" s="66">
         <f>IF(C14&lt;0,0,IF(C22&lt;C13,1,IF(C20&gt;0,2,IF(C22&lt;C23,3,IF(C25&lt;0.25*C13,4,IF(C25&lt;C13,5,6))))))</f>
         <v/>
       </c>
     </row>
+    <row r="10"/>
     <row r="11">
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="26" t="inlineStr">
         <is>
           <t>MONEY</t>
         </is>
       </c>
-      <c r="E11" s="25" t="inlineStr">
+      <c r="E11" s="26" t="inlineStr">
         <is>
           <t>TIME &amp; OPTIONS</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="18" customHeight="1">
       <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Money in / month</t>
         </is>
       </c>
-      <c r="C12" s="65">
+      <c r="C12" s="67">
         <f>'T · Track'!E13</f>
         <v/>
       </c>
@@ -1543,18 +1543,18 @@
           <t>1 hour of your life is worth</t>
         </is>
       </c>
-      <c r="F12" s="66">
+      <c r="F12" s="68">
         <f>'U · Understand'!C29</f>
         <v/>
       </c>
     </row>
-    <row r="13">
+    <row r="13" ht="18" customHeight="1">
       <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Needs (baseline)</t>
         </is>
       </c>
-      <c r="C13" s="67">
+      <c r="C13" s="69">
         <f>'T · Track'!E58</f>
         <v/>
       </c>
@@ -1563,18 +1563,18 @@
           <t>Keep your first hour / month</t>
         </is>
       </c>
-      <c r="F13" s="68">
+      <c r="F13" s="70">
         <f>'U · Understand'!C31</f>
         <v/>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="18" customHeight="1">
       <c r="B14" s="17" t="inlineStr">
         <is>
           <t>What you KEEP / month</t>
         </is>
       </c>
-      <c r="C14" s="68">
+      <c r="C14" s="70">
         <f>'T · Track'!E62</f>
         <v/>
       </c>
@@ -1583,18 +1583,18 @@
           <t>Hours / week on income streams</t>
         </is>
       </c>
-      <c r="F14" s="69">
+      <c r="F14" s="71">
         <f>'Income Streams'!E25</f>
         <v/>
       </c>
     </row>
-    <row r="15">
+    <row r="15" ht="18" customHeight="1">
       <c r="B15" s="17" t="inlineStr">
         <is>
           <t>Keep rate</t>
         </is>
       </c>
-      <c r="C15" s="70">
+      <c r="C15" s="72">
         <f>'T · Track'!E63</f>
         <v/>
       </c>
@@ -1603,18 +1603,18 @@
           <t>Needs covered by extra income</t>
         </is>
       </c>
-      <c r="F15" s="71">
+      <c r="F15" s="73">
         <f>'Income Streams'!G26</f>
         <v/>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="18" customHeight="1">
       <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Wants</t>
         </is>
       </c>
-      <c r="C16" s="72">
+      <c r="C16" s="74">
         <f>'T · Track'!E59</f>
         <v/>
       </c>
@@ -1623,18 +1623,18 @@
           <t>Family time gained / week (goal)</t>
         </is>
       </c>
-      <c r="F16" s="73">
+      <c r="F16" s="75">
         <f>'T · Time'!C22</f>
         <v/>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="31" customHeight="1">
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Reclaimable / month</t>
         </is>
       </c>
-      <c r="C17" s="68">
+      <c r="C17" s="70">
         <f>'R · Reclaim'!F32</f>
         <v/>
       </c>
@@ -1643,18 +1643,18 @@
           <t>Unassigned KEEP after savings plan</t>
         </is>
       </c>
-      <c r="F17" s="65">
+      <c r="F17" s="67">
         <f>'S · Save'!E32</f>
         <v/>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="18" customHeight="1">
       <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Reclaimable / year</t>
         </is>
       </c>
-      <c r="C18" s="68">
+      <c r="C18" s="70">
         <f>'R · Reclaim'!F33</f>
         <v/>
       </c>
@@ -1663,155 +1663,184 @@
           <t>Career growth / month</t>
         </is>
       </c>
-      <c r="F18" s="68">
+      <c r="F18" s="70">
         <f>'Income Streams'!G24</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>SAFETY</t>
         </is>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="18" customHeight="1">
       <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Debt to clear</t>
         </is>
       </c>
-      <c r="C20" s="72">
+      <c r="C20" s="74">
         <f>'U · Understand'!C17</f>
         <v/>
       </c>
-      <c r="E20" s="74" t="inlineStr">
+      <c r="E20" s="76" t="inlineStr">
         <is>
           <t>THE FREEDOM LADDER</t>
         </is>
       </c>
     </row>
-    <row r="21">
+    <row r="21" ht="18" customHeight="1">
       <c r="B21" s="17" t="inlineStr">
         <is>
           <t>Interest you pay / year</t>
         </is>
       </c>
-      <c r="C21" s="72">
+      <c r="C21" s="74">
         <f>'U · Understand'!C19</f>
         <v/>
       </c>
-      <c r="E21" s="75" t="inlineStr">
+      <c r="E21" s="77" t="inlineStr">
         <is>
           <t>0 · Overwhelmed: more out than in</t>
         </is>
       </c>
-    </row>
-    <row r="22">
+      <c r="G21" s="78">
+        <f>IF($C$9=0,"◀ you are here","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
       <c r="B22" s="17" t="inlineStr">
         <is>
           <t>Emergency fund saved</t>
         </is>
       </c>
-      <c r="C22" s="68">
+      <c r="C22" s="70">
         <f>'S · Save'!C11</f>
         <v/>
       </c>
-      <c r="E22" s="75" t="inlineStr">
+      <c r="E22" s="77" t="inlineStr">
         <is>
           <t>1 · Stable: KEEP is €0 or more</t>
         </is>
       </c>
-    </row>
-    <row r="23">
+      <c r="G22" s="78">
+        <f>IF($C$9=1,"◀ you are here","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
       <c r="B23" s="17" t="inlineStr">
         <is>
           <t>Emergency fund target</t>
         </is>
       </c>
-      <c r="C23" s="67">
+      <c r="C23" s="69">
         <f>'S · Save'!C10</f>
         <v/>
       </c>
-      <c r="E23" s="75" t="inlineStr">
+      <c r="E23" s="77" t="inlineStr">
         <is>
           <t>2 · Buffered: 1 month of needs saved</t>
         </is>
       </c>
-    </row>
-    <row r="24">
+      <c r="G23" s="78">
+        <f>IF($C$9=2,"◀ you are here","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Fund progress</t>
         </is>
       </c>
-      <c r="C24" s="70">
+      <c r="C24" s="72">
         <f>'S · Save'!C12</f>
         <v/>
       </c>
-      <c r="E24" s="75" t="inlineStr">
+      <c r="E24" s="77" t="inlineStr">
         <is>
           <t>3 · Debt-free: consumer debt cleared</t>
         </is>
       </c>
-    </row>
-    <row r="25">
+      <c r="G24" s="78">
+        <f>IF($C$9=3,"◀ you are here","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
       <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Extra income / month</t>
         </is>
       </c>
-      <c r="C25" s="68">
+      <c r="C25" s="70">
         <f>'Income Streams'!G23</f>
         <v/>
       </c>
-      <c r="E25" s="75" t="inlineStr">
+      <c r="E25" s="77" t="inlineStr">
         <is>
           <t>4 · Secure: full emergency fund</t>
         </is>
       </c>
-    </row>
-    <row r="26">
+      <c r="G25" s="78">
+        <f>IF($C$9=4,"◀ you are here","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
       <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Invested / month</t>
         </is>
       </c>
-      <c r="C26" s="68">
+      <c r="C26" s="70">
         <f>Invest!D38</f>
         <v/>
       </c>
-      <c r="E26" s="75" t="inlineStr">
+      <c r="E26" s="77" t="inlineStr">
         <is>
           <t>5 · Flexible: extra income ≥ 25% of needs</t>
         </is>
       </c>
-    </row>
-    <row r="27">
+      <c r="G26" s="78">
+        <f>IF($C$9=5,"◀ you are here","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27" ht="18" customHeight="1">
       <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Roadmap stages done</t>
         </is>
       </c>
-      <c r="C27" s="76">
+      <c r="C27" s="79">
         <f>'7 Stages'!D14</f>
         <v/>
       </c>
-      <c r="E27" s="75" t="inlineStr">
+      <c r="E27" s="77" t="inlineStr">
         <is>
           <t>6 · Free to choose: extra income ≥ needs</t>
         </is>
       </c>
-    </row>
+      <c r="G27" s="78">
+        <f>IF($C$9=6,"◀ you are here","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28"/>
     <row r="29">
-      <c r="B29" s="77" t="inlineStr">
+      <c r="B29" s="80" t="inlineStr">
         <is>
           <t>Your career is the engine. Keep your first hour, and keep going. — Liliane</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="78" t="inlineStr">
+      <c r="B30" s="81" t="inlineStr">
         <is>
           <t>Educational tool. Not financial advice.</t>
         </is>
@@ -1831,16 +1860,6 @@
     <mergeCell ref="E26:F26"/>
     <mergeCell ref="E21:F21"/>
   </mergeCells>
-  <conditionalFormatting sqref="E21:F27">
-    <cfRule type="expression" priority="1" dxfId="1">
-      <formula>ROW(E21)-21=$C$9</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C14">
-    <cfRule type="cellIs" priority="2" operator="lessThan" dxfId="2">
-      <formula>0</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1852,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:L17"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1865,10 +1884,11 @@
     <col width="14" customWidth="1" min="8" max="8"/>
     <col width="13" customWidth="1" min="9" max="9"/>
     <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
     <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -1893,6 +1913,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -1951,600 +1972,314 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="27" t="n">
         <v>2500</v>
       </c>
-      <c r="D6" s="26" t="n">
+      <c r="D6" s="27" t="n">
         <v>1650</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="27" t="n">
         <v>330</v>
       </c>
-      <c r="F6" s="36">
-        <f>IF(C6="","",C6-N(D6)-N(E6))</f>
-        <v/>
-      </c>
-      <c r="G6" s="50">
-        <f>IF(N(C6)&gt;0,F6/C6,"")</f>
-        <v/>
-      </c>
-      <c r="H6" s="26" t="n">
+      <c r="F6" s="37">
+        <f>IF(C6="","",C6-(D6)-(E6))</f>
+        <v/>
+      </c>
+      <c r="G6" s="51">
+        <f>IF((C6)&gt;0,F6/C6,"")</f>
+        <v/>
+      </c>
+      <c r="H6" s="27" t="n">
         <v>1000</v>
       </c>
-      <c r="I6" s="26" t="n">
+      <c r="I6" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="J6" s="26" t="n">
+      <c r="J6" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="79">
-        <f>IF(C6="","",INDEX(Lists!$F$1:$F$7,1+IF(F6&lt;0,0,IF(N(H6)&lt;N(D6),1,IF(N(I6)&gt;0,2,IF(N(H6)&lt;N(D6)*'S · Save'!$C$8,3,IF(N(J6)&lt;0.25*N(D6),4,IF(N(J6)&lt;N(D6),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L6" s="22" t="inlineStr">
+      <c r="K6" s="82">
+        <f>IF(C6="","",CHOOSE(1+IF(F6&lt;0,0,IF((H6)&lt;(D6),1,IF((I6)&gt;0,2,IF((H6)&lt;(D6)*'S · Save'!$C$8,3,IF((J6)&lt;0.25*(D6),4,IF((J6)&lt;(D6),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t>Cancelled 2 subscriptions</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="27" t="n">
         <v>2560</v>
       </c>
-      <c r="D7" s="26" t="n">
+      <c r="D7" s="27" t="n">
         <v>1640</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="27" t="n">
         <v>265</v>
       </c>
-      <c r="F7" s="36">
-        <f>IF(C7="","",C7-N(D7)-N(E7))</f>
-        <v/>
-      </c>
-      <c r="G7" s="50">
-        <f>IF(N(C7)&gt;0,F7/C7,"")</f>
-        <v/>
-      </c>
-      <c r="H7" s="26" t="n">
+      <c r="F7" s="37">
+        <f>IF(C7="","",C7-(D7)-(E7))</f>
+        <v/>
+      </c>
+      <c r="G7" s="51">
+        <f>IF((C7)&gt;0,F7/C7,"")</f>
+        <v/>
+      </c>
+      <c r="H7" s="27" t="n">
         <v>1200</v>
       </c>
-      <c r="I7" s="26" t="n">
+      <c r="I7" s="27" t="n">
         <v>1400</v>
       </c>
-      <c r="J7" s="26" t="n">
+      <c r="J7" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="K7" s="79">
-        <f>IF(C7="","",INDEX(Lists!$F$1:$F$7,1+IF(F7&lt;0,0,IF(N(H7)&lt;N(D7),1,IF(N(I7)&gt;0,2,IF(N(H7)&lt;N(D7)*'S · Save'!$C$8,3,IF(N(J7)&lt;0.25*N(D7),4,IF(N(J7)&lt;N(D7),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L7" s="22" t="inlineStr">
+      <c r="K7" s="82">
+        <f>IF(C7="","",CHOOSE(1+IF(F7&lt;0,0,IF((H7)&lt;(D7),1,IF((I7)&gt;0,2,IF((H7)&lt;(D7)*'S · Save'!$C$8,3,IF((J7)&lt;0.25*(D7),4,IF((J7)&lt;(D7),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t>First €60 from my guide</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="36">
-        <f>IF(C8="","",C8-N(D8)-N(E8))</f>
-        <v/>
-      </c>
-      <c r="G8" s="50">
-        <f>IF(N(C8)&gt;0,F8/C8,"")</f>
-        <v/>
-      </c>
-      <c r="H8" s="26" t="n"/>
-      <c r="I8" s="26" t="n"/>
-      <c r="J8" s="26" t="n"/>
-      <c r="K8" s="79">
-        <f>IF(C8="","",INDEX(Lists!$F$1:$F$7,1+IF(F8&lt;0,0,IF(N(H8)&lt;N(D8),1,IF(N(I8)&gt;0,2,IF(N(H8)&lt;N(D8)*'S · Save'!$C$8,3,IF(N(J8)&lt;0.25*N(D8),4,IF(N(J8)&lt;N(D8),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L8" s="22" t="n"/>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="37">
+        <f>IF(C8="","",C8-(D8)-(E8))</f>
+        <v/>
+      </c>
+      <c r="G8" s="51">
+        <f>IF((C8)&gt;0,F8/C8,"")</f>
+        <v/>
+      </c>
+      <c r="H8" s="27" t="n"/>
+      <c r="I8" s="27" t="n"/>
+      <c r="J8" s="27" t="n"/>
+      <c r="K8" s="82">
+        <f>IF(C8="","",CHOOSE(1+IF(F8&lt;0,0,IF((H8)&lt;(D8),1,IF((I8)&gt;0,2,IF((H8)&lt;(D8)*'S · Save'!$C$8,3,IF((J8)&lt;0.25*(D8),4,IF((J8)&lt;(D8),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L8" s="23" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="26" t="n"/>
-      <c r="E9" s="26" t="n"/>
-      <c r="F9" s="36">
-        <f>IF(C9="","",C9-N(D9)-N(E9))</f>
-        <v/>
-      </c>
-      <c r="G9" s="50">
-        <f>IF(N(C9)&gt;0,F9/C9,"")</f>
-        <v/>
-      </c>
-      <c r="H9" s="26" t="n"/>
-      <c r="I9" s="26" t="n"/>
-      <c r="J9" s="26" t="n"/>
-      <c r="K9" s="79">
-        <f>IF(C9="","",INDEX(Lists!$F$1:$F$7,1+IF(F9&lt;0,0,IF(N(H9)&lt;N(D9),1,IF(N(I9)&gt;0,2,IF(N(H9)&lt;N(D9)*'S · Save'!$C$8,3,IF(N(J9)&lt;0.25*N(D9),4,IF(N(J9)&lt;N(D9),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L9" s="22" t="n"/>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="37">
+        <f>IF(C9="","",C9-(D9)-(E9))</f>
+        <v/>
+      </c>
+      <c r="G9" s="51">
+        <f>IF((C9)&gt;0,F9/C9,"")</f>
+        <v/>
+      </c>
+      <c r="H9" s="27" t="n"/>
+      <c r="I9" s="27" t="n"/>
+      <c r="J9" s="27" t="n"/>
+      <c r="K9" s="82">
+        <f>IF(C9="","",CHOOSE(1+IF(F9&lt;0,0,IF((H9)&lt;(D9),1,IF((I9)&gt;0,2,IF((H9)&lt;(D9)*'S · Save'!$C$8,3,IF((J9)&lt;0.25*(D9),4,IF((J9)&lt;(D9),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="36">
-        <f>IF(C10="","",C10-N(D10)-N(E10))</f>
-        <v/>
-      </c>
-      <c r="G10" s="50">
-        <f>IF(N(C10)&gt;0,F10/C10,"")</f>
-        <v/>
-      </c>
-      <c r="H10" s="26" t="n"/>
-      <c r="I10" s="26" t="n"/>
-      <c r="J10" s="26" t="n"/>
-      <c r="K10" s="79">
-        <f>IF(C10="","",INDEX(Lists!$F$1:$F$7,1+IF(F10&lt;0,0,IF(N(H10)&lt;N(D10),1,IF(N(I10)&gt;0,2,IF(N(H10)&lt;N(D10)*'S · Save'!$C$8,3,IF(N(J10)&lt;0.25*N(D10),4,IF(N(J10)&lt;N(D10),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L10" s="22" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="37">
+        <f>IF(C10="","",C10-(D10)-(E10))</f>
+        <v/>
+      </c>
+      <c r="G10" s="51">
+        <f>IF((C10)&gt;0,F10/C10,"")</f>
+        <v/>
+      </c>
+      <c r="H10" s="27" t="n"/>
+      <c r="I10" s="27" t="n"/>
+      <c r="J10" s="27" t="n"/>
+      <c r="K10" s="82">
+        <f>IF(C10="","",CHOOSE(1+IF(F10&lt;0,0,IF((H10)&lt;(D10),1,IF((I10)&gt;0,2,IF((H10)&lt;(D10)*'S · Save'!$C$8,3,IF((J10)&lt;0.25*(D10),4,IF((J10)&lt;(D10),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L10" s="23" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="26" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="36">
-        <f>IF(C11="","",C11-N(D11)-N(E11))</f>
-        <v/>
-      </c>
-      <c r="G11" s="50">
-        <f>IF(N(C11)&gt;0,F11/C11,"")</f>
-        <v/>
-      </c>
-      <c r="H11" s="26" t="n"/>
-      <c r="I11" s="26" t="n"/>
-      <c r="J11" s="26" t="n"/>
-      <c r="K11" s="79">
-        <f>IF(C11="","",INDEX(Lists!$F$1:$F$7,1+IF(F11&lt;0,0,IF(N(H11)&lt;N(D11),1,IF(N(I11)&gt;0,2,IF(N(H11)&lt;N(D11)*'S · Save'!$C$8,3,IF(N(J11)&lt;0.25*N(D11),4,IF(N(J11)&lt;N(D11),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L11" s="22" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="37">
+        <f>IF(C11="","",C11-(D11)-(E11))</f>
+        <v/>
+      </c>
+      <c r="G11" s="51">
+        <f>IF((C11)&gt;0,F11/C11,"")</f>
+        <v/>
+      </c>
+      <c r="H11" s="27" t="n"/>
+      <c r="I11" s="27" t="n"/>
+      <c r="J11" s="27" t="n"/>
+      <c r="K11" s="82">
+        <f>IF(C11="","",CHOOSE(1+IF(F11&lt;0,0,IF((H11)&lt;(D11),1,IF((I11)&gt;0,2,IF((H11)&lt;(D11)*'S · Save'!$C$8,3,IF((J11)&lt;0.25*(D11),4,IF((J11)&lt;(D11),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L11" s="23" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="36">
-        <f>IF(C12="","",C12-N(D12)-N(E12))</f>
-        <v/>
-      </c>
-      <c r="G12" s="50">
-        <f>IF(N(C12)&gt;0,F12/C12,"")</f>
-        <v/>
-      </c>
-      <c r="H12" s="26" t="n"/>
-      <c r="I12" s="26" t="n"/>
-      <c r="J12" s="26" t="n"/>
-      <c r="K12" s="79">
-        <f>IF(C12="","",INDEX(Lists!$F$1:$F$7,1+IF(F12&lt;0,0,IF(N(H12)&lt;N(D12),1,IF(N(I12)&gt;0,2,IF(N(H12)&lt;N(D12)*'S · Save'!$C$8,3,IF(N(J12)&lt;0.25*N(D12),4,IF(N(J12)&lt;N(D12),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L12" s="22" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="37">
+        <f>IF(C12="","",C12-(D12)-(E12))</f>
+        <v/>
+      </c>
+      <c r="G12" s="51">
+        <f>IF((C12)&gt;0,F12/C12,"")</f>
+        <v/>
+      </c>
+      <c r="H12" s="27" t="n"/>
+      <c r="I12" s="27" t="n"/>
+      <c r="J12" s="27" t="n"/>
+      <c r="K12" s="82">
+        <f>IF(C12="","",CHOOSE(1+IF(F12&lt;0,0,IF((H12)&lt;(D12),1,IF((I12)&gt;0,2,IF((H12)&lt;(D12)*'S · Save'!$C$8,3,IF((J12)&lt;0.25*(D12),4,IF((J12)&lt;(D12),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L12" s="23" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="26" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="36">
-        <f>IF(C13="","",C13-N(D13)-N(E13))</f>
-        <v/>
-      </c>
-      <c r="G13" s="50">
-        <f>IF(N(C13)&gt;0,F13/C13,"")</f>
-        <v/>
-      </c>
-      <c r="H13" s="26" t="n"/>
-      <c r="I13" s="26" t="n"/>
-      <c r="J13" s="26" t="n"/>
-      <c r="K13" s="79">
-        <f>IF(C13="","",INDEX(Lists!$F$1:$F$7,1+IF(F13&lt;0,0,IF(N(H13)&lt;N(D13),1,IF(N(I13)&gt;0,2,IF(N(H13)&lt;N(D13)*'S · Save'!$C$8,3,IF(N(J13)&lt;0.25*N(D13),4,IF(N(J13)&lt;N(D13),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L13" s="22" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="27" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="37">
+        <f>IF(C13="","",C13-(D13)-(E13))</f>
+        <v/>
+      </c>
+      <c r="G13" s="51">
+        <f>IF((C13)&gt;0,F13/C13,"")</f>
+        <v/>
+      </c>
+      <c r="H13" s="27" t="n"/>
+      <c r="I13" s="27" t="n"/>
+      <c r="J13" s="27" t="n"/>
+      <c r="K13" s="82">
+        <f>IF(C13="","",CHOOSE(1+IF(F13&lt;0,0,IF((H13)&lt;(D13),1,IF((I13)&gt;0,2,IF((H13)&lt;(D13)*'S · Save'!$C$8,3,IF((J13)&lt;0.25*(D13),4,IF((J13)&lt;(D13),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L13" s="23" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="36">
-        <f>IF(C14="","",C14-N(D14)-N(E14))</f>
-        <v/>
-      </c>
-      <c r="G14" s="50">
-        <f>IF(N(C14)&gt;0,F14/C14,"")</f>
-        <v/>
-      </c>
-      <c r="H14" s="26" t="n"/>
-      <c r="I14" s="26" t="n"/>
-      <c r="J14" s="26" t="n"/>
-      <c r="K14" s="79">
-        <f>IF(C14="","",INDEX(Lists!$F$1:$F$7,1+IF(F14&lt;0,0,IF(N(H14)&lt;N(D14),1,IF(N(I14)&gt;0,2,IF(N(H14)&lt;N(D14)*'S · Save'!$C$8,3,IF(N(J14)&lt;0.25*N(D14),4,IF(N(J14)&lt;N(D14),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L14" s="22" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="37">
+        <f>IF(C14="","",C14-(D14)-(E14))</f>
+        <v/>
+      </c>
+      <c r="G14" s="51">
+        <f>IF((C14)&gt;0,F14/C14,"")</f>
+        <v/>
+      </c>
+      <c r="H14" s="27" t="n"/>
+      <c r="I14" s="27" t="n"/>
+      <c r="J14" s="27" t="n"/>
+      <c r="K14" s="82">
+        <f>IF(C14="","",CHOOSE(1+IF(F14&lt;0,0,IF((H14)&lt;(D14),1,IF((I14)&gt;0,2,IF((H14)&lt;(D14)*'S · Save'!$C$8,3,IF((J14)&lt;0.25*(D14),4,IF((J14)&lt;(D14),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L14" s="23" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="26" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="36">
-        <f>IF(C15="","",C15-N(D15)-N(E15))</f>
-        <v/>
-      </c>
-      <c r="G15" s="50">
-        <f>IF(N(C15)&gt;0,F15/C15,"")</f>
-        <v/>
-      </c>
-      <c r="H15" s="26" t="n"/>
-      <c r="I15" s="26" t="n"/>
-      <c r="J15" s="26" t="n"/>
-      <c r="K15" s="79">
-        <f>IF(C15="","",INDEX(Lists!$F$1:$F$7,1+IF(F15&lt;0,0,IF(N(H15)&lt;N(D15),1,IF(N(I15)&gt;0,2,IF(N(H15)&lt;N(D15)*'S · Save'!$C$8,3,IF(N(J15)&lt;0.25*N(D15),4,IF(N(J15)&lt;N(D15),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L15" s="22" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="37">
+        <f>IF(C15="","",C15-(D15)-(E15))</f>
+        <v/>
+      </c>
+      <c r="G15" s="51">
+        <f>IF((C15)&gt;0,F15/C15,"")</f>
+        <v/>
+      </c>
+      <c r="H15" s="27" t="n"/>
+      <c r="I15" s="27" t="n"/>
+      <c r="J15" s="27" t="n"/>
+      <c r="K15" s="82">
+        <f>IF(C15="","",CHOOSE(1+IF(F15&lt;0,0,IF((H15)&lt;(D15),1,IF((I15)&gt;0,2,IF((H15)&lt;(D15)*'S · Save'!$C$8,3,IF((J15)&lt;0.25*(D15),4,IF((J15)&lt;(D15),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="36">
-        <f>IF(C16="","",C16-N(D16)-N(E16))</f>
-        <v/>
-      </c>
-      <c r="G16" s="50">
-        <f>IF(N(C16)&gt;0,F16/C16,"")</f>
-        <v/>
-      </c>
-      <c r="H16" s="26" t="n"/>
-      <c r="I16" s="26" t="n"/>
-      <c r="J16" s="26" t="n"/>
-      <c r="K16" s="79">
-        <f>IF(C16="","",INDEX(Lists!$F$1:$F$7,1+IF(F16&lt;0,0,IF(N(H16)&lt;N(D16),1,IF(N(I16)&gt;0,2,IF(N(H16)&lt;N(D16)*'S · Save'!$C$8,3,IF(N(J16)&lt;0.25*N(D16),4,IF(N(J16)&lt;N(D16),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L16" s="22" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="37">
+        <f>IF(C16="","",C16-(D16)-(E16))</f>
+        <v/>
+      </c>
+      <c r="G16" s="51">
+        <f>IF((C16)&gt;0,F16/C16,"")</f>
+        <v/>
+      </c>
+      <c r="H16" s="27" t="n"/>
+      <c r="I16" s="27" t="n"/>
+      <c r="J16" s="27" t="n"/>
+      <c r="K16" s="82">
+        <f>IF(C16="","",CHOOSE(1+IF(F16&lt;0,0,IF((H16)&lt;(D16),1,IF((I16)&gt;0,2,IF((H16)&lt;(D16)*'S · Save'!$C$8,3,IF((J16)&lt;0.25*(D16),4,IF((J16)&lt;(D16),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L16" s="23" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="26" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="36">
-        <f>IF(C17="","",C17-N(D17)-N(E17))</f>
-        <v/>
-      </c>
-      <c r="G17" s="50">
-        <f>IF(N(C17)&gt;0,F17/C17,"")</f>
-        <v/>
-      </c>
-      <c r="H17" s="26" t="n"/>
-      <c r="I17" s="26" t="n"/>
-      <c r="J17" s="26" t="n"/>
-      <c r="K17" s="79">
-        <f>IF(C17="","",INDEX(Lists!$F$1:$F$7,1+IF(F17&lt;0,0,IF(N(H17)&lt;N(D17),1,IF(N(I17)&gt;0,2,IF(N(H17)&lt;N(D17)*'S · Save'!$C$8,3,IF(N(J17)&lt;0.25*N(D17),4,IF(N(J17)&lt;N(D17),5,6))))))))</f>
-        <v/>
-      </c>
-      <c r="L17" s="22" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="37">
+        <f>IF(C17="","",C17-(D17)-(E17))</f>
+        <v/>
+      </c>
+      <c r="G17" s="51">
+        <f>IF((C17)&gt;0,F17/C17,"")</f>
+        <v/>
+      </c>
+      <c r="H17" s="27" t="n"/>
+      <c r="I17" s="27" t="n"/>
+      <c r="J17" s="27" t="n"/>
+      <c r="K17" s="82">
+        <f>IF(C17="","",CHOOSE(1+IF(F17&lt;0,0,IF((H17)&lt;(D17),1,IF((I17)&gt;0,2,IF((H17)&lt;(D17)*'S · Save'!$C$8,3,IF((J17)&lt;0.25*(D17),4,IF((J17)&lt;(D17),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
+        <v/>
+      </c>
+      <c r="L17" s="23" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B3:L3"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H16"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Housing</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Need</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Keep</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Career (raise/promotion)</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Idea</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Level 0 · Overwhelmed</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>To do</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Utilities &amp; phone</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Want</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Cut</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Freelance / consulting</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Testing</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Level 1 · Stable</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>In progress</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Groceries</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Reduce</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Digital product</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Earning</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Level 2 · Buffered</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Done ✓</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Not sure</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Transport</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Renegotiate</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>UGC</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Paused</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Level 3 · Debt-free</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Insurance</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>YouTube / content</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Level 4 · Secure</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Childcare</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Brand deals</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Level 5 · Flexible</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Caregiving</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Affiliate</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Level 6 · Free to choose</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Investment income</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Debt payments</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Subscriptions</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Eating out</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Shopping</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Fun &amp; hobbies</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Gifts</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Travel</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2556,7 +2291,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C20"/>
+  <dimension ref="A1:C20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2565,6 +2300,7 @@
     <col width="3" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -2580,6 +2316,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="B5" s="15" t="inlineStr">
         <is>
@@ -2611,7 +2348,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="31" customHeight="1">
       <c r="B8" s="16" t="inlineStr">
         <is>
           <t>3 · Read your KEEP dashboard</t>
@@ -2623,7 +2360,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="30" customHeight="1">
+    <row r="9" ht="31" customHeight="1">
       <c r="B9" s="16" t="inlineStr">
         <is>
           <t>4 · Review once a month</t>
@@ -2635,7 +2372,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="18" customHeight="1">
       <c r="B10" s="16" t="inlineStr"/>
       <c r="C10" s="17" t="n"/>
     </row>
@@ -2646,7 +2383,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="30" customHeight="1">
+    <row r="12" ht="31" customHeight="1">
       <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Weekly money check</t>
@@ -2658,7 +2395,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="30" customHeight="1">
+    <row r="13" ht="44" customHeight="1">
       <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Heavy week?</t>
@@ -2670,7 +2407,7 @@
         </is>
       </c>
     </row>
-    <row r="14">
+    <row r="14" ht="18" customHeight="1">
       <c r="B14" s="16" t="inlineStr"/>
       <c r="C14" s="17" t="n"/>
     </row>
@@ -2681,7 +2418,7 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="18" customHeight="1">
       <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Yellow cell, blue text</t>
@@ -2693,7 +2430,7 @@
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="18" customHeight="1">
       <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Black text</t>
@@ -2705,7 +2442,7 @@
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="18" customHeight="1">
       <c r="B18" s="19" t="inlineStr">
         <is>
           <t>Bordeaux text</t>
@@ -2717,11 +2454,11 @@
         </is>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="18" customHeight="1">
       <c r="B19" s="16" t="inlineStr"/>
       <c r="C19" s="17" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="31" customHeight="1">
       <c r="B20" s="16" t="inlineStr"/>
       <c r="C20" s="17" t="inlineStr">
         <is>
@@ -2745,7 +2482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G16"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2757,6 +2494,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -2776,6 +2514,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -2809,17 +2548,15 @@
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="B6" s="21" t="n">
+        <v>1</v>
       </c>
       <c r="C6" s="16" t="inlineStr">
         <is>
           <t>Money mindset: your 9–5 is your wealth engine</t>
         </is>
       </c>
-      <c r="D6" s="21" t="inlineStr">
+      <c r="D6" s="22" t="inlineStr">
         <is>
           <t>U · Understand (real hourly value)</t>
         </is>
@@ -2829,25 +2566,23 @@
           <t>You know your real hourly value and have written your money why.</t>
         </is>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G6" s="22" t="n"/>
+      <c r="G6" s="23" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
+      <c r="B7" s="21" t="n">
+        <v>2</v>
       </c>
       <c r="C7" s="16" t="inlineStr">
         <is>
           <t>Know your salary &amp; your numbers</t>
         </is>
       </c>
-      <c r="D7" s="21" t="inlineStr">
+      <c r="D7" s="22" t="inlineStr">
         <is>
           <t>T · Track, R · Reclaim, Income Streams (Career)</t>
         </is>
@@ -2857,25 +2592,23 @@
           <t>KEEP shows your keep rate, one leak is cut and your win file is started.</t>
         </is>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G7" s="22" t="n"/>
+      <c r="G7" s="23" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
+      <c r="B8" s="21" t="n">
+        <v>3</v>
       </c>
       <c r="C8" s="16" t="inlineStr">
         <is>
           <t>Clear your debts (optional)</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="22" t="inlineStr">
         <is>
           <t>U · Understand, S · Save (starter buffer)</t>
         </is>
@@ -2885,25 +2618,23 @@
           <t>1 month of needs saved and consumer debt is €0 (Level 3).</t>
         </is>
       </c>
-      <c r="F8" s="22" t="inlineStr">
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G8" s="22" t="n"/>
+      <c r="G8" s="23" t="n"/>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
+      <c r="B9" s="21" t="n">
+        <v>4</v>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
           <t>Build a safety net</t>
         </is>
       </c>
-      <c r="D9" s="21" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
         <is>
           <t>S · Save</t>
         </is>
@@ -2913,25 +2644,23 @@
           <t>Your full emergency fund is 100% (Level 4).</t>
         </is>
       </c>
-      <c r="F9" s="22" t="inlineStr">
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G9" s="22" t="n"/>
+      <c r="G9" s="23" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="B10" s="21" t="n">
+        <v>5</v>
       </c>
       <c r="C10" s="16" t="inlineStr">
         <is>
           <t>Build wealth with smart investing</t>
         </is>
       </c>
-      <c r="D10" s="21" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>Invest</t>
         </is>
@@ -2941,25 +2670,23 @@
           <t>A fixed monthly amount runs on payday and you can explain what you own.</t>
         </is>
       </c>
-      <c r="F10" s="22" t="inlineStr">
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G10" s="22" t="n"/>
+      <c r="G10" s="23" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
+      <c r="B11" s="21" t="n">
+        <v>6</v>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
           <t>Build multiple income streams</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>Income Streams</t>
         </is>
@@ -2969,25 +2696,23 @@
           <t>One stream finished its 90-day test with a keep, change or stop decision.</t>
         </is>
       </c>
-      <c r="F11" s="22" t="inlineStr">
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G11" s="22" t="n"/>
+      <c r="G11" s="23" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+      <c r="B12" s="21" t="n">
+        <v>7</v>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
           <t>Repeat, automate &amp; buy back time</t>
         </is>
       </c>
-      <c r="D12" s="21" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>T · Time, Monthly Review</t>
         </is>
@@ -2997,26 +2722,28 @@
           <t>Transfers run on their own and you have taken back your first hours.</t>
         </is>
       </c>
-      <c r="F12" s="22" t="inlineStr">
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G12" s="22" t="n"/>
-    </row>
-    <row r="14">
+      <c r="G12" s="23" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14" ht="18" customHeight="1">
       <c r="C14" s="16" t="inlineStr">
         <is>
           <t>Stages done</t>
         </is>
       </c>
-      <c r="D14" s="23">
-        <f>COUNTIF(F6:F12,"Done ✓")&amp;" of 7"</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="C16" s="24" t="inlineStr">
+      <c r="D14" s="24">
+        <f>COUNTIF(F6:F12,"Done")&amp;" of 7"</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16" ht="31" customHeight="1">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>Stage 3 is optional: if you have no consumer debt, save the starter buffer and go straight to stage 4. Your money still grows while you pay debt off, just more slowly.</t>
         </is>
@@ -3028,14 +2755,9 @@
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="C16:G16"/>
   </mergeCells>
-  <conditionalFormatting sqref="B6:G12">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$F6="Done ✓"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="1">
     <dataValidation sqref="F6:F12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$G$1:$G$3</formula1>
+      <formula1>"To do,In progress,Done"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3049,17 +2771,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F63"/>
+  <dimension ref="A1:F63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="30" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="32" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -3078,8 +2801,9 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>MONEY IN (net, per month)</t>
         </is>
@@ -3103,79 +2827,80 @@
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Salary (net)</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Main job</t>
         </is>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="27" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Side income</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>Total from Income Streams tab</t>
         </is>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="28">
         <f>'Income Streams'!G23</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Benefits / allowances</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>e.g. child benefit, care allowance</t>
         </is>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="27" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="E10" s="26" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="E10" s="27" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="E11" s="26" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="E11" s="27" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="E12" s="26" t="n"/>
-    </row>
-    <row r="13">
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="E12" s="27" t="n"/>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="B13" s="16" t="inlineStr">
         <is>
           <t>Total money in</t>
         </is>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="29">
         <f>SUM(E7:E12)</f>
         <v/>
       </c>
     </row>
+    <row r="14"/>
     <row r="15">
-      <c r="B15" s="25" t="inlineStr">
+      <c r="B15" s="26" t="inlineStr">
         <is>
           <t>MONEY OUT (per month)</t>
         </is>
@@ -3209,491 +2934,492 @@
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="22" t="inlineStr">
+      <c r="B17" s="23" t="inlineStr">
         <is>
           <t>Rent / mortgage</t>
         </is>
       </c>
-      <c r="C17" s="22" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>Housing</t>
         </is>
       </c>
-      <c r="D17" s="22" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E17" s="26" t="n">
+      <c r="E17" s="27" t="n">
         <v>900</v>
       </c>
-      <c r="F17" s="22" t="inlineStr">
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t>Example rows: overwrite with yours</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="22" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
         <is>
           <t>Electricity, internet, phone</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>Utilities &amp; phone</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E18" s="26" t="n">
+      <c r="E18" s="27" t="n">
         <v>140</v>
       </c>
-      <c r="F18" s="22" t="n"/>
+      <c r="F18" s="23" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C19" s="22" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="D19" s="22" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="27" t="n">
         <v>320</v>
       </c>
-      <c r="F19" s="22" t="n"/>
+      <c r="F19" s="23" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Public transport / fuel</t>
         </is>
       </c>
-      <c r="C20" s="22" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="D20" s="22" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="27" t="n">
         <v>90</v>
       </c>
-      <c r="F20" s="22" t="n"/>
+      <c r="F20" s="23" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D21" s="22" t="inlineStr">
+      <c r="D21" s="23" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="27" t="n">
         <v>80</v>
       </c>
-      <c r="F21" s="22" t="n"/>
+      <c r="F21" s="23" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="22" t="inlineStr">
+      <c r="B22" s="23" t="inlineStr">
         <is>
           <t>Care support for mum</t>
         </is>
       </c>
-      <c r="C22" s="22" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Caregiving</t>
         </is>
       </c>
-      <c r="D22" s="22" t="inlineStr">
+      <c r="D22" s="23" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E22" s="26" t="n">
+      <c r="E22" s="27" t="n">
         <v>150</v>
       </c>
-      <c r="F22" s="22" t="n"/>
+      <c r="F22" s="23" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="inlineStr">
+      <c r="B23" s="23" t="inlineStr">
         <is>
           <t>Credit card minimum</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Debt payments</t>
         </is>
       </c>
-      <c r="D23" s="22" t="inlineStr">
+      <c r="D23" s="23" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E23" s="26" t="n">
+      <c r="E23" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="F23" s="22" t="n"/>
+      <c r="F23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="22" t="inlineStr">
+      <c r="B24" s="23" t="inlineStr">
         <is>
           <t>Streaming &amp; apps</t>
         </is>
       </c>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="D24" s="22" t="inlineStr">
+      <c r="D24" s="23" t="inlineStr">
         <is>
           <t>Want</t>
         </is>
       </c>
-      <c r="E24" s="26" t="n">
+      <c r="E24" s="27" t="n">
         <v>45</v>
       </c>
-      <c r="F24" s="22" t="n"/>
+      <c r="F24" s="23" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="22" t="inlineStr">
+      <c r="B25" s="23" t="inlineStr">
         <is>
           <t>Eating out &amp; takeaway</t>
         </is>
       </c>
-      <c r="C25" s="22" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>Eating out</t>
         </is>
       </c>
-      <c r="D25" s="22" t="inlineStr">
+      <c r="D25" s="23" t="inlineStr">
         <is>
           <t>Want</t>
         </is>
       </c>
-      <c r="E25" s="26" t="n">
+      <c r="E25" s="27" t="n">
         <v>120</v>
       </c>
-      <c r="F25" s="22" t="n"/>
+      <c r="F25" s="23" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="22" t="inlineStr">
+      <c r="B26" s="23" t="inlineStr">
         <is>
           <t>Clothes &amp; shopping</t>
         </is>
       </c>
-      <c r="C26" s="22" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>Shopping</t>
         </is>
       </c>
-      <c r="D26" s="22" t="inlineStr">
+      <c r="D26" s="23" t="inlineStr">
         <is>
           <t>Want</t>
         </is>
       </c>
-      <c r="E26" s="26" t="n">
+      <c r="E26" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="F26" s="22" t="n"/>
+      <c r="F26" s="23" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="22" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="22" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="23" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="23" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="22" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="22" t="n"/>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="23" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="23" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="22" t="n"/>
-      <c r="D29" s="22" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="22" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="23" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="23" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="22" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="22" t="n"/>
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="23" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="23" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="22" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="22" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="23" t="n"/>
+      <c r="E31" s="27" t="n"/>
+      <c r="F31" s="23" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="22" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="22" t="n"/>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="23" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="23" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="22" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="22" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="23" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="23" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="22" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="22" t="n"/>
+      <c r="B34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="23" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="23" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="22" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="22" t="n"/>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="23" t="n"/>
+      <c r="E35" s="27" t="n"/>
+      <c r="F35" s="23" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="22" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="22" t="n"/>
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="23" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="23" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="22" t="n"/>
-      <c r="C37" s="22" t="n"/>
-      <c r="D37" s="22" t="n"/>
-      <c r="E37" s="26" t="n"/>
-      <c r="F37" s="22" t="n"/>
+      <c r="B37" s="23" t="n"/>
+      <c r="C37" s="23" t="n"/>
+      <c r="D37" s="23" t="n"/>
+      <c r="E37" s="27" t="n"/>
+      <c r="F37" s="23" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="22" t="n"/>
-      <c r="C38" s="22" t="n"/>
-      <c r="D38" s="22" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="22" t="n"/>
+      <c r="B38" s="23" t="n"/>
+      <c r="C38" s="23" t="n"/>
+      <c r="D38" s="23" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="23" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="22" t="n"/>
-      <c r="C39" s="22" t="n"/>
-      <c r="D39" s="22" t="n"/>
-      <c r="E39" s="26" t="n"/>
-      <c r="F39" s="22" t="n"/>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="27" t="n"/>
+      <c r="F39" s="23" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="22" t="n"/>
-      <c r="C40" s="22" t="n"/>
-      <c r="D40" s="22" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="22" t="n"/>
+      <c r="B40" s="23" t="n"/>
+      <c r="C40" s="23" t="n"/>
+      <c r="D40" s="23" t="n"/>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="23" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="22" t="n"/>
-      <c r="C41" s="22" t="n"/>
-      <c r="D41" s="22" t="n"/>
-      <c r="E41" s="26" t="n"/>
-      <c r="F41" s="22" t="n"/>
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="27" t="n"/>
+      <c r="F41" s="23" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="22" t="n"/>
-      <c r="C42" s="22" t="n"/>
-      <c r="D42" s="22" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="22" t="n"/>
+      <c r="B42" s="23" t="n"/>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="23" t="n"/>
+      <c r="E42" s="27" t="n"/>
+      <c r="F42" s="23" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="22" t="n"/>
-      <c r="C43" s="22" t="n"/>
-      <c r="D43" s="22" t="n"/>
-      <c r="E43" s="26" t="n"/>
-      <c r="F43" s="22" t="n"/>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="27" t="n"/>
+      <c r="F43" s="23" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="22" t="n"/>
-      <c r="C44" s="22" t="n"/>
-      <c r="D44" s="22" t="n"/>
-      <c r="E44" s="26" t="n"/>
-      <c r="F44" s="22" t="n"/>
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="23" t="n"/>
+      <c r="E44" s="27" t="n"/>
+      <c r="F44" s="23" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="22" t="n"/>
-      <c r="C45" s="22" t="n"/>
-      <c r="D45" s="22" t="n"/>
-      <c r="E45" s="26" t="n"/>
-      <c r="F45" s="22" t="n"/>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="27" t="n"/>
+      <c r="F45" s="23" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="22" t="n"/>
-      <c r="C46" s="22" t="n"/>
-      <c r="D46" s="22" t="n"/>
-      <c r="E46" s="26" t="n"/>
-      <c r="F46" s="22" t="n"/>
+      <c r="B46" s="23" t="n"/>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="27" t="n"/>
+      <c r="F46" s="23" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="22" t="n"/>
-      <c r="C47" s="22" t="n"/>
-      <c r="D47" s="22" t="n"/>
-      <c r="E47" s="26" t="n"/>
-      <c r="F47" s="22" t="n"/>
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="27" t="n"/>
+      <c r="F47" s="23" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="22" t="n"/>
-      <c r="C48" s="22" t="n"/>
-      <c r="D48" s="22" t="n"/>
-      <c r="E48" s="26" t="n"/>
-      <c r="F48" s="22" t="n"/>
+      <c r="B48" s="23" t="n"/>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="23" t="n"/>
+      <c r="E48" s="27" t="n"/>
+      <c r="F48" s="23" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="22" t="n"/>
-      <c r="C49" s="22" t="n"/>
-      <c r="D49" s="22" t="n"/>
-      <c r="E49" s="26" t="n"/>
-      <c r="F49" s="22" t="n"/>
+      <c r="B49" s="23" t="n"/>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="23" t="n"/>
+      <c r="E49" s="27" t="n"/>
+      <c r="F49" s="23" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="22" t="n"/>
-      <c r="C50" s="22" t="n"/>
-      <c r="D50" s="22" t="n"/>
-      <c r="E50" s="26" t="n"/>
-      <c r="F50" s="22" t="n"/>
+      <c r="B50" s="23" t="n"/>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="27" t="n"/>
+      <c r="F50" s="23" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="22" t="n"/>
-      <c r="C51" s="22" t="n"/>
-      <c r="D51" s="22" t="n"/>
-      <c r="E51" s="26" t="n"/>
-      <c r="F51" s="22" t="n"/>
+      <c r="B51" s="23" t="n"/>
+      <c r="C51" s="23" t="n"/>
+      <c r="D51" s="23" t="n"/>
+      <c r="E51" s="27" t="n"/>
+      <c r="F51" s="23" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="22" t="n"/>
-      <c r="C52" s="22" t="n"/>
-      <c r="D52" s="22" t="n"/>
-      <c r="E52" s="26" t="n"/>
-      <c r="F52" s="22" t="n"/>
+      <c r="B52" s="23" t="n"/>
+      <c r="C52" s="23" t="n"/>
+      <c r="D52" s="23" t="n"/>
+      <c r="E52" s="27" t="n"/>
+      <c r="F52" s="23" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="22" t="n"/>
-      <c r="C53" s="22" t="n"/>
-      <c r="D53" s="22" t="n"/>
-      <c r="E53" s="26" t="n"/>
-      <c r="F53" s="22" t="n"/>
+      <c r="B53" s="23" t="n"/>
+      <c r="C53" s="23" t="n"/>
+      <c r="D53" s="23" t="n"/>
+      <c r="E53" s="27" t="n"/>
+      <c r="F53" s="23" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="22" t="n"/>
-      <c r="C54" s="22" t="n"/>
-      <c r="D54" s="22" t="n"/>
-      <c r="E54" s="26" t="n"/>
-      <c r="F54" s="22" t="n"/>
+      <c r="B54" s="23" t="n"/>
+      <c r="C54" s="23" t="n"/>
+      <c r="D54" s="23" t="n"/>
+      <c r="E54" s="27" t="n"/>
+      <c r="F54" s="23" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="22" t="n"/>
-      <c r="C55" s="22" t="n"/>
-      <c r="D55" s="22" t="n"/>
-      <c r="E55" s="26" t="n"/>
-      <c r="F55" s="22" t="n"/>
+      <c r="B55" s="23" t="n"/>
+      <c r="C55" s="23" t="n"/>
+      <c r="D55" s="23" t="n"/>
+      <c r="E55" s="27" t="n"/>
+      <c r="F55" s="23" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="22" t="n"/>
-      <c r="C56" s="22" t="n"/>
-      <c r="D56" s="22" t="n"/>
-      <c r="E56" s="26" t="n"/>
-      <c r="F56" s="22" t="n"/>
-    </row>
-    <row r="58">
+      <c r="B56" s="23" t="n"/>
+      <c r="C56" s="23" t="n"/>
+      <c r="D56" s="23" t="n"/>
+      <c r="E56" s="27" t="n"/>
+      <c r="F56" s="23" t="n"/>
+    </row>
+    <row r="57"/>
+    <row r="58" ht="18" customHeight="1">
       <c r="B58" s="16" t="inlineStr">
         <is>
           <t>Needs (your baseline)</t>
         </is>
       </c>
-      <c r="E58" s="28">
+      <c r="E58" s="29">
         <f>SUMIF(D17:D56,"Need",E17:E56)</f>
         <v/>
       </c>
     </row>
-    <row r="59">
+    <row r="59" ht="18" customHeight="1">
       <c r="B59" s="16" t="inlineStr">
         <is>
           <t>Wants</t>
         </is>
       </c>
-      <c r="E59" s="28">
+      <c r="E59" s="29">
         <f>SUMIF(D17:D56,"Want",E17:E56)</f>
         <v/>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="29" t="inlineStr">
+    <row r="60" ht="18" customHeight="1">
+      <c r="B60" s="30" t="inlineStr">
         <is>
           <t>of which caregiving</t>
         </is>
       </c>
-      <c r="E60" s="30">
+      <c r="E60" s="31">
         <f>SUMIF(C17:C56,"Caregiving",E17:E56)</f>
         <v/>
       </c>
     </row>
-    <row r="61">
-      <c r="B61" s="31" t="inlineStr">
+    <row r="61" ht="18" customHeight="1">
+      <c r="B61" s="32" t="inlineStr">
         <is>
           <t>Unsorted (pick Need or Want)</t>
         </is>
       </c>
-      <c r="E61" s="32">
+      <c r="E61" s="33">
         <f>SUM(E17:E56)-E58-E59</f>
         <v/>
       </c>
     </row>
-    <row r="62">
-      <c r="B62" s="33" t="inlineStr">
+    <row r="62" ht="18" customHeight="1">
+      <c r="B62" s="34" t="inlineStr">
         <is>
           <t>KEEP (in − needs − wants)</t>
         </is>
       </c>
-      <c r="E62" s="34">
+      <c r="E62" s="35">
         <f>E13-E58-E59</f>
         <v/>
       </c>
     </row>
-    <row r="63">
-      <c r="B63" s="33" t="inlineStr">
+    <row r="63" ht="18" customHeight="1">
+      <c r="B63" s="34" t="inlineStr">
         <is>
           <t>Keep rate</t>
         </is>
       </c>
-      <c r="E63" s="35">
+      <c r="E63" s="36">
         <f>IF(E13&gt;0,E62/E13,0)</f>
         <v/>
       </c>
@@ -3705,10 +3431,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C17:C56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$A$1:$A$16</formula1>
+      <formula1>"Housing,Utilities &amp; phone,Groceries,Transport,Insurance,Childcare,Caregiving,Health,Debt payments,Subscriptions,Eating out,Shopping,Fun &amp; hobbies,Gifts,Travel,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="D17:D56" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$B$1:$B$2</formula1>
+      <formula1>"Need,Want"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3723,7 +3449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3732,9 +3458,10 @@
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="33" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -3754,6 +3481,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -3787,364 +3515,366 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Second streaming service</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="27" t="n">
         <v>13</v>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Cut</t>
         </is>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="36">
-        <f>IF(OR(C6="",D6="",D6="Keep"),0,MAX(0,C6-N(E6)))</f>
-        <v/>
-      </c>
-      <c r="G6" s="22" t="inlineStr">
+      <c r="F6" s="37">
+        <f>IF(OR(C6="",D6="",D6="Keep"),0,MAX(0,C6-(E6)))</f>
+        <v/>
+      </c>
+      <c r="G6" s="23" t="inlineStr">
         <is>
           <t>Cancel before renewal on the 15th</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Gym (not used since spring)</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Reduce</t>
         </is>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="36">
-        <f>IF(OR(C7="",D7="",D7="Keep"),0,MAX(0,C7-N(E7)))</f>
-        <v/>
-      </c>
-      <c r="G7" s="22" t="inlineStr">
+      <c r="F7" s="37">
+        <f>IF(OR(C7="",D7="",D7="Keep"),0,MAX(0,C7-(E7)))</f>
+        <v/>
+      </c>
+      <c r="G7" s="23" t="inlineStr">
         <is>
           <t>Switch to off-peak plan</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>Mobile contract</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Renegotiate</t>
         </is>
       </c>
-      <c r="E8" s="26" t="n">
+      <c r="E8" s="27" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="36">
-        <f>IF(OR(C8="",D8="",D8="Keep"),0,MAX(0,C8-N(E8)))</f>
-        <v/>
-      </c>
-      <c r="G8" s="22" t="inlineStr">
+      <c r="F8" s="37">
+        <f>IF(OR(C8="",D8="",D8="Keep"),0,MAX(0,C8-(E8)))</f>
+        <v/>
+      </c>
+      <c r="G8" s="23" t="inlineStr">
         <is>
           <t>Call and ask for current tariff</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t>Cloud storage</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="36">
-        <f>IF(OR(C9="",D9="",D9="Keep"),0,MAX(0,C9-N(E9)))</f>
-        <v/>
-      </c>
-      <c r="G9" s="22" t="inlineStr"/>
+      <c r="F9" s="37">
+        <f>IF(OR(C9="",D9="",D9="Keep"),0,MAX(0,C9-(E9)))</f>
+        <v/>
+      </c>
+      <c r="G9" s="23" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="36">
-        <f>IF(OR(C10="",D10="",D10="Keep"),0,MAX(0,C10-N(E10)))</f>
-        <v/>
-      </c>
-      <c r="G10" s="22" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="37">
+        <f>IF(OR(C10="",D10="",D10="Keep"),0,MAX(0,C10-(E10)))</f>
+        <v/>
+      </c>
+      <c r="G10" s="23" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="36">
-        <f>IF(OR(C11="",D11="",D11="Keep"),0,MAX(0,C11-N(E11)))</f>
-        <v/>
-      </c>
-      <c r="G11" s="22" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="37">
+        <f>IF(OR(C11="",D11="",D11="Keep"),0,MAX(0,C11-(E11)))</f>
+        <v/>
+      </c>
+      <c r="G11" s="23" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="36">
-        <f>IF(OR(C12="",D12="",D12="Keep"),0,MAX(0,C12-N(E12)))</f>
-        <v/>
-      </c>
-      <c r="G12" s="22" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="37">
+        <f>IF(OR(C12="",D12="",D12="Keep"),0,MAX(0,C12-(E12)))</f>
+        <v/>
+      </c>
+      <c r="G12" s="23" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="36">
-        <f>IF(OR(C13="",D13="",D13="Keep"),0,MAX(0,C13-N(E13)))</f>
-        <v/>
-      </c>
-      <c r="G13" s="22" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="37">
+        <f>IF(OR(C13="",D13="",D13="Keep"),0,MAX(0,C13-(E13)))</f>
+        <v/>
+      </c>
+      <c r="G13" s="23" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="36">
-        <f>IF(OR(C14="",D14="",D14="Keep"),0,MAX(0,C14-N(E14)))</f>
-        <v/>
-      </c>
-      <c r="G14" s="22" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="37">
+        <f>IF(OR(C14="",D14="",D14="Keep"),0,MAX(0,C14-(E14)))</f>
+        <v/>
+      </c>
+      <c r="G14" s="23" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="36">
-        <f>IF(OR(C15="",D15="",D15="Keep"),0,MAX(0,C15-N(E15)))</f>
-        <v/>
-      </c>
-      <c r="G15" s="22" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="37">
+        <f>IF(OR(C15="",D15="",D15="Keep"),0,MAX(0,C15-(E15)))</f>
+        <v/>
+      </c>
+      <c r="G15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="36">
-        <f>IF(OR(C16="",D16="",D16="Keep"),0,MAX(0,C16-N(E16)))</f>
-        <v/>
-      </c>
-      <c r="G16" s="22" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="37">
+        <f>IF(OR(C16="",D16="",D16="Keep"),0,MAX(0,C16-(E16)))</f>
+        <v/>
+      </c>
+      <c r="G16" s="23" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="26" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="26" t="n"/>
-      <c r="F17" s="36">
-        <f>IF(OR(C17="",D17="",D17="Keep"),0,MAX(0,C17-N(E17)))</f>
-        <v/>
-      </c>
-      <c r="G17" s="22" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="37">
+        <f>IF(OR(C17="",D17="",D17="Keep"),0,MAX(0,C17-(E17)))</f>
+        <v/>
+      </c>
+      <c r="G17" s="23" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="36">
-        <f>IF(OR(C18="",D18="",D18="Keep"),0,MAX(0,C18-N(E18)))</f>
-        <v/>
-      </c>
-      <c r="G18" s="22" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="37">
+        <f>IF(OR(C18="",D18="",D18="Keep"),0,MAX(0,C18-(E18)))</f>
+        <v/>
+      </c>
+      <c r="G18" s="23" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="26" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="26" t="n"/>
-      <c r="F19" s="36">
-        <f>IF(OR(C19="",D19="",D19="Keep"),0,MAX(0,C19-N(E19)))</f>
-        <v/>
-      </c>
-      <c r="G19" s="22" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="37">
+        <f>IF(OR(C19="",D19="",D19="Keep"),0,MAX(0,C19-(E19)))</f>
+        <v/>
+      </c>
+      <c r="G19" s="23" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="36">
-        <f>IF(OR(C20="",D20="",D20="Keep"),0,MAX(0,C20-N(E20)))</f>
-        <v/>
-      </c>
-      <c r="G20" s="22" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="37">
+        <f>IF(OR(C20="",D20="",D20="Keep"),0,MAX(0,C20-(E20)))</f>
+        <v/>
+      </c>
+      <c r="G20" s="23" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="26" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="26" t="n"/>
-      <c r="F21" s="36">
-        <f>IF(OR(C21="",D21="",D21="Keep"),0,MAX(0,C21-N(E21)))</f>
-        <v/>
-      </c>
-      <c r="G21" s="22" t="n"/>
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="37">
+        <f>IF(OR(C21="",D21="",D21="Keep"),0,MAX(0,C21-(E21)))</f>
+        <v/>
+      </c>
+      <c r="G21" s="23" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="22" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="36">
-        <f>IF(OR(C22="",D22="",D22="Keep"),0,MAX(0,C22-N(E22)))</f>
-        <v/>
-      </c>
-      <c r="G22" s="22" t="n"/>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="23" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="37">
+        <f>IF(OR(C22="",D22="",D22="Keep"),0,MAX(0,C22-(E22)))</f>
+        <v/>
+      </c>
+      <c r="G22" s="23" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="22" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="36">
-        <f>IF(OR(C23="",D23="",D23="Keep"),0,MAX(0,C23-N(E23)))</f>
-        <v/>
-      </c>
-      <c r="G23" s="22" t="n"/>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="23" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="37">
+        <f>IF(OR(C23="",D23="",D23="Keep"),0,MAX(0,C23-(E23)))</f>
+        <v/>
+      </c>
+      <c r="G23" s="23" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="22" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="36">
-        <f>IF(OR(C24="",D24="",D24="Keep"),0,MAX(0,C24-N(E24)))</f>
-        <v/>
-      </c>
-      <c r="G24" s="22" t="n"/>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="23" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="37">
+        <f>IF(OR(C24="",D24="",D24="Keep"),0,MAX(0,C24-(E24)))</f>
+        <v/>
+      </c>
+      <c r="G24" s="23" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="22" t="n"/>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="36">
-        <f>IF(OR(C25="",D25="",D25="Keep"),0,MAX(0,C25-N(E25)))</f>
-        <v/>
-      </c>
-      <c r="G25" s="22" t="n"/>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="23" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="37">
+        <f>IF(OR(C25="",D25="",D25="Keep"),0,MAX(0,C25-(E25)))</f>
+        <v/>
+      </c>
+      <c r="G25" s="23" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="22" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="36">
-        <f>IF(OR(C26="",D26="",D26="Keep"),0,MAX(0,C26-N(E26)))</f>
-        <v/>
-      </c>
-      <c r="G26" s="22" t="n"/>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="23" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="37">
+        <f>IF(OR(C26="",D26="",D26="Keep"),0,MAX(0,C26-(E26)))</f>
+        <v/>
+      </c>
+      <c r="G26" s="23" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="22" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="36">
-        <f>IF(OR(C27="",D27="",D27="Keep"),0,MAX(0,C27-N(E27)))</f>
-        <v/>
-      </c>
-      <c r="G27" s="22" t="n"/>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="23" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="37">
+        <f>IF(OR(C27="",D27="",D27="Keep"),0,MAX(0,C27-(E27)))</f>
+        <v/>
+      </c>
+      <c r="G27" s="23" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="22" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="36">
-        <f>IF(OR(C28="",D28="",D28="Keep"),0,MAX(0,C28-N(E28)))</f>
-        <v/>
-      </c>
-      <c r="G28" s="22" t="n"/>
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="23" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="37">
+        <f>IF(OR(C28="",D28="",D28="Keep"),0,MAX(0,C28-(E28)))</f>
+        <v/>
+      </c>
+      <c r="G28" s="23" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="26" t="n"/>
-      <c r="D29" s="22" t="n"/>
-      <c r="E29" s="26" t="n"/>
-      <c r="F29" s="36">
-        <f>IF(OR(C29="",D29="",D29="Keep"),0,MAX(0,C29-N(E29)))</f>
-        <v/>
-      </c>
-      <c r="G29" s="22" t="n"/>
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="27" t="n"/>
+      <c r="D29" s="23" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="37">
+        <f>IF(OR(C29="",D29="",D29="Keep"),0,MAX(0,C29-(E29)))</f>
+        <v/>
+      </c>
+      <c r="G29" s="23" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="22" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="22" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="36">
-        <f>IF(OR(C30="",D30="",D30="Keep"),0,MAX(0,C30-N(E30)))</f>
-        <v/>
-      </c>
-      <c r="G30" s="22" t="n"/>
-    </row>
-    <row r="32">
+      <c r="B30" s="23" t="n"/>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="23" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="37">
+        <f>IF(OR(C30="",D30="",D30="Keep"),0,MAX(0,C30-(E30)))</f>
+        <v/>
+      </c>
+      <c r="G30" s="23" t="n"/>
+    </row>
+    <row r="31"/>
+    <row r="32" ht="18" customHeight="1">
       <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Reclaimable per month</t>
         </is>
       </c>
-      <c r="F32" s="34">
+      <c r="F32" s="35">
         <f>SUM(F6:F30)</f>
         <v/>
       </c>
     </row>
-    <row r="33">
+    <row r="33" ht="18" customHeight="1">
       <c r="B33" s="16" t="inlineStr">
         <is>
           <t>Reclaimable per year</t>
         </is>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <f>F32*12</f>
         <v/>
       </c>
     </row>
+    <row r="34"/>
     <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="24" t="inlineStr">
+      <c r="B35" s="25" t="inlineStr">
         <is>
           <t>Rule: reclaimed money gets a job the same day. Move it to your buffer or debt before it disappears into everyday spending.</t>
         </is>
@@ -4158,7 +3888,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="D6:D30" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$C$1:$C$4</formula1>
+      <formula1>"Keep,Cut,Reduce,Renegotiate"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4172,7 +3902,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I31"/>
+  <dimension ref="A1:I31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4182,10 +3912,11 @@
     <col width="14" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -4207,6 +3938,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -4250,259 +3982,262 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Credit card</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="37" t="n">
+      <c r="D6" s="38" t="n">
         <v>0.199</v>
       </c>
-      <c r="E6" s="26" t="n">
+      <c r="E6" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="F6" s="26" t="n">
+      <c r="F6" s="27" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="38">
-        <f>IF(N(C6)&gt;0,C6*N(D6)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H6" s="39">
-        <f>IF(N(C6)&lt;=0,"",IF(N(E6)+N(F6)&lt;=G6,"Payment too low",ROUNDUP(IF(N(D6)=0,C6/(N(E6)+N(F6)),NPER(D6/12,-(N(E6)+N(F6)),C6)),0)))</f>
-        <v/>
-      </c>
-      <c r="I6" s="40">
-        <f>IF(N(C6)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D6))+1)</f>
+      <c r="G6" s="39">
+        <f>IF((C6)&gt;0,C6*(D6)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H6" s="40">
+        <f>IF((C6)&lt;=0,"",IF((E6)+(F6)&lt;=G6,"Payment too low",ROUNDUP(IF((D6)=0,C6/((E6)+(F6)),NPER(D6/12,-((E6)+(F6)),C6)),0)))</f>
+        <v/>
+      </c>
+      <c r="I6" s="41">
+        <f>IF((C6)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D6))+1)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Overdraft</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="37" t="n">
+      <c r="D7" s="38" t="n">
         <v>0.12</v>
       </c>
-      <c r="E7" s="26" t="n">
+      <c r="E7" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="26" t="n">
+      <c r="F7" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="38">
-        <f>IF(N(C7)&gt;0,C7*N(D7)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H7" s="39">
-        <f>IF(N(C7)&lt;=0,"",IF(N(E7)+N(F7)&lt;=G7,"Payment too low",ROUNDUP(IF(N(D7)=0,C7/(N(E7)+N(F7)),NPER(D7/12,-(N(E7)+N(F7)),C7)),0)))</f>
-        <v/>
-      </c>
-      <c r="I7" s="40">
-        <f>IF(N(C7)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D7))+1)</f>
+      <c r="G7" s="39">
+        <f>IF((C7)&gt;0,C7*(D7)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H7" s="40">
+        <f>IF((C7)&lt;=0,"",IF((E7)+(F7)&lt;=G7,"Payment too low",ROUNDUP(IF((D7)=0,C7/((E7)+(F7)),NPER(D7/12,-((E7)+(F7)),C7)),0)))</f>
+        <v/>
+      </c>
+      <c r="I7" s="41">
+        <f>IF((C7)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D7))+1)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="22" t="n"/>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="37" t="n"/>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="26" t="n"/>
-      <c r="G8" s="38">
-        <f>IF(N(C8)&gt;0,C8*N(D8)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H8" s="39">
-        <f>IF(N(C8)&lt;=0,"",IF(N(E8)+N(F8)&lt;=G8,"Payment too low",ROUNDUP(IF(N(D8)=0,C8/(N(E8)+N(F8)),NPER(D8/12,-(N(E8)+N(F8)),C8)),0)))</f>
-        <v/>
-      </c>
-      <c r="I8" s="40">
-        <f>IF(N(C8)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D8))+1)</f>
+      <c r="B8" s="23" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="38" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="39">
+        <f>IF((C8)&gt;0,C8*(D8)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H8" s="40">
+        <f>IF((C8)&lt;=0,"",IF((E8)+(F8)&lt;=G8,"Payment too low",ROUNDUP(IF((D8)=0,C8/((E8)+(F8)),NPER(D8/12,-((E8)+(F8)),C8)),0)))</f>
+        <v/>
+      </c>
+      <c r="I8" s="41">
+        <f>IF((C8)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D8))+1)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="26" t="n"/>
-      <c r="D9" s="37" t="n"/>
-      <c r="E9" s="26" t="n"/>
-      <c r="F9" s="26" t="n"/>
-      <c r="G9" s="38">
-        <f>IF(N(C9)&gt;0,C9*N(D9)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H9" s="39">
-        <f>IF(N(C9)&lt;=0,"",IF(N(E9)+N(F9)&lt;=G9,"Payment too low",ROUNDUP(IF(N(D9)=0,C9/(N(E9)+N(F9)),NPER(D9/12,-(N(E9)+N(F9)),C9)),0)))</f>
-        <v/>
-      </c>
-      <c r="I9" s="40">
-        <f>IF(N(C9)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D9))+1)</f>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="27" t="n"/>
+      <c r="D9" s="38" t="n"/>
+      <c r="E9" s="27" t="n"/>
+      <c r="F9" s="27" t="n"/>
+      <c r="G9" s="39">
+        <f>IF((C9)&gt;0,C9*(D9)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H9" s="40">
+        <f>IF((C9)&lt;=0,"",IF((E9)+(F9)&lt;=G9,"Payment too low",ROUNDUP(IF((D9)=0,C9/((E9)+(F9)),NPER(D9/12,-((E9)+(F9)),C9)),0)))</f>
+        <v/>
+      </c>
+      <c r="I9" s="41">
+        <f>IF((C9)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D9))+1)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="37" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="38">
-        <f>IF(N(C10)&gt;0,C10*N(D10)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H10" s="39">
-        <f>IF(N(C10)&lt;=0,"",IF(N(E10)+N(F10)&lt;=G10,"Payment too low",ROUNDUP(IF(N(D10)=0,C10/(N(E10)+N(F10)),NPER(D10/12,-(N(E10)+N(F10)),C10)),0)))</f>
-        <v/>
-      </c>
-      <c r="I10" s="40">
-        <f>IF(N(C10)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D10))+1)</f>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="38" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="39">
+        <f>IF((C10)&gt;0,C10*(D10)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H10" s="40">
+        <f>IF((C10)&lt;=0,"",IF((E10)+(F10)&lt;=G10,"Payment too low",ROUNDUP(IF((D10)=0,C10/((E10)+(F10)),NPER(D10/12,-((E10)+(F10)),C10)),0)))</f>
+        <v/>
+      </c>
+      <c r="I10" s="41">
+        <f>IF((C10)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D10))+1)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="26" t="n"/>
-      <c r="D11" s="37" t="n"/>
-      <c r="E11" s="26" t="n"/>
-      <c r="F11" s="26" t="n"/>
-      <c r="G11" s="38">
-        <f>IF(N(C11)&gt;0,C11*N(D11)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H11" s="39">
-        <f>IF(N(C11)&lt;=0,"",IF(N(E11)+N(F11)&lt;=G11,"Payment too low",ROUNDUP(IF(N(D11)=0,C11/(N(E11)+N(F11)),NPER(D11/12,-(N(E11)+N(F11)),C11)),0)))</f>
-        <v/>
-      </c>
-      <c r="I11" s="40">
-        <f>IF(N(C11)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D11))+1)</f>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="38" t="n"/>
+      <c r="E11" s="27" t="n"/>
+      <c r="F11" s="27" t="n"/>
+      <c r="G11" s="39">
+        <f>IF((C11)&gt;0,C11*(D11)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H11" s="40">
+        <f>IF((C11)&lt;=0,"",IF((E11)+(F11)&lt;=G11,"Payment too low",ROUNDUP(IF((D11)=0,C11/((E11)+(F11)),NPER(D11/12,-((E11)+(F11)),C11)),0)))</f>
+        <v/>
+      </c>
+      <c r="I11" s="41">
+        <f>IF((C11)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D11))+1)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="37" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="38">
-        <f>IF(N(C12)&gt;0,C12*N(D12)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H12" s="39">
-        <f>IF(N(C12)&lt;=0,"",IF(N(E12)+N(F12)&lt;=G12,"Payment too low",ROUNDUP(IF(N(D12)=0,C12/(N(E12)+N(F12)),NPER(D12/12,-(N(E12)+N(F12)),C12)),0)))</f>
-        <v/>
-      </c>
-      <c r="I12" s="40">
-        <f>IF(N(C12)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D12))+1)</f>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="38" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="39">
+        <f>IF((C12)&gt;0,C12*(D12)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H12" s="40">
+        <f>IF((C12)&lt;=0,"",IF((E12)+(F12)&lt;=G12,"Payment too low",ROUNDUP(IF((D12)=0,C12/((E12)+(F12)),NPER(D12/12,-((E12)+(F12)),C12)),0)))</f>
+        <v/>
+      </c>
+      <c r="I12" s="41">
+        <f>IF((C12)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D12))+1)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="26" t="n"/>
-      <c r="D13" s="37" t="n"/>
-      <c r="E13" s="26" t="n"/>
-      <c r="F13" s="26" t="n"/>
-      <c r="G13" s="38">
-        <f>IF(N(C13)&gt;0,C13*N(D13)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H13" s="39">
-        <f>IF(N(C13)&lt;=0,"",IF(N(E13)+N(F13)&lt;=G13,"Payment too low",ROUNDUP(IF(N(D13)=0,C13/(N(E13)+N(F13)),NPER(D13/12,-(N(E13)+N(F13)),C13)),0)))</f>
-        <v/>
-      </c>
-      <c r="I13" s="40">
-        <f>IF(N(C13)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D13))+1)</f>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="27" t="n"/>
+      <c r="D13" s="38" t="n"/>
+      <c r="E13" s="27" t="n"/>
+      <c r="F13" s="27" t="n"/>
+      <c r="G13" s="39">
+        <f>IF((C13)&gt;0,C13*(D13)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H13" s="40">
+        <f>IF((C13)&lt;=0,"",IF((E13)+(F13)&lt;=G13,"Payment too low",ROUNDUP(IF((D13)=0,C13/((E13)+(F13)),NPER(D13/12,-((E13)+(F13)),C13)),0)))</f>
+        <v/>
+      </c>
+      <c r="I13" s="41">
+        <f>IF((C13)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D13))+1)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="37" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="38">
-        <f>IF(N(C14)&gt;0,C14*N(D14)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H14" s="39">
-        <f>IF(N(C14)&lt;=0,"",IF(N(E14)+N(F14)&lt;=G14,"Payment too low",ROUNDUP(IF(N(D14)=0,C14/(N(E14)+N(F14)),NPER(D14/12,-(N(E14)+N(F14)),C14)),0)))</f>
-        <v/>
-      </c>
-      <c r="I14" s="40">
-        <f>IF(N(C14)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D14))+1)</f>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="38" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="39">
+        <f>IF((C14)&gt;0,C14*(D14)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H14" s="40">
+        <f>IF((C14)&lt;=0,"",IF((E14)+(F14)&lt;=G14,"Payment too low",ROUNDUP(IF((D14)=0,C14/((E14)+(F14)),NPER(D14/12,-((E14)+(F14)),C14)),0)))</f>
+        <v/>
+      </c>
+      <c r="I14" s="41">
+        <f>IF((C14)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D14))+1)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="26" t="n"/>
-      <c r="D15" s="37" t="n"/>
-      <c r="E15" s="26" t="n"/>
-      <c r="F15" s="26" t="n"/>
-      <c r="G15" s="38">
-        <f>IF(N(C15)&gt;0,C15*N(D15)/12,0)</f>
-        <v/>
-      </c>
-      <c r="H15" s="39">
-        <f>IF(N(C15)&lt;=0,"",IF(N(E15)+N(F15)&lt;=G15,"Payment too low",ROUNDUP(IF(N(D15)=0,C15/(N(E15)+N(F15)),NPER(D15/12,-(N(E15)+N(F15)),C15)),0)))</f>
-        <v/>
-      </c>
-      <c r="I15" s="40">
-        <f>IF(N(C15)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;N(D15))+1)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="38" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
+      <c r="G15" s="39">
+        <f>IF((C15)&gt;0,C15*(D15)/12,0)</f>
+        <v/>
+      </c>
+      <c r="H15" s="40">
+        <f>IF((C15)&lt;=0,"",IF((E15)+(F15)&lt;=G15,"Payment too low",ROUNDUP(IF((D15)=0,C15/((E15)+(F15)),NPER(D15/12,-((E15)+(F15)),C15)),0)))</f>
+        <v/>
+      </c>
+      <c r="I15" s="41">
+        <f>IF((C15)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D15))+1)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17" ht="18" customHeight="1">
       <c r="B17" s="16" t="inlineStr">
         <is>
           <t>Total debt</t>
         </is>
       </c>
-      <c r="C17" s="41">
+      <c r="C17" s="42">
         <f>SUM(C6:C15)</f>
         <v/>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>Priority 1 = highest interest rate. Send every extra euro there, pay minimums on the rest. Months to clear is an estimate with fixed payments.</t>
         </is>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="18" customHeight="1">
       <c r="B18" s="16" t="inlineStr">
         <is>
           <t>Interest you pay / month</t>
         </is>
       </c>
-      <c r="C18" s="42">
+      <c r="C18" s="43">
         <f>SUM(G6:G15)</f>
         <v/>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="18" customHeight="1">
       <c r="B19" s="16" t="inlineStr">
         <is>
           <t>Interest you pay / year</t>
         </is>
       </c>
-      <c r="C19" s="41">
+      <c r="C19" s="42">
         <f>C18*12</f>
         <v/>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22">
-      <c r="B22" s="25" t="inlineStr">
+      <c r="B22" s="26" t="inlineStr">
         <is>
           <t>WHAT ONE HOUR OF YOUR LIFE IS WORTH</t>
         </is>
@@ -4520,97 +4255,97 @@
         </is>
       </c>
     </row>
-    <row r="24">
+    <row r="24" ht="18" customHeight="1">
       <c r="B24" s="17" t="inlineStr">
         <is>
           <t>Net money in / month</t>
         </is>
       </c>
-      <c r="C24" s="43">
+      <c r="C24" s="44">
         <f>'T · Track'!E7</f>
         <v/>
       </c>
-      <c r="D24" s="24" t="inlineStr">
+      <c r="D24" s="25" t="inlineStr">
         <is>
           <t>Keep your first hour: the first hour of every workday is paid to you, not to your bills. Set up a standing transfer for this amount on payday. If it's too much right now, start with a quarter of it.</t>
         </is>
       </c>
     </row>
-    <row r="25">
+    <row r="25" ht="18" customHeight="1">
       <c r="B25" s="17" t="inlineStr">
         <is>
           <t>Contract hours / week</t>
         </is>
       </c>
-      <c r="C25" s="44" t="n">
+      <c r="C25" s="45" t="n">
         <v>39</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="18" customHeight="1">
       <c r="B26" s="17" t="inlineStr">
         <is>
           <t>Unpaid overtime / week</t>
         </is>
       </c>
-      <c r="C26" s="44" t="n">
+      <c r="C26" s="45" t="n">
         <v>4</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" ht="18" customHeight="1">
       <c r="B27" s="17" t="inlineStr">
         <is>
           <t>Commute hours / week</t>
         </is>
       </c>
-      <c r="C27" s="44" t="n">
+      <c r="C27" s="45" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="45" t="inlineStr">
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="46" t="inlineStr">
         <is>
           <t>Real hours / month</t>
         </is>
       </c>
-      <c r="C28" s="46">
-        <f>(N(C25)+N(C26)+N(C27))*52/12</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="33" t="inlineStr">
+      <c r="C28" s="47">
+        <f>((C25)+(C26)+(C27))*52/12</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29" ht="18" customHeight="1">
+      <c r="B29" s="34" t="inlineStr">
         <is>
           <t>Your real hourly value</t>
         </is>
       </c>
-      <c r="C29" s="47">
+      <c r="C29" s="48">
         <f>IF(C28&gt;0,C24/C28,0)</f>
         <v/>
       </c>
-      <c r="D29" s="24" t="inlineStr">
+      <c r="D29" s="25" t="inlineStr">
         <is>
           <t>Before any purchase over €50, divide the price by your real hourly value. That's how many hours of your life it costs.</t>
         </is>
       </c>
     </row>
-    <row r="30">
+    <row r="30" ht="18" customHeight="1">
       <c r="B30" s="17" t="inlineStr">
         <is>
           <t>Workdays / month</t>
         </is>
       </c>
-      <c r="C30" s="48" t="n">
+      <c r="C30" s="49" t="n">
         <v>21</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="33" t="inlineStr">
+    <row r="31" ht="31" customHeight="1">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>Keep your first hour / month</t>
         </is>
       </c>
-      <c r="C31" s="34">
-        <f>C29*N(C30)</f>
+      <c r="C31" s="35">
+        <f>C29*(C30)</f>
         <v/>
       </c>
     </row>
@@ -4634,7 +4369,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G33"/>
+  <dimension ref="A1:G33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -4646,6 +4381,7 @@
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -4665,8 +4401,9 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>EMERGENCY FUND</t>
         </is>
@@ -4684,98 +4421,100 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="18" customHeight="1">
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Monthly needs (baseline)</t>
         </is>
       </c>
-      <c r="C7" s="43">
+      <c r="C7" s="44">
         <f>'T · Track'!E58</f>
         <v/>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>Keep it separate from your everyday account, easy to reach within a day or two, and boring. This money is insurance, not an investment.</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="18" customHeight="1">
       <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Months of safety you want</t>
         </is>
       </c>
-      <c r="C8" s="48" t="n">
+      <c r="C8" s="49" t="n">
         <v>3</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="45" t="inlineStr">
+    <row r="9" ht="18" customHeight="1">
+      <c r="B9" s="46" t="inlineStr">
         <is>
           <t>Starter buffer (1 month)</t>
         </is>
       </c>
-      <c r="C9" s="49">
+      <c r="C9" s="50">
         <f>C7</f>
         <v/>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="45" t="inlineStr">
+    <row r="10" ht="18" customHeight="1">
+      <c r="B10" s="46" t="inlineStr">
         <is>
           <t>Full emergency fund target</t>
         </is>
       </c>
-      <c r="C10" s="28">
-        <f>C7*N(C8)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10" s="29">
+        <f>C7*(C8)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1">
       <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Saved so far</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="27" t="n">
         <v>1200</v>
       </c>
     </row>
-    <row r="12">
-      <c r="B12" s="33" t="inlineStr">
+    <row r="12" ht="18" customHeight="1">
+      <c r="B12" s="34" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="C12" s="35">
-        <f>IF(C10&gt;0,MIN(1,N(C11)/C10),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
+      <c r="C12" s="36">
+        <f>IF(C10&gt;0,MIN(1,(C11)/C10),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
       <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Monthly transfer to it</t>
         </is>
       </c>
-      <c r="C13" s="26" t="n">
+      <c r="C13" s="27" t="n">
         <v>250</v>
       </c>
     </row>
-    <row r="14">
-      <c r="B14" s="45" t="inlineStr">
+    <row r="14" ht="18" customHeight="1">
+      <c r="B14" s="46" t="inlineStr">
         <is>
           <t>Months until full fund</t>
         </is>
       </c>
-      <c r="C14" s="39">
-        <f>IF(N(C11)&gt;=C10,"Done ✓",IF(N(C13)&gt;0,ROUNDUP((C10-N(C11))/C13,0),"Add a transfer"))</f>
-        <v/>
-      </c>
-    </row>
+      <c r="C14" s="40">
+        <f>IF((C11)&gt;=C10,"Done ✓",IF((C13)&gt;0,ROUNDUP((C10-(C11))/C13,0),"Add a transfer"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="26" t="inlineStr">
         <is>
           <t>GOAL POTS (sinking funds)</t>
         </is>
@@ -4814,210 +4553,211 @@
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="22" t="inlineStr">
+      <c r="B19" s="23" t="inlineStr">
         <is>
           <t>Care costs &amp; time off</t>
         </is>
       </c>
-      <c r="C19" s="26" t="n">
+      <c r="C19" s="27" t="n">
         <v>1500</v>
       </c>
-      <c r="D19" s="26" t="n">
+      <c r="D19" s="27" t="n">
         <v>300</v>
       </c>
-      <c r="E19" s="26" t="n">
+      <c r="E19" s="27" t="n">
         <v>75</v>
       </c>
-      <c r="F19" s="39">
-        <f>IF(N(C19)=0,"",IF(N(D19)&gt;=C19,"Done ✓",IF(N(E19)&gt;0,ROUNDUP((C19-N(D19))/E19,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G19" s="50">
-        <f>IF(N(C19)&gt;0,MIN(1,N(D19)/C19),0)</f>
+      <c r="F19" s="40">
+        <f>IF((C19)=0,"",IF((D19)&gt;=C19,"Done ✓",IF((E19)&gt;0,ROUNDUP((C19-(D19))/E19,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G19" s="51">
+        <f>IF((C19)&gt;0,MIN(1,(D19)/C19),0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="22" t="inlineStr">
+      <c r="B20" s="23" t="inlineStr">
         <is>
           <t>Christmas &amp; birthdays</t>
         </is>
       </c>
-      <c r="C20" s="26" t="n">
+      <c r="C20" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="D20" s="26" t="n">
+      <c r="D20" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="E20" s="26" t="n">
+      <c r="E20" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="39">
-        <f>IF(N(C20)=0,"",IF(N(D20)&gt;=C20,"Done ✓",IF(N(E20)&gt;0,ROUNDUP((C20-N(D20))/E20,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G20" s="50">
-        <f>IF(N(C20)&gt;0,MIN(1,N(D20)/C20),0)</f>
+      <c r="F20" s="40">
+        <f>IF((C20)=0,"",IF((D20)&gt;=C20,"Done ✓",IF((E20)&gt;0,ROUNDUP((C20-(D20))/E20,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G20" s="51">
+        <f>IF((C20)&gt;0,MIN(1,(D20)/C20),0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="22" t="inlineStr">
+      <c r="B21" s="23" t="inlineStr">
         <is>
           <t>Holiday with family</t>
         </is>
       </c>
-      <c r="C21" s="26" t="n">
+      <c r="C21" s="27" t="n">
         <v>1800</v>
       </c>
-      <c r="D21" s="26" t="n">
+      <c r="D21" s="27" t="n">
         <v>250</v>
       </c>
-      <c r="E21" s="26" t="n">
+      <c r="E21" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="F21" s="39">
-        <f>IF(N(C21)=0,"",IF(N(D21)&gt;=C21,"Done ✓",IF(N(E21)&gt;0,ROUNDUP((C21-N(D21))/E21,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G21" s="50">
-        <f>IF(N(C21)&gt;0,MIN(1,N(D21)/C21),0)</f>
+      <c r="F21" s="40">
+        <f>IF((C21)=0,"",IF((D21)&gt;=C21,"Done ✓",IF((E21)&gt;0,ROUNDUP((C21-(D21))/E21,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G21" s="51">
+        <f>IF((C21)&gt;0,MIN(1,(D21)/C21),0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="22" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="39">
-        <f>IF(N(C22)=0,"",IF(N(D22)&gt;=C22,"Done ✓",IF(N(E22)&gt;0,ROUNDUP((C22-N(D22))/E22,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G22" s="50">
-        <f>IF(N(C22)&gt;0,MIN(1,N(D22)/C22),0)</f>
+      <c r="B22" s="23" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="40">
+        <f>IF((C22)=0,"",IF((D22)&gt;=C22,"Done ✓",IF((E22)&gt;0,ROUNDUP((C22-(D22))/E22,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G22" s="51">
+        <f>IF((C22)&gt;0,MIN(1,(D22)/C22),0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="22" t="n"/>
-      <c r="C23" s="26" t="n"/>
-      <c r="D23" s="26" t="n"/>
-      <c r="E23" s="26" t="n"/>
-      <c r="F23" s="39">
-        <f>IF(N(C23)=0,"",IF(N(D23)&gt;=C23,"Done ✓",IF(N(E23)&gt;0,ROUNDUP((C23-N(D23))/E23,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G23" s="50">
-        <f>IF(N(C23)&gt;0,MIN(1,N(D23)/C23),0)</f>
+      <c r="B23" s="23" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+      <c r="E23" s="27" t="n"/>
+      <c r="F23" s="40">
+        <f>IF((C23)=0,"",IF((D23)&gt;=C23,"Done ✓",IF((E23)&gt;0,ROUNDUP((C23-(D23))/E23,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G23" s="51">
+        <f>IF((C23)&gt;0,MIN(1,(D23)/C23),0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="22" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="39">
-        <f>IF(N(C24)=0,"",IF(N(D24)&gt;=C24,"Done ✓",IF(N(E24)&gt;0,ROUNDUP((C24-N(D24))/E24,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G24" s="50">
-        <f>IF(N(C24)&gt;0,MIN(1,N(D24)/C24),0)</f>
+      <c r="B24" s="23" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="40">
+        <f>IF((C24)=0,"",IF((D24)&gt;=C24,"Done ✓",IF((E24)&gt;0,ROUNDUP((C24-(D24))/E24,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G24" s="51">
+        <f>IF((C24)&gt;0,MIN(1,(D24)/C24),0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="26" t="n"/>
-      <c r="D25" s="26" t="n"/>
-      <c r="E25" s="26" t="n"/>
-      <c r="F25" s="39">
-        <f>IF(N(C25)=0,"",IF(N(D25)&gt;=C25,"Done ✓",IF(N(E25)&gt;0,ROUNDUP((C25-N(D25))/E25,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G25" s="50">
-        <f>IF(N(C25)&gt;0,MIN(1,N(D25)/C25),0)</f>
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="40">
+        <f>IF((C25)=0,"",IF((D25)&gt;=C25,"Done ✓",IF((E25)&gt;0,ROUNDUP((C25-(D25))/E25,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G25" s="51">
+        <f>IF((C25)&gt;0,MIN(1,(D25)/C25),0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="22" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="39">
-        <f>IF(N(C26)=0,"",IF(N(D26)&gt;=C26,"Done ✓",IF(N(E26)&gt;0,ROUNDUP((C26-N(D26))/E26,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G26" s="50">
-        <f>IF(N(C26)&gt;0,MIN(1,N(D26)/C26),0)</f>
+      <c r="B26" s="23" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="40">
+        <f>IF((C26)=0,"",IF((D26)&gt;=C26,"Done ✓",IF((E26)&gt;0,ROUNDUP((C26-(D26))/E26,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G26" s="51">
+        <f>IF((C26)&gt;0,MIN(1,(D26)/C26),0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="22" t="n"/>
-      <c r="C27" s="26" t="n"/>
-      <c r="D27" s="26" t="n"/>
-      <c r="E27" s="26" t="n"/>
-      <c r="F27" s="39">
-        <f>IF(N(C27)=0,"",IF(N(D27)&gt;=C27,"Done ✓",IF(N(E27)&gt;0,ROUNDUP((C27-N(D27))/E27,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G27" s="50">
-        <f>IF(N(C27)&gt;0,MIN(1,N(D27)/C27),0)</f>
+      <c r="B27" s="23" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
+      <c r="E27" s="27" t="n"/>
+      <c r="F27" s="40">
+        <f>IF((C27)=0,"",IF((D27)&gt;=C27,"Done ✓",IF((E27)&gt;0,ROUNDUP((C27-(D27))/E27,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G27" s="51">
+        <f>IF((C27)&gt;0,MIN(1,(D27)/C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="22" t="n"/>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="39">
-        <f>IF(N(C28)=0,"",IF(N(D28)&gt;=C28,"Done ✓",IF(N(E28)&gt;0,ROUNDUP((C28-N(D28))/E28,0),"–")))</f>
-        <v/>
-      </c>
-      <c r="G28" s="50">
-        <f>IF(N(C28)&gt;0,MIN(1,N(D28)/C28),0)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="45" t="inlineStr">
+      <c r="B28" s="23" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="40">
+        <f>IF((C28)=0,"",IF((D28)&gt;=C28,"Done ✓",IF((E28)&gt;0,ROUNDUP((C28-(D28))/E28,0),"–")))</f>
+        <v/>
+      </c>
+      <c r="G28" s="51">
+        <f>IF((C28)&gt;0,MIN(1,(D28)/C28),0)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30" ht="18" customHeight="1">
+      <c r="B30" s="46" t="inlineStr">
         <is>
           <t>Total monthly to goal pots</t>
         </is>
       </c>
-      <c r="E30" s="28">
+      <c r="E30" s="29">
         <f>SUM(E19:E28)</f>
         <v/>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="33" t="inlineStr">
+    <row r="31" ht="31" customHeight="1">
+      <c r="B31" s="34" t="inlineStr">
         <is>
           <t>Total monthly saving (fund + pots)</t>
         </is>
       </c>
-      <c r="E31" s="34">
-        <f>N(C13)+E30</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
+      <c r="E31" s="35">
+        <f>(C13)+E30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
       <c r="B32" s="16" t="inlineStr">
         <is>
           <t>Still unassigned from KEEP</t>
         </is>
       </c>
-      <c r="E32" s="28">
+      <c r="E32" s="29">
         <f>'T · Track'!E62-E31</f>
         <v/>
       </c>
     </row>
-    <row r="33">
-      <c r="B33" s="24" t="inlineStr">
+    <row r="33" ht="18" customHeight="1">
+      <c r="B33" s="25" t="inlineStr">
         <is>
           <t>If 'still unassigned' is negative, your plan spends more than you keep. Lower a transfer until it's zero or positive.</t>
         </is>
@@ -5041,18 +4781,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:G41"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="27" customWidth="1" min="3" max="3"/>
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -5072,8 +4813,9 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="26" t="inlineStr">
         <is>
           <t>BEFORE YOU INVEST · CHECK</t>
         </is>
@@ -5091,82 +4833,83 @@
         </is>
       </c>
     </row>
-    <row r="7">
+    <row r="7" ht="18" customHeight="1">
       <c r="B7" s="17" t="inlineStr">
         <is>
           <t>Full emergency fund in place?</t>
         </is>
       </c>
-      <c r="C7" s="51">
+      <c r="C7" s="52">
         <f>IF('S · Save'!C12&gt;=1,"Yes ✓","Not yet")</f>
         <v/>
       </c>
-      <c r="D7" s="24" t="inlineStr">
+      <c r="D7" s="25" t="inlineStr">
         <is>
           <t>If any answer is not 'Yes', fix that first. Learning counts as progress.</t>
         </is>
       </c>
     </row>
-    <row r="8">
+    <row r="8" ht="18" customHeight="1">
       <c r="B8" s="17" t="inlineStr">
         <is>
           <t>Consumer debt cleared?</t>
         </is>
       </c>
-      <c r="C8" s="51">
-        <f>IF(N('U · Understand'!C17)&lt;=0,"Yes ✓","Not yet")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8" s="52">
+        <f>IF(('U · Understand'!C17)&lt;=0,"Yes ✓","Not yet")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1">
       <c r="B9" s="17" t="inlineStr">
         <is>
           <t>Money not needed for 5+ years?</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="10">
+    <row r="10" ht="31" customHeight="1">
       <c r="B10" s="17" t="inlineStr">
         <is>
           <t>Can you explain it in two sentences?</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>Not sure</t>
         </is>
       </c>
     </row>
-    <row r="11">
+    <row r="11" ht="31" customHeight="1">
       <c r="B11" s="17" t="inlineStr">
         <is>
           <t>Provider is regulated (e.g. BaFin register)?</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
-    <row r="12">
+    <row r="12" ht="18" customHeight="1">
       <c r="B12" s="16" t="inlineStr">
         <is>
           <t>Ready to start?</t>
         </is>
       </c>
-      <c r="C12" s="52">
+      <c r="C12" s="53">
         <f>IF(AND(C7="Yes ✓",C8="Yes ✓",C9="Yes",C10="Yes",C11="Yes"),"Ready ✓","Not yet: finish the checks")</f>
         <v/>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
-      <c r="B14" s="25" t="inlineStr">
+      <c r="B14" s="26" t="inlineStr">
         <is>
           <t>WHAT TIME COULD DO · ILLUSTRATION ONLY</t>
         </is>
@@ -5184,107 +4927,109 @@
         </is>
       </c>
     </row>
-    <row r="16">
+    <row r="16" ht="18" customHeight="1">
       <c r="B16" s="17" t="inlineStr">
         <is>
           <t>Monthly amount</t>
         </is>
       </c>
-      <c r="C16" s="26" t="n">
+      <c r="C16" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>Change the yellow cells to see how time, amount and fees change the result. Fixed growth is a simplification: real returns go up and down, aren't guaranteed, and you can lose money. Taxes and inflation are not included.</t>
         </is>
       </c>
     </row>
-    <row r="17">
+    <row r="17" ht="18" customHeight="1">
       <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Starting amount</t>
         </is>
       </c>
-      <c r="C17" s="26" t="n">
+      <c r="C17" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" ht="18" customHeight="1">
       <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Years</t>
         </is>
       </c>
-      <c r="C18" s="48" t="n">
+      <c r="C18" s="49" t="n">
         <v>25</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" ht="18" customHeight="1">
       <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Hypothetical yearly growth</t>
         </is>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="38" t="n">
         <v>0.05</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" ht="18" customHeight="1">
       <c r="B20" s="17" t="inlineStr">
         <is>
           <t>Yearly costs (fees)</t>
         </is>
       </c>
-      <c r="C20" s="53" t="n">
+      <c r="C20" s="54" t="n">
         <v>0.005</v>
       </c>
     </row>
-    <row r="21">
-      <c r="B21" s="45" t="inlineStr">
+    <row r="21" ht="18" customHeight="1">
+      <c r="B21" s="46" t="inlineStr">
         <is>
           <t>You pay in</t>
         </is>
       </c>
-      <c r="C21" s="49">
-        <f>N(C17)+N(C16)*12*N(C18)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="B22" s="33" t="inlineStr">
+      <c r="C21" s="50">
+        <f>(C17)+(C16)*12*(C18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="B22" s="34" t="inlineStr">
         <is>
           <t>Value before fees</t>
         </is>
       </c>
-      <c r="C22" s="34">
-        <f>IF(N(C19)=0,C21,FV(N(C19)/12,N(C18)*12,-N(C16),-N(C17)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="33" t="inlineStr">
+      <c r="C22" s="35">
+        <f>IF((C19)=0,C21,FV((C19)/12,(C18)*12,-(C16),-(C17)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Value after fees</t>
         </is>
       </c>
-      <c r="C23" s="34">
-        <f>IF(N(C19)-N(C20)=0,C21,FV((N(C19)-N(C20))/12,N(C18)*12,-N(C16),-N(C17)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
+      <c r="C23" s="35">
+        <f>IF((C19)-(C20)=0,C21,FV(((C19)-(C20))/12,(C18)*12,-(C16),-(C17)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
       <c r="B24" s="19" t="inlineStr">
         <is>
           <t>What the fees cost you</t>
         </is>
       </c>
-      <c r="C24" s="41">
+      <c r="C24" s="42">
         <f>C22-C23</f>
         <v/>
       </c>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>WHAT YOU ALREADY INVEST</t>
         </is>
@@ -5323,129 +5068,131 @@
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="22" t="inlineStr">
+      <c r="B29" s="23" t="inlineStr">
         <is>
           <t>Workplace pension</t>
         </is>
       </c>
-      <c r="C29" s="22" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>Employer plan</t>
         </is>
       </c>
-      <c r="D29" s="26" t="n">
+      <c r="D29" s="27" t="n">
         <v>100</v>
       </c>
-      <c r="E29" s="26" t="n">
+      <c r="E29" s="27" t="n">
         <v>2400</v>
       </c>
-      <c r="F29" s="53" t="n">
+      <c r="F29" s="54" t="n">
         <v>0.006</v>
       </c>
-      <c r="G29" s="22" t="inlineStr">
+      <c r="G29" s="23" t="inlineStr">
         <is>
           <t>Employer adds €50 a month</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="22" t="inlineStr">
+      <c r="B30" s="23" t="inlineStr">
         <is>
           <t>Long-term plan</t>
         </is>
       </c>
-      <c r="C30" s="22" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>Monthly savings plan</t>
         </is>
       </c>
-      <c r="D30" s="26" t="n">
+      <c r="D30" s="27" t="n">
         <v>50</v>
       </c>
-      <c r="E30" s="26" t="n">
+      <c r="E30" s="27" t="n">
         <v>600</v>
       </c>
-      <c r="F30" s="53" t="n">
+      <c r="F30" s="54" t="n">
         <v>0.002</v>
       </c>
-      <c r="G30" s="22" t="inlineStr">
+      <c r="G30" s="23" t="inlineStr">
         <is>
           <t>Example rows: overwrite with yours</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="22" t="n"/>
-      <c r="C31" s="22" t="n"/>
-      <c r="D31" s="26" t="n"/>
-      <c r="E31" s="26" t="n"/>
-      <c r="F31" s="53" t="n"/>
-      <c r="G31" s="22" t="n"/>
+      <c r="B31" s="23" t="n"/>
+      <c r="C31" s="23" t="n"/>
+      <c r="D31" s="27" t="n"/>
+      <c r="E31" s="27" t="n"/>
+      <c r="F31" s="54" t="n"/>
+      <c r="G31" s="23" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="22" t="n"/>
-      <c r="C32" s="22" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="53" t="n"/>
-      <c r="G32" s="22" t="n"/>
+      <c r="B32" s="23" t="n"/>
+      <c r="C32" s="23" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="54" t="n"/>
+      <c r="G32" s="23" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="22" t="n"/>
-      <c r="C33" s="22" t="n"/>
-      <c r="D33" s="26" t="n"/>
-      <c r="E33" s="26" t="n"/>
-      <c r="F33" s="53" t="n"/>
-      <c r="G33" s="22" t="n"/>
+      <c r="B33" s="23" t="n"/>
+      <c r="C33" s="23" t="n"/>
+      <c r="D33" s="27" t="n"/>
+      <c r="E33" s="27" t="n"/>
+      <c r="F33" s="54" t="n"/>
+      <c r="G33" s="23" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="22" t="n"/>
-      <c r="C34" s="22" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="53" t="n"/>
-      <c r="G34" s="22" t="n"/>
+      <c r="B34" s="23" t="n"/>
+      <c r="C34" s="23" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="54" t="n"/>
+      <c r="G34" s="23" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="22" t="n"/>
-      <c r="C35" s="22" t="n"/>
-      <c r="D35" s="26" t="n"/>
-      <c r="E35" s="26" t="n"/>
-      <c r="F35" s="53" t="n"/>
-      <c r="G35" s="22" t="n"/>
+      <c r="B35" s="23" t="n"/>
+      <c r="C35" s="23" t="n"/>
+      <c r="D35" s="27" t="n"/>
+      <c r="E35" s="27" t="n"/>
+      <c r="F35" s="54" t="n"/>
+      <c r="G35" s="23" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="22" t="n"/>
-      <c r="C36" s="22" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="53" t="n"/>
-      <c r="G36" s="22" t="n"/>
-    </row>
-    <row r="38">
-      <c r="B38" s="33" t="inlineStr">
+      <c r="B36" s="23" t="n"/>
+      <c r="C36" s="23" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="54" t="n"/>
+      <c r="G36" s="23" t="n"/>
+    </row>
+    <row r="37"/>
+    <row r="38" ht="18" customHeight="1">
+      <c r="B38" s="34" t="inlineStr">
         <is>
           <t>Invested / month</t>
         </is>
       </c>
-      <c r="D38" s="34">
+      <c r="D38" s="35">
         <f>SUM(D29:D36)</f>
         <v/>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="33" t="inlineStr">
+    <row r="39" ht="18" customHeight="1">
+      <c r="B39" s="34" t="inlineStr">
         <is>
           <t>Invested so far</t>
         </is>
       </c>
-      <c r="E39" s="34">
+      <c r="E39" s="35">
         <f>SUM(E29:E36)</f>
         <v/>
       </c>
     </row>
-    <row r="41">
-      <c r="B41" s="24" t="inlineStr">
+    <row r="40"/>
+    <row r="41" ht="18" customHeight="1">
+      <c r="B41" s="25" t="inlineStr">
         <is>
           <t>Rule: automate a fixed amount on payday, review once a year, and never invest money you might need within 5 years.</t>
         </is>
@@ -5461,7 +5208,7 @@
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="C9:C11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$H$1:$H$3</formula1>
+      <formula1>"Yes,No,Not sure"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -5475,7 +5222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:I28"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -5484,11 +5231,12 @@
     <col width="11" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
     <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="40" customHeight="1">
       <c r="B2" s="12" t="inlineStr">
         <is>
@@ -5510,6 +5258,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="30" customHeight="1">
       <c r="B5" s="20" t="inlineStr">
         <is>
@@ -5553,327 +5302,329 @@
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="22" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Salary raise negotiated</t>
         </is>
       </c>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>Career (raise/promotion)</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>Earning</t>
         </is>
       </c>
-      <c r="E6" s="44" t="n">
+      <c r="E6" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="22" t="inlineStr">
+      <c r="F6" s="23" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="G6" s="26" t="n">
+      <c r="G6" s="27" t="n">
         <v>150</v>
       </c>
-      <c r="H6" s="54">
-        <f>IF(N(E6)&gt;0,N(G6)/(E6*52/12),IF(N(G6)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I6" s="22" t="inlineStr">
+      <c r="H6" s="55">
+        <f>IF((E6)&gt;0,(G6)/(E6*52/12),IF((G6)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I6" s="23" t="inlineStr">
         <is>
           <t>Prepare next review in March</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="22" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t>Cybersecurity starter guide</t>
         </is>
       </c>
-      <c r="C7" s="22" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>Digital product</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="E7" s="44" t="n">
+      <c r="E7" s="45" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="22" t="inlineStr">
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="G7" s="26" t="n">
+      <c r="G7" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="H7" s="54">
-        <f>IF(N(E7)&gt;0,N(G7)/(E7*52/12),IF(N(G7)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I7" s="22" t="inlineStr">
+      <c r="H7" s="55">
+        <f>IF((E7)&gt;0,(G7)/(E7*52/12),IF((G7)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I7" s="23" t="inlineStr">
         <is>
           <t>Post 3 reels pointing to it</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="22" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t>UGC for a skincare brand</t>
         </is>
       </c>
-      <c r="C8" s="22" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>UGC</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="E8" s="44" t="n">
+      <c r="E8" s="45" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="22" t="inlineStr"/>
-      <c r="G8" s="26" t="n">
+      <c r="F8" s="23" t="inlineStr"/>
+      <c r="G8" s="27" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="54">
-        <f>IF(N(E8)&gt;0,N(G8)/(E8*52/12),IF(N(G8)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I8" s="22" t="inlineStr">
+      <c r="H8" s="55">
+        <f>IF((E8)&gt;0,(G8)/(E8*52/12),IF((G8)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I8" s="23" t="inlineStr">
         <is>
           <t>Make 2 sample videos</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="22" t="n"/>
-      <c r="C9" s="22" t="n"/>
-      <c r="D9" s="22" t="n"/>
-      <c r="E9" s="44" t="n"/>
-      <c r="F9" s="22" t="n"/>
-      <c r="G9" s="26" t="n"/>
-      <c r="H9" s="54">
-        <f>IF(N(E9)&gt;0,N(G9)/(E9*52/12),IF(N(G9)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I9" s="22" t="n"/>
+      <c r="B9" s="23" t="n"/>
+      <c r="C9" s="23" t="n"/>
+      <c r="D9" s="23" t="n"/>
+      <c r="E9" s="45" t="n"/>
+      <c r="F9" s="23" t="n"/>
+      <c r="G9" s="27" t="n"/>
+      <c r="H9" s="55">
+        <f>IF((E9)&gt;0,(G9)/(E9*52/12),IF((G9)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I9" s="23" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="22" t="n"/>
-      <c r="C10" s="22" t="n"/>
-      <c r="D10" s="22" t="n"/>
-      <c r="E10" s="44" t="n"/>
-      <c r="F10" s="22" t="n"/>
-      <c r="G10" s="26" t="n"/>
-      <c r="H10" s="54">
-        <f>IF(N(E10)&gt;0,N(G10)/(E10*52/12),IF(N(G10)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I10" s="22" t="n"/>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="23" t="n"/>
+      <c r="E10" s="45" t="n"/>
+      <c r="F10" s="23" t="n"/>
+      <c r="G10" s="27" t="n"/>
+      <c r="H10" s="55">
+        <f>IF((E10)&gt;0,(G10)/(E10*52/12),IF((G10)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I10" s="23" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="22" t="n"/>
-      <c r="D11" s="22" t="n"/>
-      <c r="E11" s="44" t="n"/>
-      <c r="F11" s="22" t="n"/>
-      <c r="G11" s="26" t="n"/>
-      <c r="H11" s="54">
-        <f>IF(N(E11)&gt;0,N(G11)/(E11*52/12),IF(N(G11)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I11" s="22" t="n"/>
+      <c r="B11" s="23" t="n"/>
+      <c r="C11" s="23" t="n"/>
+      <c r="D11" s="23" t="n"/>
+      <c r="E11" s="45" t="n"/>
+      <c r="F11" s="23" t="n"/>
+      <c r="G11" s="27" t="n"/>
+      <c r="H11" s="55">
+        <f>IF((E11)&gt;0,(G11)/(E11*52/12),IF((G11)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I11" s="23" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="22" t="n"/>
-      <c r="C12" s="22" t="n"/>
-      <c r="D12" s="22" t="n"/>
-      <c r="E12" s="44" t="n"/>
-      <c r="F12" s="22" t="n"/>
-      <c r="G12" s="26" t="n"/>
-      <c r="H12" s="54">
-        <f>IF(N(E12)&gt;0,N(G12)/(E12*52/12),IF(N(G12)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I12" s="22" t="n"/>
+      <c r="B12" s="23" t="n"/>
+      <c r="C12" s="23" t="n"/>
+      <c r="D12" s="23" t="n"/>
+      <c r="E12" s="45" t="n"/>
+      <c r="F12" s="23" t="n"/>
+      <c r="G12" s="27" t="n"/>
+      <c r="H12" s="55">
+        <f>IF((E12)&gt;0,(G12)/(E12*52/12),IF((G12)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I12" s="23" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="22" t="n"/>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="22" t="n"/>
-      <c r="E13" s="44" t="n"/>
-      <c r="F13" s="22" t="n"/>
-      <c r="G13" s="26" t="n"/>
-      <c r="H13" s="54">
-        <f>IF(N(E13)&gt;0,N(G13)/(E13*52/12),IF(N(G13)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I13" s="22" t="n"/>
+      <c r="B13" s="23" t="n"/>
+      <c r="C13" s="23" t="n"/>
+      <c r="D13" s="23" t="n"/>
+      <c r="E13" s="45" t="n"/>
+      <c r="F13" s="23" t="n"/>
+      <c r="G13" s="27" t="n"/>
+      <c r="H13" s="55">
+        <f>IF((E13)&gt;0,(G13)/(E13*52/12),IF((G13)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I13" s="23" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="22" t="n"/>
-      <c r="C14" s="22" t="n"/>
-      <c r="D14" s="22" t="n"/>
-      <c r="E14" s="44" t="n"/>
-      <c r="F14" s="22" t="n"/>
-      <c r="G14" s="26" t="n"/>
-      <c r="H14" s="54">
-        <f>IF(N(E14)&gt;0,N(G14)/(E14*52/12),IF(N(G14)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I14" s="22" t="n"/>
+      <c r="B14" s="23" t="n"/>
+      <c r="C14" s="23" t="n"/>
+      <c r="D14" s="23" t="n"/>
+      <c r="E14" s="45" t="n"/>
+      <c r="F14" s="23" t="n"/>
+      <c r="G14" s="27" t="n"/>
+      <c r="H14" s="55">
+        <f>IF((E14)&gt;0,(G14)/(E14*52/12),IF((G14)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I14" s="23" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="22" t="n"/>
-      <c r="C15" s="22" t="n"/>
-      <c r="D15" s="22" t="n"/>
-      <c r="E15" s="44" t="n"/>
-      <c r="F15" s="22" t="n"/>
-      <c r="G15" s="26" t="n"/>
-      <c r="H15" s="54">
-        <f>IF(N(E15)&gt;0,N(G15)/(E15*52/12),IF(N(G15)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I15" s="22" t="n"/>
+      <c r="B15" s="23" t="n"/>
+      <c r="C15" s="23" t="n"/>
+      <c r="D15" s="23" t="n"/>
+      <c r="E15" s="45" t="n"/>
+      <c r="F15" s="23" t="n"/>
+      <c r="G15" s="27" t="n"/>
+      <c r="H15" s="55">
+        <f>IF((E15)&gt;0,(G15)/(E15*52/12),IF((G15)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I15" s="23" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="22" t="n"/>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="22" t="n"/>
-      <c r="E16" s="44" t="n"/>
-      <c r="F16" s="22" t="n"/>
-      <c r="G16" s="26" t="n"/>
-      <c r="H16" s="54">
-        <f>IF(N(E16)&gt;0,N(G16)/(E16*52/12),IF(N(G16)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I16" s="22" t="n"/>
+      <c r="B16" s="23" t="n"/>
+      <c r="C16" s="23" t="n"/>
+      <c r="D16" s="23" t="n"/>
+      <c r="E16" s="45" t="n"/>
+      <c r="F16" s="23" t="n"/>
+      <c r="G16" s="27" t="n"/>
+      <c r="H16" s="55">
+        <f>IF((E16)&gt;0,(G16)/(E16*52/12),IF((G16)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I16" s="23" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="22" t="n"/>
-      <c r="C17" s="22" t="n"/>
-      <c r="D17" s="22" t="n"/>
-      <c r="E17" s="44" t="n"/>
-      <c r="F17" s="22" t="n"/>
-      <c r="G17" s="26" t="n"/>
-      <c r="H17" s="54">
-        <f>IF(N(E17)&gt;0,N(G17)/(E17*52/12),IF(N(G17)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I17" s="22" t="n"/>
+      <c r="B17" s="23" t="n"/>
+      <c r="C17" s="23" t="n"/>
+      <c r="D17" s="23" t="n"/>
+      <c r="E17" s="45" t="n"/>
+      <c r="F17" s="23" t="n"/>
+      <c r="G17" s="27" t="n"/>
+      <c r="H17" s="55">
+        <f>IF((E17)&gt;0,(G17)/(E17*52/12),IF((G17)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I17" s="23" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="22" t="n"/>
-      <c r="C18" s="22" t="n"/>
-      <c r="D18" s="22" t="n"/>
-      <c r="E18" s="44" t="n"/>
-      <c r="F18" s="22" t="n"/>
-      <c r="G18" s="26" t="n"/>
-      <c r="H18" s="54">
-        <f>IF(N(E18)&gt;0,N(G18)/(E18*52/12),IF(N(G18)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I18" s="22" t="n"/>
+      <c r="B18" s="23" t="n"/>
+      <c r="C18" s="23" t="n"/>
+      <c r="D18" s="23" t="n"/>
+      <c r="E18" s="45" t="n"/>
+      <c r="F18" s="23" t="n"/>
+      <c r="G18" s="27" t="n"/>
+      <c r="H18" s="55">
+        <f>IF((E18)&gt;0,(G18)/(E18*52/12),IF((G18)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I18" s="23" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="22" t="n"/>
-      <c r="C19" s="22" t="n"/>
-      <c r="D19" s="22" t="n"/>
-      <c r="E19" s="44" t="n"/>
-      <c r="F19" s="22" t="n"/>
-      <c r="G19" s="26" t="n"/>
-      <c r="H19" s="54">
-        <f>IF(N(E19)&gt;0,N(G19)/(E19*52/12),IF(N(G19)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I19" s="22" t="n"/>
+      <c r="B19" s="23" t="n"/>
+      <c r="C19" s="23" t="n"/>
+      <c r="D19" s="23" t="n"/>
+      <c r="E19" s="45" t="n"/>
+      <c r="F19" s="23" t="n"/>
+      <c r="G19" s="27" t="n"/>
+      <c r="H19" s="55">
+        <f>IF((E19)&gt;0,(G19)/(E19*52/12),IF((G19)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I19" s="23" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="22" t="n"/>
-      <c r="C20" s="22" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="44" t="n"/>
-      <c r="F20" s="22" t="n"/>
-      <c r="G20" s="26" t="n"/>
-      <c r="H20" s="54">
-        <f>IF(N(E20)&gt;0,N(G20)/(E20*52/12),IF(N(G20)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I20" s="22" t="n"/>
+      <c r="B20" s="23" t="n"/>
+      <c r="C20" s="23" t="n"/>
+      <c r="D20" s="23" t="n"/>
+      <c r="E20" s="45" t="n"/>
+      <c r="F20" s="23" t="n"/>
+      <c r="G20" s="27" t="n"/>
+      <c r="H20" s="55">
+        <f>IF((E20)&gt;0,(G20)/(E20*52/12),IF((G20)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I20" s="23" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="22" t="n"/>
-      <c r="C21" s="22" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="44" t="n"/>
-      <c r="F21" s="22" t="n"/>
-      <c r="G21" s="26" t="n"/>
-      <c r="H21" s="54">
-        <f>IF(N(E21)&gt;0,N(G21)/(E21*52/12),IF(N(G21)&gt;0,"no time logged",""))</f>
-        <v/>
-      </c>
-      <c r="I21" s="22" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="33" t="inlineStr">
+      <c r="B21" s="23" t="n"/>
+      <c r="C21" s="23" t="n"/>
+      <c r="D21" s="23" t="n"/>
+      <c r="E21" s="45" t="n"/>
+      <c r="F21" s="23" t="n"/>
+      <c r="G21" s="27" t="n"/>
+      <c r="H21" s="55">
+        <f>IF((E21)&gt;0,(G21)/(E21*52/12),IF((G21)&gt;0,"no time logged",""))</f>
+        <v/>
+      </c>
+      <c r="I21" s="23" t="n"/>
+    </row>
+    <row r="22"/>
+    <row r="23" ht="18" customHeight="1">
+      <c r="B23" s="34" t="inlineStr">
         <is>
           <t>Total extra income / month</t>
         </is>
       </c>
-      <c r="G23" s="34">
+      <c r="G23" s="35">
         <f>SUMIF(C6:C21,"&lt;&gt;Career (raise/promotion)",G6:G21)</f>
         <v/>
       </c>
     </row>
-    <row r="24">
-      <c r="B24" s="45" t="inlineStr">
+    <row r="24" ht="31" customHeight="1">
+      <c r="B24" s="46" t="inlineStr">
         <is>
           <t>Career growth / month (in salary)</t>
         </is>
       </c>
-      <c r="G24" s="28">
+      <c r="G24" s="29">
         <f>SUMIF(C6:C21,"Career (raise/promotion)",G6:G21)</f>
         <v/>
       </c>
     </row>
-    <row r="25">
-      <c r="B25" s="45" t="inlineStr">
+    <row r="25" ht="18" customHeight="1">
+      <c r="B25" s="46" t="inlineStr">
         <is>
           <t>Hours / week on streams</t>
         </is>
       </c>
-      <c r="E25" s="55">
+      <c r="E25" s="56">
         <f>SUM(E6:E21)</f>
         <v/>
       </c>
     </row>
-    <row r="26">
+    <row r="26" ht="31" customHeight="1">
       <c r="B26" s="19" t="inlineStr">
         <is>
           <t>Share of your needs covered by extra income</t>
         </is>
       </c>
-      <c r="G26" s="56">
+      <c r="G26" s="57">
         <f>IF('T · Track'!E58&gt;0,G23/'T · Track'!E58,0)</f>
         <v/>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="24" t="inlineStr">
+    <row r="27"/>
+    <row r="28" ht="18" customHeight="1">
+      <c r="B28" s="25" t="inlineStr">
         <is>
           <t>A raise already shows up in your net salary on T · Track, so it is counted separately and not added to side income twice.</t>
         </is>
@@ -5887,10 +5638,10 @@
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="C6:C21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$D$1:$D$9</formula1>
+      <formula1>"Career (raise/promotion),Freelance / consulting,Digital product,UGC,YouTube / content,Brand deals,Affiliate,Investment income,Other"</formula1>
     </dataValidation>
     <dataValidation sqref="D6:D21" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
-      <formula1>=Lists!$E$1:$E$4</formula1>
+      <formula1>"Idea,Testing,Earning,Paused"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/icyber/TRUST-Tracker-Pro.xlsx
+++ b/icyber/TRUST-Tracker-Pro.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="167" formatCode="€#,##0.00;-€#,##0.00;&quot;–&quot;"/>
     <numFmt numFmtId="168" formatCode="0.0"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -202,6 +202,12 @@
       <sz val="8"/>
     </font>
     <font>
+      <name val="Arial"/>
+      <i val="1"/>
+      <color rgb="006E8180"/>
+      <sz val="8"/>
+    </font>
+    <font>
       <name val="Georgia"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
@@ -272,8 +278,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="84">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
@@ -386,7 +395,7 @@
     <xf numFmtId="168" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="6" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="167" fontId="21" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -808,13 +817,13 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009E1B5E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -822,16 +831,22 @@
     <col width="3" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="44" customHeight="1">
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Hey, I'm Liliane.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="41.4" customHeight="1">
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>You work hard for your money. But is it creating the life you're working so hard for?</t>
         </is>
@@ -839,28 +854,28 @@
     </row>
     <row r="4"/>
     <row r="5" ht="86.90000000000001" customHeight="1">
-      <c r="B5" s="3" t="inlineStr">
+      <c r="B5" s="4" t="inlineStr">
         <is>
           <t>I'm a full-time cybersecurity consultant at a Big Four firm, working in the financial sector. I work a demanding job, and alongside my 9–5 I support my mum, who receives care at home after her cerebral haemorrhage. Balancing both is demanding, so I know how little time is left at the end of the day. Everything here comes from my own experience: I paid off €30,000 of debt and I'm building wealth beside my career with the same system I share here. I don't teach this from the outside. I've experienced it myself.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="49" customHeight="1">
-      <c r="B6" s="4" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>You have a demanding career, bills to pay and people who depend on you. You earn a respectable income. Yet despite everything you do, you don't always feel as financially secure or independent as you thought you would.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="36.2" customHeight="1">
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="6" t="inlineStr">
         <is>
           <t>How do I build a financially secure future without missing out on the people and moments that matter most today?</t>
         </is>
       </c>
     </row>
     <row r="8" ht="109" customHeight="1">
-      <c r="B8" s="4" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>I know that feeling. I started as a flight attendant working toward becoming a pilot, until COVID changed those plans. I rebuilt my path in cybersecurity consulting. My income grew, but financial security didn't automatically follow. In my 20s I took on loans for my study fees, made wrong financial decisions and even fell for an online scam: I was heavily into trading without knowing much about it. My rule since then: only invest in what you understand. I paid off €30,000 of debt not by first earning more, but by understanding my finances and making deliberate changes. Now in my 30s, this is what I wish someone had told me in my 20s.</t>
         </is>
@@ -868,28 +883,28 @@
     </row>
     <row r="9"/>
     <row r="10" ht="19" customHeight="1">
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>WHY I REALLY BUILT THIS</t>
         </is>
       </c>
     </row>
     <row r="11" ht="94" customHeight="1">
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>My mum is 83. When she had her cerebral haemorrhage, I realised how valuable time really is, and how little of it I had left. For years I worked long hours and stayed late almost every single day, because I believed climbing the corporate ladder was what success meant. But true success is realising what truly matters in life, and then taking the steps, one by one, that lead you there. We only get this one life. I want to spend as much time with her as I possibly can. Not someday, but now.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="100.5" customHeight="1">
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Most of the financial advice out there told me to quit my job, hustle harder or get rich fast. That's unrealistic unless you're willing to risk your financial security, and when people depend on you, that's not a risk worth taking. None were made for someone with a demanding career and a mum who needs them. I wish I'd had a clear, honest plan for the few hours I actually had left, when I wasn't already exhausted from work and every other responsibility around me. So I decided to build it for myself, step by step. You shouldn't need a wake-up call to start. Begin before yours comes, or before it's too late.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="49" customHeight="1">
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>That's why I created TRUST Tracker Pro, the full version of my free TRUST Sheet, built to work hand in hand with The Wealth Roadmap. No judgment. No unrealistic promises. No complicated jargon. Just a practical system for making your money work toward the life you actually want.</t>
         </is>
@@ -897,49 +912,49 @@
     </row>
     <row r="14"/>
     <row r="15" ht="19" customHeight="1">
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>WHO THIS IS FOR</t>
         </is>
       </c>
     </row>
     <row r="16" ht="19" customHeight="1">
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>✓  Your financial progress doesn't reflect the effort you put into your career.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1">
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>✓  You balance work, family or caregiving, and need a system that fits your limited time.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="19" customHeight="1">
-      <c r="B18" s="4" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>✓  You earn a decent income and want clarity on what you keep, spend, save and owe.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="19" customHeight="1">
-      <c r="B19" s="4" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>✓  You want a strong foundation before building wealth or extra income streams.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="32.3" customHeight="1">
-      <c r="B20" s="4" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>✓  You want financial independence for a reason: more choices and more time with the people you love.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="9" t="inlineStr">
         <is>
           <t>Not for anyone looking for overnight wealth or guaranteed returns.</t>
         </is>
@@ -947,56 +962,56 @@
     </row>
     <row r="22"/>
     <row r="23" ht="19" customHeight="1">
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>THE METHOD · KEEP + TRUST</t>
         </is>
       </c>
     </row>
     <row r="24" ht="34" customHeight="1">
-      <c r="B24" s="3" t="inlineStr">
+      <c r="B24" s="4" t="inlineStr">
         <is>
           <t>KEEP = Know your Earnings to Escape your Paycheck. Your salary can be the foundation of your financial future. It doesn't have to define your limits.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="19" customHeight="1">
-      <c r="B25" s="4" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>T · Track: know your numbers. What comes in, what goes out, what you actually keep.</t>
         </is>
       </c>
     </row>
     <row r="26" ht="19" customHeight="1">
-      <c r="B26" s="4" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>R · Reclaim: find where money slips away and redirect it toward what matters to you.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="19" customHeight="1">
-      <c r="B27" s="4" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>U · Understand: see your position clearly, including debt and the real value of your hour.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="19" customHeight="1">
-      <c r="B28" s="4" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>S · Save: build resilience, set priorities and prepare for your future.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="19" customHeight="1">
-      <c r="B29" s="4" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>T · Time: see how money and time connect, and why independence is really about choices.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="34" customHeight="1">
-      <c r="B30" s="8" t="inlineStr">
+      <c r="B30" s="9" t="inlineStr">
         <is>
           <t>Knowing your numbers is the beginning, not the goal. TRUST is the foundation for debt freedom, wealth building and additional income.</t>
         </is>
@@ -1004,14 +1019,14 @@
     </row>
     <row r="31"/>
     <row r="32" ht="19" customHeight="1">
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="7" t="inlineStr">
         <is>
           <t>HOW IT FOLLOWS THE ROADMAP</t>
         </is>
       </c>
     </row>
     <row r="33" ht="34" customHeight="1">
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>The Wealth Roadmap has 7 stages. Each stage uses one or two tabs in this tracker. The 7 Stages tab shows which tab belongs to which stage, and lets you tick off each stage when it is done.</t>
         </is>
@@ -1019,49 +1034,49 @@
     </row>
     <row r="34"/>
     <row r="35" ht="19" customHeight="1">
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="7" t="inlineStr">
         <is>
           <t>WEALTH STARTS WITH YOUR MINDSET</t>
         </is>
       </c>
     </row>
     <row r="36" ht="34" customHeight="1">
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Becoming wealthy starts with how you think about money and with understanding the laws of money. Money management is a skill you learn, not a talent you're born with.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="19" customHeight="1">
-      <c r="B37" s="4" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>1 · Spend less than you earn. The gap is where all wealth begins.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="19" customHeight="1">
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>2 · Pay yourself first. Your future gets paid on payday, before bills and wants.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="19" customHeight="1">
-      <c r="B39" s="4" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>3 · Protect what you have. A safety net and no expensive debt.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="19" customHeight="1">
-      <c r="B40" s="4" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>4 · Make your money work for you. Only invest in what you understand.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="19" customHeight="1">
-      <c r="B41" s="4" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>5 · Give it time. Compound growth rewards patience more than luck.</t>
         </is>
@@ -1069,14 +1084,14 @@
     </row>
     <row r="42"/>
     <row r="43" ht="19" customHeight="1">
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="7" t="inlineStr">
         <is>
           <t>YOUR NEXT STEP</t>
         </is>
       </c>
     </row>
     <row r="44" ht="46" customHeight="1">
-      <c r="B44" s="4" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Head to the How to Use tab, then the 7 Stages tab. In about 20 minutes you'll have your first financial snapshot. You don't need everything figured out today. You just need somewhere meaningful to start.</t>
         </is>
@@ -1084,14 +1099,14 @@
     </row>
     <row r="45"/>
     <row r="46" ht="64" customHeight="1">
-      <c r="B46" s="9" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>Financial freedom isn't about quitting your 9–5. It's about using your career as the engine to fuel your financial independence, build multiple income streams, and create the freedom to spend more time with the people you love.</t>
         </is>
       </c>
     </row>
     <row r="47" ht="46" customHeight="1">
-      <c r="B47" s="10" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
         <is>
           <t>Build your options without quitting your 9–5.  Know your money. Build your wealth. Reclaim your time.
 — Liliane · iCyber · @cyber_cnslt · cybercnslt.com</t>
@@ -1100,19 +1115,50 @@
     </row>
     <row r="48"/>
     <row r="49" ht="38.1" customHeight="1">
-      <c r="B49" s="11" t="inlineStr">
+      <c r="B49" s="12" t="inlineStr">
         <is>
           <t>Educational information only, not individualised financial or investment advice. TRUST Tracker Pro helps you organise and understand your finances; it doesn't guarantee financial outcomes. Your financial information stays in your own copy of the workbook unless you choose to share it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50"/>
+    <row r="51" ht="19" customHeight="1">
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>COPYRIGHT &amp; HOW THIS WAS MADE</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="49" customHeight="1">
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber. All rights reserved. TRUST Tracker Pro and The Wealth Roadmap are licensed for the personal use of the purchaser only. Copying, sharing, reselling, redistributing or publishing them, in full or in part, is not permitted without written permission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="49" customHeight="1">
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>All ideas, the 7-stage structure, the KEEP and TRUST methods, the frameworks and the stories are my own original work. Some text and design elements were created with the help of AI tools, then reviewed, edited and approved by me.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001A9E9E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1128,19 +1174,25 @@
     <col width="40" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>T · Time</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Roadmap stage 7 · A week has 168 hours. Map a realistic one, including care and recovery. Then decide which hours you'll protect for the people you love, and how many (if any) go to building options.</t>
         </is>
@@ -1148,256 +1200,256 @@
     </row>
     <row r="4"/>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Area</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Hours / week now</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Hours / week goal</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>What would change it?</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Sleep</t>
         </is>
       </c>
-      <c r="C6" s="45" t="n">
+      <c r="C6" s="46" t="n">
         <v>49</v>
       </c>
-      <c r="D6" s="45" t="n">
+      <c r="D6" s="46" t="n">
         <v>52</v>
       </c>
-      <c r="E6" s="23" t="inlineStr">
+      <c r="E6" s="24" t="inlineStr">
         <is>
           <t>Phone out of the bedroom</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Paid work (incl. overtime)</t>
         </is>
       </c>
-      <c r="C7" s="45" t="n">
+      <c r="C7" s="46" t="n">
         <v>43</v>
       </c>
-      <c r="D7" s="45" t="n">
+      <c r="D7" s="46" t="n">
         <v>40</v>
       </c>
-      <c r="E7" s="23" t="inlineStr">
+      <c r="E7" s="24" t="inlineStr">
         <is>
           <t>Stop answering email after 7pm</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Commute</t>
         </is>
       </c>
-      <c r="C8" s="45" t="n">
+      <c r="C8" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="D8" s="45" t="n">
+      <c r="D8" s="46" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="23" t="inlineStr"/>
+      <c r="E8" s="24" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Caregiving</t>
         </is>
       </c>
-      <c r="C9" s="45" t="n">
+      <c r="C9" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="D9" s="45" t="n">
+      <c r="D9" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="E9" s="23" t="inlineStr">
+      <c r="E9" s="24" t="inlineStr">
         <is>
           <t>Ask sibling for one fixed day</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Household &amp; admin</t>
         </is>
       </c>
-      <c r="C10" s="45" t="n">
+      <c r="C10" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="D10" s="45" t="n">
+      <c r="D10" s="46" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="23" t="inlineStr">
+      <c r="E10" s="24" t="inlineStr">
         <is>
           <t>One big shop per week</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Family &amp; friends time</t>
         </is>
       </c>
-      <c r="C11" s="45" t="n">
+      <c r="C11" s="46" t="n">
         <v>12</v>
       </c>
-      <c r="D11" s="45" t="n">
+      <c r="D11" s="46" t="n">
         <v>16</v>
       </c>
-      <c r="E11" s="23" t="inlineStr">
+      <c r="E11" s="24" t="inlineStr">
         <is>
           <t>Protected Sunday afternoon</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Health &amp; movement</t>
         </is>
       </c>
-      <c r="C12" s="45" t="n">
+      <c r="C12" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="45" t="n">
+      <c r="D12" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="E12" s="23" t="inlineStr">
+      <c r="E12" s="24" t="inlineStr">
         <is>
           <t>Walk at lunch</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Building options (learning / side income)</t>
         </is>
       </c>
-      <c r="C13" s="45" t="n">
+      <c r="C13" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="D13" s="45" t="n">
+      <c r="D13" s="46" t="n">
         <v>4</v>
       </c>
-      <c r="E13" s="23" t="inlineStr">
+      <c r="E13" s="24" t="inlineStr">
         <is>
           <t>Two 2-hour blocks, Tue &amp; Sat</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Rest &amp; yourself</t>
         </is>
       </c>
-      <c r="C14" s="45" t="n">
+      <c r="C14" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="D14" s="45" t="n">
+      <c r="D14" s="46" t="n">
         <v>10</v>
       </c>
-      <c r="E14" s="23" t="inlineStr"/>
+      <c r="E14" s="24" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="45" t="n"/>
-      <c r="D15" s="45" t="n"/>
-      <c r="E15" s="23" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="46" t="n"/>
+      <c r="D15" s="46" t="n"/>
+      <c r="E15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="45" t="n"/>
-      <c r="D16" s="45" t="n"/>
-      <c r="E16" s="23" t="n"/>
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="46" t="n"/>
+      <c r="D16" s="46" t="n"/>
+      <c r="E16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="45" t="n"/>
-      <c r="D17" s="45" t="n"/>
-      <c r="E17" s="23" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="46" t="n"/>
+      <c r="D17" s="46" t="n"/>
+      <c r="E17" s="24" t="n"/>
     </row>
     <row r="18"/>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="46" t="inlineStr">
+      <c r="B19" s="47" t="inlineStr">
         <is>
           <t>Hours planned</t>
         </is>
       </c>
-      <c r="C19" s="58">
+      <c r="C19" s="59">
         <f>SUM(C6:C17)</f>
         <v/>
       </c>
-      <c r="D19" s="58">
+      <c r="D19" s="59">
         <f>SUM(D6:D17)</f>
         <v/>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="34" t="inlineStr">
+      <c r="B20" s="35" t="inlineStr">
         <is>
           <t>Unplanned hours (of 168)</t>
         </is>
       </c>
-      <c r="C20" s="59">
+      <c r="C20" s="60">
         <f>168-C19</f>
         <v/>
       </c>
-      <c r="D20" s="59">
+      <c r="D20" s="60">
         <f>168-D19</f>
         <v/>
       </c>
     </row>
     <row r="21"/>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="19" t="inlineStr">
+      <c r="B22" s="20" t="inlineStr">
         <is>
           <t>Family time gained / week</t>
         </is>
       </c>
-      <c r="C22" s="60">
+      <c r="C22" s="61">
         <f>SUMIF(B6:B17,"Family*",D6:D17)-SUMIF(B6:B17,"Family*",C6:C17)</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="19" t="inlineStr">
+      <c r="B23" s="20" t="inlineStr">
         <is>
           <t>Family time gained / year</t>
         </is>
       </c>
-      <c r="C23" s="61">
+      <c r="C23" s="62">
         <f>C22*52</f>
         <v/>
       </c>
     </row>
     <row r="24"/>
     <row r="25" ht="24" customHeight="1">
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Negative unplanned hours mean the week doesn't fit. Something has to go before anything new comes in. Never take side-project hours out of sleep or family first.</t>
         </is>
@@ -1406,28 +1458,28 @@
     <row r="26"/>
     <row r="27"/>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="46" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
         <is>
           <t>Your hourly value at work</t>
         </is>
       </c>
-      <c r="C28" s="62">
+      <c r="C28" s="63">
         <f>'U · Understand'!C29</f>
         <v/>
       </c>
-      <c r="D28" s="25" t="inlineStr">
+      <c r="D28" s="26" t="inlineStr">
         <is>
           <t>This is roughly what extra income or savings would need to replace if you reduced your paid hours to your goal. A concrete target for the Income Streams tab.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="31" customHeight="1">
-      <c r="B29" s="46" t="inlineStr">
+      <c r="B29" s="47" t="inlineStr">
         <is>
           <t>Value of the work hours you want back / year</t>
         </is>
       </c>
-      <c r="C29" s="29">
+      <c r="C29" s="30">
         <f>MAX(0,SUMIF(B6:B17,"Paid work*",C6:C17)-SUMIF(B6:B17,"Paid work*",D6:D17))*52*C28</f>
         <v/>
       </c>
@@ -1441,11 +1493,20 @@
     <mergeCell ref="D28:E30"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009E1B5E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1463,20 +1524,26 @@
     <col width="18" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="63" t="inlineStr">
+      <c r="B2" s="64" t="inlineStr">
         <is>
           <t>KEEP — Know your Earnings to Escape your Paycheck</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Your month on one page. Nothing to fill in here: it reads every other tab.</t>
         </is>
@@ -1484,363 +1551,363 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>YOUR FREEDOM LEVEL</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1">
-      <c r="B6" s="64">
+      <c r="B6" s="65">
         <f>CHOOSE(C9+1,"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose")</f>
         <v/>
       </c>
-      <c r="E6" s="65">
+      <c r="E6" s="66">
         <f>CHOOSE(C9+1,"Next step: more goes out than comes in. Use R · Reclaim and cut wants until KEEP is at least €0.","Next step: build a starter buffer of one month of needs before anything else.","Next step: clear consumer debt, highest interest first (Priority 1 on U · Understand).","Next step: grow the buffer into your full emergency fund on S · Save.","Next step: you are secure. Stage 5: learn investing basics on the Invest tab, then start ONE income stream.","Next step: extra income covers 25%+ of needs. Keep investing; decide what time you want back.","You have choices. Extra income covers your baseline. Decide on your terms how much you want to work.")</f>
         <v/>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1">
-      <c r="C7" s="13" t="n"/>
+      <c r="C7" s="14" t="n"/>
     </row>
     <row r="8"/>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Level number</t>
         </is>
       </c>
-      <c r="C9" s="66">
+      <c r="C9" s="67">
         <f>IF(C14&lt;0,0,IF(C22&lt;C13,1,IF(C20&gt;0,2,IF(C22&lt;C23,3,IF(C25&lt;0.25*C13,4,IF(C25&lt;C13,5,6))))))</f>
         <v/>
       </c>
     </row>
     <row r="10"/>
     <row r="11">
-      <c r="B11" s="26" t="inlineStr">
+      <c r="B11" s="27" t="inlineStr">
         <is>
           <t>MONEY</t>
         </is>
       </c>
-      <c r="E11" s="26" t="inlineStr">
+      <c r="E11" s="27" t="inlineStr">
         <is>
           <t>TIME &amp; OPTIONS</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="18" t="inlineStr">
         <is>
           <t>Money in / month</t>
         </is>
       </c>
-      <c r="C12" s="67">
+      <c r="C12" s="68">
         <f>'T · Track'!E13</f>
         <v/>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>1 hour of your life is worth</t>
         </is>
       </c>
-      <c r="F12" s="68">
+      <c r="F12" s="69">
         <f>'U · Understand'!C29</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Needs (baseline)</t>
         </is>
       </c>
-      <c r="C13" s="69">
+      <c r="C13" s="70">
         <f>'T · Track'!E58</f>
         <v/>
       </c>
-      <c r="E13" s="17" t="inlineStr">
+      <c r="E13" s="18" t="inlineStr">
         <is>
           <t>Keep your first hour / month</t>
         </is>
       </c>
-      <c r="F13" s="70">
+      <c r="F13" s="71">
         <f>'U · Understand'!C31</f>
         <v/>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr">
         <is>
           <t>What you KEEP / month</t>
         </is>
       </c>
-      <c r="C14" s="70">
+      <c r="C14" s="71">
         <f>'T · Track'!E62</f>
         <v/>
       </c>
-      <c r="E14" s="17" t="inlineStr">
+      <c r="E14" s="18" t="inlineStr">
         <is>
           <t>Hours / week on income streams</t>
         </is>
       </c>
-      <c r="F14" s="71">
+      <c r="F14" s="72">
         <f>'Income Streams'!E25</f>
         <v/>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr">
         <is>
           <t>Keep rate</t>
         </is>
       </c>
-      <c r="C15" s="72">
+      <c r="C15" s="73">
         <f>'T · Track'!E63</f>
         <v/>
       </c>
-      <c r="E15" s="17" t="inlineStr">
+      <c r="E15" s="18" t="inlineStr">
         <is>
           <t>Needs covered by extra income</t>
         </is>
       </c>
-      <c r="F15" s="73">
+      <c r="F15" s="74">
         <f>'Income Streams'!G26</f>
         <v/>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Wants</t>
         </is>
       </c>
-      <c r="C16" s="74">
+      <c r="C16" s="75">
         <f>'T · Track'!E59</f>
         <v/>
       </c>
-      <c r="E16" s="17" t="inlineStr">
+      <c r="E16" s="18" t="inlineStr">
         <is>
           <t>Family time gained / week (goal)</t>
         </is>
       </c>
-      <c r="F16" s="75">
+      <c r="F16" s="76">
         <f>'T · Time'!C22</f>
         <v/>
       </c>
     </row>
     <row r="17" ht="31" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Reclaimable / month</t>
         </is>
       </c>
-      <c r="C17" s="70">
+      <c r="C17" s="71">
         <f>'R · Reclaim'!F32</f>
         <v/>
       </c>
-      <c r="E17" s="17" t="inlineStr">
+      <c r="E17" s="18" t="inlineStr">
         <is>
           <t>Unassigned KEEP after savings plan</t>
         </is>
       </c>
-      <c r="F17" s="67">
+      <c r="F17" s="68">
         <f>'S · Save'!E32</f>
         <v/>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Reclaimable / year</t>
         </is>
       </c>
-      <c r="C18" s="70">
+      <c r="C18" s="71">
         <f>'R · Reclaim'!F33</f>
         <v/>
       </c>
-      <c r="E18" s="17" t="inlineStr">
+      <c r="E18" s="18" t="inlineStr">
         <is>
           <t>Career growth / month</t>
         </is>
       </c>
-      <c r="F18" s="70">
+      <c r="F18" s="71">
         <f>'Income Streams'!G24</f>
         <v/>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="26" t="inlineStr">
+      <c r="B19" s="27" t="inlineStr">
         <is>
           <t>SAFETY</t>
         </is>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Debt to clear</t>
         </is>
       </c>
-      <c r="C20" s="74">
+      <c r="C20" s="75">
         <f>'U · Understand'!C17</f>
         <v/>
       </c>
-      <c r="E20" s="76" t="inlineStr">
+      <c r="E20" s="77" t="inlineStr">
         <is>
           <t>THE FREEDOM LADDER</t>
         </is>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="17" t="inlineStr">
+      <c r="B21" s="18" t="inlineStr">
         <is>
           <t>Interest you pay / year</t>
         </is>
       </c>
-      <c r="C21" s="74">
+      <c r="C21" s="75">
         <f>'U · Understand'!C19</f>
         <v/>
       </c>
-      <c r="E21" s="77" t="inlineStr">
+      <c r="E21" s="78" t="inlineStr">
         <is>
           <t>0 · Overwhelmed: more out than in</t>
         </is>
       </c>
-      <c r="G21" s="78">
+      <c r="G21" s="79">
         <f>IF($C$9=0,"◀ you are here","")</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="17" t="inlineStr">
+      <c r="B22" s="18" t="inlineStr">
         <is>
           <t>Emergency fund saved</t>
         </is>
       </c>
-      <c r="C22" s="70">
+      <c r="C22" s="71">
         <f>'S · Save'!C11</f>
         <v/>
       </c>
-      <c r="E22" s="77" t="inlineStr">
+      <c r="E22" s="78" t="inlineStr">
         <is>
           <t>1 · Stable: KEEP is €0 or more</t>
         </is>
       </c>
-      <c r="G22" s="78">
+      <c r="G22" s="79">
         <f>IF($C$9=1,"◀ you are here","")</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="17" t="inlineStr">
+      <c r="B23" s="18" t="inlineStr">
         <is>
           <t>Emergency fund target</t>
         </is>
       </c>
-      <c r="C23" s="69">
+      <c r="C23" s="70">
         <f>'S · Save'!C10</f>
         <v/>
       </c>
-      <c r="E23" s="77" t="inlineStr">
+      <c r="E23" s="78" t="inlineStr">
         <is>
           <t>2 · Buffered: 1 month of needs saved</t>
         </is>
       </c>
-      <c r="G23" s="78">
+      <c r="G23" s="79">
         <f>IF($C$9=2,"◀ you are here","")</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Fund progress</t>
         </is>
       </c>
-      <c r="C24" s="72">
+      <c r="C24" s="73">
         <f>'S · Save'!C12</f>
         <v/>
       </c>
-      <c r="E24" s="77" t="inlineStr">
+      <c r="E24" s="78" t="inlineStr">
         <is>
           <t>3 · Debt-free: consumer debt cleared</t>
         </is>
       </c>
-      <c r="G24" s="78">
+      <c r="G24" s="79">
         <f>IF($C$9=3,"◀ you are here","")</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Extra income / month</t>
         </is>
       </c>
-      <c r="C25" s="70">
+      <c r="C25" s="71">
         <f>'Income Streams'!G23</f>
         <v/>
       </c>
-      <c r="E25" s="77" t="inlineStr">
+      <c r="E25" s="78" t="inlineStr">
         <is>
           <t>4 · Secure: full emergency fund</t>
         </is>
       </c>
-      <c r="G25" s="78">
+      <c r="G25" s="79">
         <f>IF($C$9=4,"◀ you are here","")</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Invested / month</t>
         </is>
       </c>
-      <c r="C26" s="70">
+      <c r="C26" s="71">
         <f>Invest!D38</f>
         <v/>
       </c>
-      <c r="E26" s="77" t="inlineStr">
+      <c r="E26" s="78" t="inlineStr">
         <is>
           <t>5 · Flexible: extra income ≥ 25% of needs</t>
         </is>
       </c>
-      <c r="G26" s="78">
+      <c r="G26" s="79">
         <f>IF($C$9=5,"◀ you are here","")</f>
         <v/>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Roadmap stages done</t>
         </is>
       </c>
-      <c r="C27" s="79">
+      <c r="C27" s="80">
         <f>'7 Stages'!D14</f>
         <v/>
       </c>
-      <c r="E27" s="77" t="inlineStr">
+      <c r="E27" s="78" t="inlineStr">
         <is>
           <t>6 · Free to choose: extra income ≥ needs</t>
         </is>
       </c>
-      <c r="G27" s="78">
+      <c r="G27" s="79">
         <f>IF($C$9=6,"◀ you are here","")</f>
         <v/>
       </c>
     </row>
     <row r="28"/>
     <row r="29">
-      <c r="B29" s="80" t="inlineStr">
+      <c r="B29" s="81" t="inlineStr">
         <is>
           <t>Your career is the engine. Keep your first hour, and keep going. — Liliane</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="81" t="inlineStr">
+      <c r="B30" s="82" t="inlineStr">
         <is>
           <t>Educational tool. Not financial advice.</t>
         </is>
@@ -1861,11 +1928,20 @@
     <mergeCell ref="E21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F6E6E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1888,26 +1964,32 @@
     <col width="34" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Monthly Review</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="13" t="n"/>
-      <c r="H2" s="13" t="n"/>
-      <c r="I2" s="13" t="n"/>
-      <c r="J2" s="13" t="n"/>
-      <c r="K2" s="13" t="n"/>
-      <c r="L2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
+      <c r="J2" s="14" t="n"/>
+      <c r="K2" s="14" t="n"/>
+      <c r="L2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Once a month, 15 minutes: copy the numbers from KEEP into a new row. The level calculates itself. Write one win, however small.</t>
         </is>
@@ -1915,365 +1997,365 @@
     </row>
     <row r="4"/>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Money in</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Needs</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Wants</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>KEEP</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Keep rate</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>Emergency fund</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="J5" s="20" t="inlineStr">
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t>Extra income</t>
         </is>
       </c>
-      <c r="K5" s="20" t="inlineStr">
+      <c r="K5" s="21" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="L5" s="21" t="inlineStr">
         <is>
           <t>One win this month</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Sep 2026</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>2500</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="28" t="n">
         <v>1650</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="28" t="n">
         <v>330</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="38">
         <f>IF(C6="","",C6-(D6)-(E6))</f>
         <v/>
       </c>
-      <c r="G6" s="51">
+      <c r="G6" s="52">
         <f>IF((C6)&gt;0,F6/C6,"")</f>
         <v/>
       </c>
-      <c r="H6" s="27" t="n">
+      <c r="H6" s="28" t="n">
         <v>1000</v>
       </c>
-      <c r="I6" s="27" t="n">
+      <c r="I6" s="28" t="n">
         <v>1500</v>
       </c>
-      <c r="J6" s="27" t="n">
+      <c r="J6" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="K6" s="82">
+      <c r="K6" s="83">
         <f>IF(C6="","",CHOOSE(1+IF(F6&lt;0,0,IF((H6)&lt;(D6),1,IF((I6)&gt;0,2,IF((H6)&lt;(D6)*'S · Save'!$C$8,3,IF((J6)&lt;0.25*(D6),4,IF((J6)&lt;(D6),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L6" s="23" t="inlineStr">
+      <c r="L6" s="24" t="inlineStr">
         <is>
           <t>Cancelled 2 subscriptions</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Oct 2026</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>2560</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="28" t="n">
         <v>1640</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="28" t="n">
         <v>265</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="38">
         <f>IF(C7="","",C7-(D7)-(E7))</f>
         <v/>
       </c>
-      <c r="G7" s="51">
+      <c r="G7" s="52">
         <f>IF((C7)&gt;0,F7/C7,"")</f>
         <v/>
       </c>
-      <c r="H7" s="27" t="n">
+      <c r="H7" s="28" t="n">
         <v>1200</v>
       </c>
-      <c r="I7" s="27" t="n">
+      <c r="I7" s="28" t="n">
         <v>1400</v>
       </c>
-      <c r="J7" s="27" t="n">
+      <c r="J7" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="K7" s="82">
+      <c r="K7" s="83">
         <f>IF(C7="","",CHOOSE(1+IF(F7&lt;0,0,IF((H7)&lt;(D7),1,IF((I7)&gt;0,2,IF((H7)&lt;(D7)*'S · Save'!$C$8,3,IF((J7)&lt;0.25*(D7),4,IF((J7)&lt;(D7),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L7" s="23" t="inlineStr">
+      <c r="L7" s="24" t="inlineStr">
         <is>
           <t>First €60 from my guide</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="27" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="37">
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="28" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="38">
         <f>IF(C8="","",C8-(D8)-(E8))</f>
         <v/>
       </c>
-      <c r="G8" s="51">
+      <c r="G8" s="52">
         <f>IF((C8)&gt;0,F8/C8,"")</f>
         <v/>
       </c>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="27" t="n"/>
-      <c r="J8" s="27" t="n"/>
-      <c r="K8" s="82">
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="28" t="n"/>
+      <c r="J8" s="28" t="n"/>
+      <c r="K8" s="83">
         <f>IF(C8="","",CHOOSE(1+IF(F8&lt;0,0,IF((H8)&lt;(D8),1,IF((I8)&gt;0,2,IF((H8)&lt;(D8)*'S · Save'!$C$8,3,IF((J8)&lt;0.25*(D8),4,IF((J8)&lt;(D8),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L8" s="23" t="n"/>
+      <c r="L8" s="24" t="n"/>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="27" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="37">
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="28" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="38">
         <f>IF(C9="","",C9-(D9)-(E9))</f>
         <v/>
       </c>
-      <c r="G9" s="51">
+      <c r="G9" s="52">
         <f>IF((C9)&gt;0,F9/C9,"")</f>
         <v/>
       </c>
-      <c r="H9" s="27" t="n"/>
-      <c r="I9" s="27" t="n"/>
-      <c r="J9" s="27" t="n"/>
-      <c r="K9" s="82">
+      <c r="H9" s="28" t="n"/>
+      <c r="I9" s="28" t="n"/>
+      <c r="J9" s="28" t="n"/>
+      <c r="K9" s="83">
         <f>IF(C9="","",CHOOSE(1+IF(F9&lt;0,0,IF((H9)&lt;(D9),1,IF((I9)&gt;0,2,IF((H9)&lt;(D9)*'S · Save'!$C$8,3,IF((J9)&lt;0.25*(D9),4,IF((J9)&lt;(D9),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L9" s="23" t="n"/>
+      <c r="L9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="27" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="37">
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="28" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="38">
         <f>IF(C10="","",C10-(D10)-(E10))</f>
         <v/>
       </c>
-      <c r="G10" s="51">
+      <c r="G10" s="52">
         <f>IF((C10)&gt;0,F10/C10,"")</f>
         <v/>
       </c>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="27" t="n"/>
-      <c r="J10" s="27" t="n"/>
-      <c r="K10" s="82">
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="28" t="n"/>
+      <c r="J10" s="28" t="n"/>
+      <c r="K10" s="83">
         <f>IF(C10="","",CHOOSE(1+IF(F10&lt;0,0,IF((H10)&lt;(D10),1,IF((I10)&gt;0,2,IF((H10)&lt;(D10)*'S · Save'!$C$8,3,IF((J10)&lt;0.25*(D10),4,IF((J10)&lt;(D10),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L10" s="23" t="n"/>
+      <c r="L10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="27" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="37">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="28" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="38">
         <f>IF(C11="","",C11-(D11)-(E11))</f>
         <v/>
       </c>
-      <c r="G11" s="51">
+      <c r="G11" s="52">
         <f>IF((C11)&gt;0,F11/C11,"")</f>
         <v/>
       </c>
-      <c r="H11" s="27" t="n"/>
-      <c r="I11" s="27" t="n"/>
-      <c r="J11" s="27" t="n"/>
-      <c r="K11" s="82">
+      <c r="H11" s="28" t="n"/>
+      <c r="I11" s="28" t="n"/>
+      <c r="J11" s="28" t="n"/>
+      <c r="K11" s="83">
         <f>IF(C11="","",CHOOSE(1+IF(F11&lt;0,0,IF((H11)&lt;(D11),1,IF((I11)&gt;0,2,IF((H11)&lt;(D11)*'S · Save'!$C$8,3,IF((J11)&lt;0.25*(D11),4,IF((J11)&lt;(D11),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L11" s="23" t="n"/>
+      <c r="L11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="27" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="37">
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="28" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="38">
         <f>IF(C12="","",C12-(D12)-(E12))</f>
         <v/>
       </c>
-      <c r="G12" s="51">
+      <c r="G12" s="52">
         <f>IF((C12)&gt;0,F12/C12,"")</f>
         <v/>
       </c>
-      <c r="H12" s="27" t="n"/>
-      <c r="I12" s="27" t="n"/>
-      <c r="J12" s="27" t="n"/>
-      <c r="K12" s="82">
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="28" t="n"/>
+      <c r="J12" s="28" t="n"/>
+      <c r="K12" s="83">
         <f>IF(C12="","",CHOOSE(1+IF(F12&lt;0,0,IF((H12)&lt;(D12),1,IF((I12)&gt;0,2,IF((H12)&lt;(D12)*'S · Save'!$C$8,3,IF((J12)&lt;0.25*(D12),4,IF((J12)&lt;(D12),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L12" s="23" t="n"/>
+      <c r="L12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="27" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="37">
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="28" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="38">
         <f>IF(C13="","",C13-(D13)-(E13))</f>
         <v/>
       </c>
-      <c r="G13" s="51">
+      <c r="G13" s="52">
         <f>IF((C13)&gt;0,F13/C13,"")</f>
         <v/>
       </c>
-      <c r="H13" s="27" t="n"/>
-      <c r="I13" s="27" t="n"/>
-      <c r="J13" s="27" t="n"/>
-      <c r="K13" s="82">
+      <c r="H13" s="28" t="n"/>
+      <c r="I13" s="28" t="n"/>
+      <c r="J13" s="28" t="n"/>
+      <c r="K13" s="83">
         <f>IF(C13="","",CHOOSE(1+IF(F13&lt;0,0,IF((H13)&lt;(D13),1,IF((I13)&gt;0,2,IF((H13)&lt;(D13)*'S · Save'!$C$8,3,IF((J13)&lt;0.25*(D13),4,IF((J13)&lt;(D13),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L13" s="23" t="n"/>
+      <c r="L13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="27" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="37">
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="38">
         <f>IF(C14="","",C14-(D14)-(E14))</f>
         <v/>
       </c>
-      <c r="G14" s="51">
+      <c r="G14" s="52">
         <f>IF((C14)&gt;0,F14/C14,"")</f>
         <v/>
       </c>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="27" t="n"/>
-      <c r="J14" s="27" t="n"/>
-      <c r="K14" s="82">
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="28" t="n"/>
+      <c r="J14" s="28" t="n"/>
+      <c r="K14" s="83">
         <f>IF(C14="","",CHOOSE(1+IF(F14&lt;0,0,IF((H14)&lt;(D14),1,IF((I14)&gt;0,2,IF((H14)&lt;(D14)*'S · Save'!$C$8,3,IF((J14)&lt;0.25*(D14),4,IF((J14)&lt;(D14),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L14" s="23" t="n"/>
+      <c r="L14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="27" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="37">
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="28" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="38">
         <f>IF(C15="","",C15-(D15)-(E15))</f>
         <v/>
       </c>
-      <c r="G15" s="51">
+      <c r="G15" s="52">
         <f>IF((C15)&gt;0,F15/C15,"")</f>
         <v/>
       </c>
-      <c r="H15" s="27" t="n"/>
-      <c r="I15" s="27" t="n"/>
-      <c r="J15" s="27" t="n"/>
-      <c r="K15" s="82">
+      <c r="H15" s="28" t="n"/>
+      <c r="I15" s="28" t="n"/>
+      <c r="J15" s="28" t="n"/>
+      <c r="K15" s="83">
         <f>IF(C15="","",CHOOSE(1+IF(F15&lt;0,0,IF((H15)&lt;(D15),1,IF((I15)&gt;0,2,IF((H15)&lt;(D15)*'S · Save'!$C$8,3,IF((J15)&lt;0.25*(D15),4,IF((J15)&lt;(D15),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L15" s="23" t="n"/>
+      <c r="L15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="27" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="37">
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="28" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="38">
         <f>IF(C16="","",C16-(D16)-(E16))</f>
         <v/>
       </c>
-      <c r="G16" s="51">
+      <c r="G16" s="52">
         <f>IF((C16)&gt;0,F16/C16,"")</f>
         <v/>
       </c>
-      <c r="H16" s="27" t="n"/>
-      <c r="I16" s="27" t="n"/>
-      <c r="J16" s="27" t="n"/>
-      <c r="K16" s="82">
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="28" t="n"/>
+      <c r="J16" s="28" t="n"/>
+      <c r="K16" s="83">
         <f>IF(C16="","",CHOOSE(1+IF(F16&lt;0,0,IF((H16)&lt;(D16),1,IF((I16)&gt;0,2,IF((H16)&lt;(D16)*'S · Save'!$C$8,3,IF((J16)&lt;0.25*(D16),4,IF((J16)&lt;(D16),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L16" s="23" t="n"/>
+      <c r="L16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="27" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="37">
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="28" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="38">
         <f>IF(C17="","",C17-(D17)-(E17))</f>
         <v/>
       </c>
-      <c r="G17" s="51">
+      <c r="G17" s="52">
         <f>IF((C17)&gt;0,F17/C17,"")</f>
         <v/>
       </c>
-      <c r="H17" s="27" t="n"/>
-      <c r="I17" s="27" t="n"/>
-      <c r="J17" s="27" t="n"/>
-      <c r="K17" s="82">
+      <c r="H17" s="28" t="n"/>
+      <c r="I17" s="28" t="n"/>
+      <c r="J17" s="28" t="n"/>
+      <c r="K17" s="83">
         <f>IF(C17="","",CHOOSE(1+IF(F17&lt;0,0,IF((H17)&lt;(D17),1,IF((I17)&gt;0,2,IF((H17)&lt;(D17)*'S · Save'!$C$8,3,IF((J17)&lt;0.25*(D17),4,IF((J17)&lt;(D17),5,6)))))),"Level 0 · Overwhelmed","Level 1 · Stable","Level 2 · Buffered","Level 3 · Debt-free","Level 4 · Secure","Level 5 · Flexible","Level 6 · Free to choose"))</f>
         <v/>
       </c>
-      <c r="L17" s="23" t="n"/>
+      <c r="L17" s="24" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2281,17 +2363,26 @@
     <mergeCell ref="B3:L3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009E1B5E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C20"/>
+  <dimension ref="A1:C21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -2300,17 +2391,23 @@
     <col width="3" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>How to Use</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>About 20 minutes to set up, 15 minutes a week to run. Built for busy weeks.</t>
         </is>
@@ -2318,151 +2415,167 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="B5" s="15" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>FIRST SNAPSHOT · ABOUT 20 MINUTES</t>
         </is>
       </c>
     </row>
     <row r="6" ht="45" customHeight="1">
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>1 · Fill the yellow cells</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C6" s="18" t="inlineStr">
         <is>
           <t>Every cell with a pale yellow background and blue text is yours to edit. Everything else calculates itself. The rows already filled in are EXAMPLES: overwrite or delete them.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45" customHeight="1">
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>2 · Go tab by tab, in order</t>
         </is>
       </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="C7" s="18" t="inlineStr">
         <is>
           <t>T Track → R Reclaim → U Understand → S Save → T Time. Then Invest and Income Streams when your roadmap stage gets there. The 7 Stages tab shows which tab belongs to which stage.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="31" customHeight="1">
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="17" t="inlineStr">
         <is>
           <t>3 · Read your KEEP dashboard</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="18" t="inlineStr">
         <is>
           <t>It shows what you keep, your Freedom Level (0–6) and the one next step that matters now.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="31" customHeight="1">
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>4 · Review once a month</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="18" t="inlineStr">
         <is>
           <t>Copy this month's dashboard numbers into Monthly Review. 12 rows, one per month. Watch your level climb.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="16" t="inlineStr"/>
-      <c r="C10" s="17" t="n"/>
+      <c r="B10" s="17" t="inlineStr"/>
+      <c r="C10" s="18" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>EVERY WEEK · 15 MINUTES</t>
         </is>
       </c>
     </row>
     <row r="12" ht="31" customHeight="1">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Weekly money check</t>
         </is>
       </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="C12" s="18" t="inlineStr">
         <is>
           <t>Open KEEP and look at what you keep. Add new costs or income. Move this week's saving or debt payment.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="44" customHeight="1">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Heavy week?</t>
         </is>
       </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="C13" s="18" t="inlineStr">
         <is>
           <t>Caring for someone, deadlines, illness: open the KEEP dashboard, look at one number, close it. That counts. The system is built to pause without breaking.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="16" t="inlineStr"/>
-      <c r="C14" s="17" t="n"/>
+      <c r="B14" s="17" t="inlineStr"/>
+      <c r="C14" s="18" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="15" t="inlineStr">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>COLOUR KEY</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="18" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
         <is>
           <t>Yellow cell, blue text</t>
         </is>
       </c>
-      <c r="C16" s="17" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>Your input</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Black text</t>
         </is>
       </c>
-      <c r="C17" s="17" t="inlineStr">
+      <c r="C17" s="18" t="inlineStr">
         <is>
           <t>Calculated: please don't overwrite</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="19" t="inlineStr">
+      <c r="B18" s="20" t="inlineStr">
         <is>
           <t>Bordeaux text</t>
         </is>
       </c>
-      <c r="C18" s="17" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>Money going out or still owed (debt)</t>
         </is>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="16" t="inlineStr"/>
-      <c r="C19" s="17" t="n"/>
-    </row>
-    <row r="20" ht="31" customHeight="1">
-      <c r="B20" s="16" t="inlineStr"/>
-      <c r="C20" s="17" t="inlineStr">
-        <is>
-          <t>© cybercnslt.com · Liliane · @cyber_cnslt · For personal use by the purchaser only, please don't resell or share.</t>
+      <c r="B19" s="17" t="inlineStr"/>
+      <c r="C19" s="18" t="n"/>
+    </row>
+    <row r="20" ht="60" customHeight="1">
+      <c r="B20" s="17" t="inlineStr">
+        <is>
+          <t>Copyright</t>
+        </is>
+      </c>
+      <c r="C20" s="18" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber. All rights reserved. TRUST Tracker Pro and The Wealth Roadmap are licensed for the personal use of the purchaser only. Copying, sharing, reselling, redistributing or publishing them, in full or in part, is not permitted without written permission.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="57" customHeight="1">
+      <c r="B21" s="17" t="inlineStr">
+        <is>
+          <t>How this was made</t>
+        </is>
+      </c>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>All ideas, the 7-stage structure, the KEEP and TRUST methods, the frameworks and the stories are my own original work. Some text and design elements were created with the help of AI tools, then reviewed, edited and approved by me.</t>
         </is>
       </c>
     </row>
@@ -2472,11 +2585,20 @@
     <mergeCell ref="B2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="009E1B5E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2494,21 +2616,27 @@
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Your 7 stages</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>The Wealth Roadmap, one row per stage. Use the tabs listed, tick the stage off when the 'done when' is true, and write the date. Then move to the next stage.</t>
         </is>
@@ -2516,234 +2644,234 @@
     </row>
     <row r="4"/>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Stage</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Tabs to use</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Done when</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Date done</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
-      <c r="B6" s="21" t="n">
+      <c r="B6" s="22" t="n">
         <v>1</v>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>Money mindset: your 9–5 is your wealth engine</t>
         </is>
       </c>
-      <c r="D6" s="22" t="inlineStr">
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t>U · Understand (real hourly value)</t>
         </is>
       </c>
-      <c r="E6" s="17" t="inlineStr">
+      <c r="E6" s="18" t="inlineStr">
         <is>
           <t>You know your real hourly value and have written your money why.</t>
         </is>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G6" s="23" t="n"/>
+      <c r="G6" s="24" t="n"/>
     </row>
     <row r="7" ht="34" customHeight="1">
-      <c r="B7" s="21" t="n">
+      <c r="B7" s="22" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>Know your salary &amp; your numbers</t>
         </is>
       </c>
-      <c r="D7" s="22" t="inlineStr">
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t>T · Track, R · Reclaim, Income Streams (Career)</t>
         </is>
       </c>
-      <c r="E7" s="17" t="inlineStr">
+      <c r="E7" s="18" t="inlineStr">
         <is>
           <t>KEEP shows your keep rate, one leak is cut and your win file is started.</t>
         </is>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G7" s="23" t="n"/>
+      <c r="G7" s="24" t="n"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="B8" s="21" t="n">
+      <c r="B8" s="22" t="n">
         <v>3</v>
       </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="C8" s="17" t="inlineStr">
         <is>
           <t>Clear your debts (optional)</t>
         </is>
       </c>
-      <c r="D8" s="22" t="inlineStr">
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t>U · Understand, S · Save (starter buffer)</t>
         </is>
       </c>
-      <c r="E8" s="17" t="inlineStr">
+      <c r="E8" s="18" t="inlineStr">
         <is>
           <t>1 month of needs saved and consumer debt is €0 (Level 3).</t>
         </is>
       </c>
-      <c r="F8" s="23" t="inlineStr">
+      <c r="F8" s="24" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G8" s="23" t="n"/>
+      <c r="G8" s="24" t="n"/>
     </row>
     <row r="9" ht="34" customHeight="1">
-      <c r="B9" s="21" t="n">
+      <c r="B9" s="22" t="n">
         <v>4</v>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>Build a safety net</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t>S · Save</t>
         </is>
       </c>
-      <c r="E9" s="17" t="inlineStr">
+      <c r="E9" s="18" t="inlineStr">
         <is>
           <t>Your full emergency fund is 100% (Level 4).</t>
         </is>
       </c>
-      <c r="F9" s="23" t="inlineStr">
+      <c r="F9" s="24" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G9" s="23" t="n"/>
+      <c r="G9" s="24" t="n"/>
     </row>
     <row r="10" ht="34" customHeight="1">
-      <c r="B10" s="21" t="n">
+      <c r="B10" s="22" t="n">
         <v>5</v>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>Build wealth with smart investing</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t>Invest</t>
         </is>
       </c>
-      <c r="E10" s="17" t="inlineStr">
+      <c r="E10" s="18" t="inlineStr">
         <is>
           <t>A fixed monthly amount runs on payday and you can explain what you own.</t>
         </is>
       </c>
-      <c r="F10" s="23" t="inlineStr">
+      <c r="F10" s="24" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G10" s="23" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11" ht="34" customHeight="1">
-      <c r="B11" s="21" t="n">
+      <c r="B11" s="22" t="n">
         <v>6</v>
       </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>Build multiple income streams</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t>Income Streams</t>
         </is>
       </c>
-      <c r="E11" s="17" t="inlineStr">
+      <c r="E11" s="18" t="inlineStr">
         <is>
           <t>One stream finished its 90-day test with a keep, change or stop decision.</t>
         </is>
       </c>
-      <c r="F11" s="23" t="inlineStr">
+      <c r="F11" s="24" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G11" s="23" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12" ht="34" customHeight="1">
-      <c r="B12" s="21" t="n">
+      <c r="B12" s="22" t="n">
         <v>7</v>
       </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>Repeat, automate &amp; buy back time</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t>T · Time, Monthly Review</t>
         </is>
       </c>
-      <c r="E12" s="17" t="inlineStr">
+      <c r="E12" s="18" t="inlineStr">
         <is>
           <t>Transfers run on their own and you have taken back your first hours.</t>
         </is>
       </c>
-      <c r="F12" s="23" t="inlineStr">
+      <c r="F12" s="24" t="inlineStr">
         <is>
           <t>To do</t>
         </is>
       </c>
-      <c r="G12" s="23" t="n"/>
+      <c r="G12" s="24" t="n"/>
     </row>
     <row r="13"/>
     <row r="14" ht="18" customHeight="1">
-      <c r="C14" s="16" t="inlineStr">
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>Stages done</t>
         </is>
       </c>
-      <c r="D14" s="24">
+      <c r="D14" s="25">
         <f>COUNTIF(F6:F12,"Done")&amp;" of 7"</f>
         <v/>
       </c>
     </row>
     <row r="15"/>
     <row r="16" ht="31" customHeight="1">
-      <c r="C16" s="25" t="inlineStr">
+      <c r="C16" s="26" t="inlineStr">
         <is>
           <t>Stage 3 is optional: if you have no consumer debt, save the starter buffer and go straight to stage 4. Your money still grows while you pay debt off, just more slowly.</t>
         </is>
@@ -2761,11 +2889,20 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001A9E9E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2782,20 +2919,26 @@
     <col width="34" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>T · Track</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Roadmap stage 2 · List what comes in and what goes out in a normal month. Yearly costs? Divide by 12. Debt minimum payments are a Need. Don't list savings transfers here: what's left over is what you KEEP.</t>
         </is>
@@ -2803,623 +2946,623 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>MONEY IN (net, per month)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Source</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
-      <c r="E6" s="20" t="inlineStr">
+      <c r="E6" s="21" t="inlineStr">
         <is>
           <t>€ / month</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Salary (net)</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Main job</t>
         </is>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="28" t="n">
         <v>2500</v>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Side income</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>Total from Income Streams tab</t>
         </is>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="29">
         <f>'Income Streams'!G23</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Benefits / allowances</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>e.g. child benefit, care allowance</t>
         </is>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="E10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="E11" s="27" t="n"/>
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="E11" s="28" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="E12" s="28" t="n"/>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>Total money in</t>
         </is>
       </c>
-      <c r="E13" s="29">
+      <c r="E13" s="30">
         <f>SUM(E7:E12)</f>
         <v/>
       </c>
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="B15" s="26" t="inlineStr">
+      <c r="B15" s="27" t="inlineStr">
         <is>
           <t>MONEY OUT (per month)</t>
         </is>
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="B16" s="20" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>Expense</t>
         </is>
       </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>Category</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>Need / Want</t>
         </is>
       </c>
-      <c r="E16" s="20" t="inlineStr">
+      <c r="E16" s="21" t="inlineStr">
         <is>
           <t>€ / month</t>
         </is>
       </c>
-      <c r="F16" s="20" t="inlineStr">
+      <c r="F16" s="21" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="B17" s="23" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Rent / mortgage</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>Housing</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="28" t="n">
         <v>900</v>
       </c>
-      <c r="F17" s="23" t="inlineStr">
+      <c r="F17" s="24" t="inlineStr">
         <is>
           <t>Example rows: overwrite with yours</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Electricity, internet, phone</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>Utilities &amp; phone</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="28" t="n">
         <v>140</v>
       </c>
-      <c r="F18" s="23" t="n"/>
+      <c r="F18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="C19" s="23" t="inlineStr">
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>Groceries</t>
         </is>
       </c>
-      <c r="D19" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="28" t="n">
         <v>320</v>
       </c>
-      <c r="F19" s="23" t="n"/>
+      <c r="F19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Public transport / fuel</t>
         </is>
       </c>
-      <c r="C20" s="23" t="inlineStr">
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="D20" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <v>90</v>
       </c>
-      <c r="F20" s="23" t="n"/>
+      <c r="F20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="C21" s="23" t="inlineStr">
+      <c r="C21" s="24" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="D21" s="23" t="inlineStr">
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="28" t="n">
         <v>80</v>
       </c>
-      <c r="F21" s="23" t="n"/>
+      <c r="F21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="23" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Care support for mum</t>
         </is>
       </c>
-      <c r="C22" s="23" t="inlineStr">
+      <c r="C22" s="24" t="inlineStr">
         <is>
           <t>Caregiving</t>
         </is>
       </c>
-      <c r="D22" s="23" t="inlineStr">
+      <c r="D22" s="24" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E22" s="27" t="n">
+      <c r="E22" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="F22" s="23" t="n"/>
+      <c r="F22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="23" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Credit card minimum</t>
         </is>
       </c>
-      <c r="C23" s="23" t="inlineStr">
+      <c r="C23" s="24" t="inlineStr">
         <is>
           <t>Debt payments</t>
         </is>
       </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
         <is>
           <t>Need</t>
         </is>
       </c>
-      <c r="E23" s="27" t="n">
+      <c r="E23" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="F23" s="23" t="n"/>
+      <c r="F23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="23" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Streaming &amp; apps</t>
         </is>
       </c>
-      <c r="C24" s="23" t="inlineStr">
+      <c r="C24" s="24" t="inlineStr">
         <is>
           <t>Subscriptions</t>
         </is>
       </c>
-      <c r="D24" s="23" t="inlineStr">
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>Want</t>
         </is>
       </c>
-      <c r="E24" s="27" t="n">
+      <c r="E24" s="28" t="n">
         <v>45</v>
       </c>
-      <c r="F24" s="23" t="n"/>
+      <c r="F24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="23" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Eating out &amp; takeaway</t>
         </is>
       </c>
-      <c r="C25" s="23" t="inlineStr">
+      <c r="C25" s="24" t="inlineStr">
         <is>
           <t>Eating out</t>
         </is>
       </c>
-      <c r="D25" s="23" t="inlineStr">
+      <c r="D25" s="24" t="inlineStr">
         <is>
           <t>Want</t>
         </is>
       </c>
-      <c r="E25" s="27" t="n">
+      <c r="E25" s="28" t="n">
         <v>120</v>
       </c>
-      <c r="F25" s="23" t="n"/>
+      <c r="F25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="23" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Clothes &amp; shopping</t>
         </is>
       </c>
-      <c r="C26" s="23" t="inlineStr">
+      <c r="C26" s="24" t="inlineStr">
         <is>
           <t>Shopping</t>
         </is>
       </c>
-      <c r="D26" s="23" t="inlineStr">
+      <c r="D26" s="24" t="inlineStr">
         <is>
           <t>Want</t>
         </is>
       </c>
-      <c r="E26" s="27" t="n">
+      <c r="E26" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="F26" s="23" t="n"/>
+      <c r="F26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="23" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="27" t="n"/>
-      <c r="F27" s="23" t="n"/>
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="24" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="23" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="23" t="n"/>
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="24" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="23" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="23" t="n"/>
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="24" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="24" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="23" t="n"/>
-      <c r="C30" s="23" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="23" t="n"/>
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="24" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="24" t="n"/>
     </row>
     <row r="31">
-      <c r="B31" s="23" t="n"/>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="23" t="n"/>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="23" t="n"/>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="24" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="23" t="n"/>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="23" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="23" t="n"/>
+      <c r="B32" s="24" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="24" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="24" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="23" t="n"/>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="23" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="23" t="n"/>
+      <c r="B33" s="24" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="24" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="23" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="23" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="24" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="23" t="n"/>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="23" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="23" t="n"/>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="24" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="23" t="n"/>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="23" t="n"/>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="24" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="24" t="n"/>
     </row>
     <row r="37">
-      <c r="B37" s="23" t="n"/>
-      <c r="C37" s="23" t="n"/>
-      <c r="D37" s="23" t="n"/>
-      <c r="E37" s="27" t="n"/>
-      <c r="F37" s="23" t="n"/>
+      <c r="B37" s="24" t="n"/>
+      <c r="C37" s="24" t="n"/>
+      <c r="D37" s="24" t="n"/>
+      <c r="E37" s="28" t="n"/>
+      <c r="F37" s="24" t="n"/>
     </row>
     <row r="38">
-      <c r="B38" s="23" t="n"/>
-      <c r="C38" s="23" t="n"/>
-      <c r="D38" s="23" t="n"/>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="23" t="n"/>
+      <c r="B38" s="24" t="n"/>
+      <c r="C38" s="24" t="n"/>
+      <c r="D38" s="24" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="24" t="n"/>
     </row>
     <row r="39">
-      <c r="B39" s="23" t="n"/>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="27" t="n"/>
-      <c r="F39" s="23" t="n"/>
+      <c r="B39" s="24" t="n"/>
+      <c r="C39" s="24" t="n"/>
+      <c r="D39" s="24" t="n"/>
+      <c r="E39" s="28" t="n"/>
+      <c r="F39" s="24" t="n"/>
     </row>
     <row r="40">
-      <c r="B40" s="23" t="n"/>
-      <c r="C40" s="23" t="n"/>
-      <c r="D40" s="23" t="n"/>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="23" t="n"/>
+      <c r="B40" s="24" t="n"/>
+      <c r="C40" s="24" t="n"/>
+      <c r="D40" s="24" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="24" t="n"/>
     </row>
     <row r="41">
-      <c r="B41" s="23" t="n"/>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="27" t="n"/>
-      <c r="F41" s="23" t="n"/>
+      <c r="B41" s="24" t="n"/>
+      <c r="C41" s="24" t="n"/>
+      <c r="D41" s="24" t="n"/>
+      <c r="E41" s="28" t="n"/>
+      <c r="F41" s="24" t="n"/>
     </row>
     <row r="42">
-      <c r="B42" s="23" t="n"/>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="23" t="n"/>
+      <c r="B42" s="24" t="n"/>
+      <c r="C42" s="24" t="n"/>
+      <c r="D42" s="24" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="24" t="n"/>
     </row>
     <row r="43">
-      <c r="B43" s="23" t="n"/>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="23" t="n"/>
-      <c r="E43" s="27" t="n"/>
-      <c r="F43" s="23" t="n"/>
+      <c r="B43" s="24" t="n"/>
+      <c r="C43" s="24" t="n"/>
+      <c r="D43" s="24" t="n"/>
+      <c r="E43" s="28" t="n"/>
+      <c r="F43" s="24" t="n"/>
     </row>
     <row r="44">
-      <c r="B44" s="23" t="n"/>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="27" t="n"/>
-      <c r="F44" s="23" t="n"/>
+      <c r="B44" s="24" t="n"/>
+      <c r="C44" s="24" t="n"/>
+      <c r="D44" s="24" t="n"/>
+      <c r="E44" s="28" t="n"/>
+      <c r="F44" s="24" t="n"/>
     </row>
     <row r="45">
-      <c r="B45" s="23" t="n"/>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="23" t="n"/>
-      <c r="E45" s="27" t="n"/>
-      <c r="F45" s="23" t="n"/>
+      <c r="B45" s="24" t="n"/>
+      <c r="C45" s="24" t="n"/>
+      <c r="D45" s="24" t="n"/>
+      <c r="E45" s="28" t="n"/>
+      <c r="F45" s="24" t="n"/>
     </row>
     <row r="46">
-      <c r="B46" s="23" t="n"/>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="23" t="n"/>
-      <c r="E46" s="27" t="n"/>
-      <c r="F46" s="23" t="n"/>
+      <c r="B46" s="24" t="n"/>
+      <c r="C46" s="24" t="n"/>
+      <c r="D46" s="24" t="n"/>
+      <c r="E46" s="28" t="n"/>
+      <c r="F46" s="24" t="n"/>
     </row>
     <row r="47">
-      <c r="B47" s="23" t="n"/>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="23" t="n"/>
-      <c r="E47" s="27" t="n"/>
-      <c r="F47" s="23" t="n"/>
+      <c r="B47" s="24" t="n"/>
+      <c r="C47" s="24" t="n"/>
+      <c r="D47" s="24" t="n"/>
+      <c r="E47" s="28" t="n"/>
+      <c r="F47" s="24" t="n"/>
     </row>
     <row r="48">
-      <c r="B48" s="23" t="n"/>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="23" t="n"/>
-      <c r="E48" s="27" t="n"/>
-      <c r="F48" s="23" t="n"/>
+      <c r="B48" s="24" t="n"/>
+      <c r="C48" s="24" t="n"/>
+      <c r="D48" s="24" t="n"/>
+      <c r="E48" s="28" t="n"/>
+      <c r="F48" s="24" t="n"/>
     </row>
     <row r="49">
-      <c r="B49" s="23" t="n"/>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="23" t="n"/>
-      <c r="E49" s="27" t="n"/>
-      <c r="F49" s="23" t="n"/>
+      <c r="B49" s="24" t="n"/>
+      <c r="C49" s="24" t="n"/>
+      <c r="D49" s="24" t="n"/>
+      <c r="E49" s="28" t="n"/>
+      <c r="F49" s="24" t="n"/>
     </row>
     <row r="50">
-      <c r="B50" s="23" t="n"/>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="23" t="n"/>
-      <c r="E50" s="27" t="n"/>
-      <c r="F50" s="23" t="n"/>
+      <c r="B50" s="24" t="n"/>
+      <c r="C50" s="24" t="n"/>
+      <c r="D50" s="24" t="n"/>
+      <c r="E50" s="28" t="n"/>
+      <c r="F50" s="24" t="n"/>
     </row>
     <row r="51">
-      <c r="B51" s="23" t="n"/>
-      <c r="C51" s="23" t="n"/>
-      <c r="D51" s="23" t="n"/>
-      <c r="E51" s="27" t="n"/>
-      <c r="F51" s="23" t="n"/>
+      <c r="B51" s="24" t="n"/>
+      <c r="C51" s="24" t="n"/>
+      <c r="D51" s="24" t="n"/>
+      <c r="E51" s="28" t="n"/>
+      <c r="F51" s="24" t="n"/>
     </row>
     <row r="52">
-      <c r="B52" s="23" t="n"/>
-      <c r="C52" s="23" t="n"/>
-      <c r="D52" s="23" t="n"/>
-      <c r="E52" s="27" t="n"/>
-      <c r="F52" s="23" t="n"/>
+      <c r="B52" s="24" t="n"/>
+      <c r="C52" s="24" t="n"/>
+      <c r="D52" s="24" t="n"/>
+      <c r="E52" s="28" t="n"/>
+      <c r="F52" s="24" t="n"/>
     </row>
     <row r="53">
-      <c r="B53" s="23" t="n"/>
-      <c r="C53" s="23" t="n"/>
-      <c r="D53" s="23" t="n"/>
-      <c r="E53" s="27" t="n"/>
-      <c r="F53" s="23" t="n"/>
+      <c r="B53" s="24" t="n"/>
+      <c r="C53" s="24" t="n"/>
+      <c r="D53" s="24" t="n"/>
+      <c r="E53" s="28" t="n"/>
+      <c r="F53" s="24" t="n"/>
     </row>
     <row r="54">
-      <c r="B54" s="23" t="n"/>
-      <c r="C54" s="23" t="n"/>
-      <c r="D54" s="23" t="n"/>
-      <c r="E54" s="27" t="n"/>
-      <c r="F54" s="23" t="n"/>
+      <c r="B54" s="24" t="n"/>
+      <c r="C54" s="24" t="n"/>
+      <c r="D54" s="24" t="n"/>
+      <c r="E54" s="28" t="n"/>
+      <c r="F54" s="24" t="n"/>
     </row>
     <row r="55">
-      <c r="B55" s="23" t="n"/>
-      <c r="C55" s="23" t="n"/>
-      <c r="D55" s="23" t="n"/>
-      <c r="E55" s="27" t="n"/>
-      <c r="F55" s="23" t="n"/>
+      <c r="B55" s="24" t="n"/>
+      <c r="C55" s="24" t="n"/>
+      <c r="D55" s="24" t="n"/>
+      <c r="E55" s="28" t="n"/>
+      <c r="F55" s="24" t="n"/>
     </row>
     <row r="56">
-      <c r="B56" s="23" t="n"/>
-      <c r="C56" s="23" t="n"/>
-      <c r="D56" s="23" t="n"/>
-      <c r="E56" s="27" t="n"/>
-      <c r="F56" s="23" t="n"/>
+      <c r="B56" s="24" t="n"/>
+      <c r="C56" s="24" t="n"/>
+      <c r="D56" s="24" t="n"/>
+      <c r="E56" s="28" t="n"/>
+      <c r="F56" s="24" t="n"/>
     </row>
     <row r="57"/>
     <row r="58" ht="18" customHeight="1">
-      <c r="B58" s="16" t="inlineStr">
+      <c r="B58" s="17" t="inlineStr">
         <is>
           <t>Needs (your baseline)</t>
         </is>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="30">
         <f>SUMIF(D17:D56,"Need",E17:E56)</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="18" customHeight="1">
-      <c r="B59" s="16" t="inlineStr">
+      <c r="B59" s="17" t="inlineStr">
         <is>
           <t>Wants</t>
         </is>
       </c>
-      <c r="E59" s="29">
+      <c r="E59" s="30">
         <f>SUMIF(D17:D56,"Want",E17:E56)</f>
         <v/>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
-      <c r="B60" s="30" t="inlineStr">
+      <c r="B60" s="31" t="inlineStr">
         <is>
           <t>of which caregiving</t>
         </is>
       </c>
-      <c r="E60" s="31">
+      <c r="E60" s="32">
         <f>SUMIF(C17:C56,"Caregiving",E17:E56)</f>
         <v/>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
-      <c r="B61" s="32" t="inlineStr">
+      <c r="B61" s="33" t="inlineStr">
         <is>
           <t>Unsorted (pick Need or Want)</t>
         </is>
       </c>
-      <c r="E61" s="33">
+      <c r="E61" s="34">
         <f>SUM(E17:E56)-E58-E59</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
-      <c r="B62" s="34" t="inlineStr">
+      <c r="B62" s="35" t="inlineStr">
         <is>
           <t>KEEP (in − needs − wants)</t>
         </is>
       </c>
-      <c r="E62" s="35">
+      <c r="E62" s="36">
         <f>E13-E58-E59</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="18" customHeight="1">
-      <c r="B63" s="34" t="inlineStr">
+      <c r="B63" s="35" t="inlineStr">
         <is>
           <t>Keep rate</t>
         </is>
       </c>
-      <c r="E63" s="36">
+      <c r="E63" s="37">
         <f>IF(E13&gt;0,E62/E13,0)</f>
         <v/>
       </c>
@@ -3438,12 +3581,21 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001A9E9E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3461,21 +3613,27 @@
     <col width="33" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>R · Reclaim</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Roadmap stage 2 · Go through bank statements for 10 minutes. Every subscription, fee and contract goes here. Decide: Keep, Cut, Reduce or Renegotiate. One call to a provider can be worth hundreds a year.</t>
         </is>
@@ -3483,398 +3641,398 @@
     </row>
     <row r="4"/>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Subscription / cost</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Now € / month</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Decision</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>New € / month</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>Reclaimed € / month</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Next action</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Second streaming service</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>13</v>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Cut</t>
         </is>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="37">
+      <c r="F6" s="38">
         <f>IF(OR(C6="",D6="",D6="Keep"),0,MAX(0,C6-(E6)))</f>
         <v/>
       </c>
-      <c r="G6" s="23" t="inlineStr">
+      <c r="G6" s="24" t="inlineStr">
         <is>
           <t>Cancel before renewal on the 15th</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Gym (not used since spring)</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>35</v>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>Reduce</t>
         </is>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="28" t="n">
         <v>15</v>
       </c>
-      <c r="F7" s="37">
+      <c r="F7" s="38">
         <f>IF(OR(C7="",D7="",D7="Keep"),0,MAX(0,C7-(E7)))</f>
         <v/>
       </c>
-      <c r="G7" s="23" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>Switch to off-peak plan</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Mobile contract</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>Renegotiate</t>
         </is>
       </c>
-      <c r="E8" s="27" t="n">
+      <c r="E8" s="28" t="n">
         <v>25</v>
       </c>
-      <c r="F8" s="37">
+      <c r="F8" s="38">
         <f>IF(OR(C8="",D8="",D8="Keep"),0,MAX(0,C8-(E8)))</f>
         <v/>
       </c>
-      <c r="G8" s="23" t="inlineStr">
+      <c r="G8" s="24" t="inlineStr">
         <is>
           <t>Call and ask for current tariff</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Cloud storage</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>Keep</t>
         </is>
       </c>
-      <c r="E9" s="27" t="n">
+      <c r="E9" s="28" t="n">
         <v>3</v>
       </c>
-      <c r="F9" s="37">
+      <c r="F9" s="38">
         <f>IF(OR(C9="",D9="",D9="Keep"),0,MAX(0,C9-(E9)))</f>
         <v/>
       </c>
-      <c r="G9" s="23" t="inlineStr"/>
+      <c r="G9" s="24" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="37">
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="38">
         <f>IF(OR(C10="",D10="",D10="Keep"),0,MAX(0,C10-(E10)))</f>
         <v/>
       </c>
-      <c r="G10" s="23" t="n"/>
+      <c r="G10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="37">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="38">
         <f>IF(OR(C11="",D11="",D11="Keep"),0,MAX(0,C11-(E11)))</f>
         <v/>
       </c>
-      <c r="G11" s="23" t="n"/>
+      <c r="G11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="37">
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="38">
         <f>IF(OR(C12="",D12="",D12="Keep"),0,MAX(0,C12-(E12)))</f>
         <v/>
       </c>
-      <c r="G12" s="23" t="n"/>
+      <c r="G12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="37">
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="38">
         <f>IF(OR(C13="",D13="",D13="Keep"),0,MAX(0,C13-(E13)))</f>
         <v/>
       </c>
-      <c r="G13" s="23" t="n"/>
+      <c r="G13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="37">
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="38">
         <f>IF(OR(C14="",D14="",D14="Keep"),0,MAX(0,C14-(E14)))</f>
         <v/>
       </c>
-      <c r="G14" s="23" t="n"/>
+      <c r="G14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="37">
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="38">
         <f>IF(OR(C15="",D15="",D15="Keep"),0,MAX(0,C15-(E15)))</f>
         <v/>
       </c>
-      <c r="G15" s="23" t="n"/>
+      <c r="G15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="27" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="37">
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="28" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="38">
         <f>IF(OR(C16="",D16="",D16="Keep"),0,MAX(0,C16-(E16)))</f>
         <v/>
       </c>
-      <c r="G16" s="23" t="n"/>
+      <c r="G16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="27" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="27" t="n"/>
-      <c r="F17" s="37">
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="28" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="28" t="n"/>
+      <c r="F17" s="38">
         <f>IF(OR(C17="",D17="",D17="Keep"),0,MAX(0,C17-(E17)))</f>
         <v/>
       </c>
-      <c r="G17" s="23" t="n"/>
+      <c r="G17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="27" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="37">
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="28" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="38">
         <f>IF(OR(C18="",D18="",D18="Keep"),0,MAX(0,C18-(E18)))</f>
         <v/>
       </c>
-      <c r="G18" s="23" t="n"/>
+      <c r="G18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="23" t="n"/>
-      <c r="C19" s="27" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="27" t="n"/>
-      <c r="F19" s="37">
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="28" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="28" t="n"/>
+      <c r="F19" s="38">
         <f>IF(OR(C19="",D19="",D19="Keep"),0,MAX(0,C19-(E19)))</f>
         <v/>
       </c>
-      <c r="G19" s="23" t="n"/>
+      <c r="G19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="27" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="37">
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="28" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="38">
         <f>IF(OR(C20="",D20="",D20="Keep"),0,MAX(0,C20-(E20)))</f>
         <v/>
       </c>
-      <c r="G20" s="23" t="n"/>
+      <c r="G20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="27" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="27" t="n"/>
-      <c r="F21" s="37">
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="28" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="28" t="n"/>
+      <c r="F21" s="38">
         <f>IF(OR(C21="",D21="",D21="Keep"),0,MAX(0,C21-(E21)))</f>
         <v/>
       </c>
-      <c r="G21" s="23" t="n"/>
+      <c r="G21" s="24" t="n"/>
     </row>
     <row r="22">
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="23" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="37">
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="24" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="38">
         <f>IF(OR(C22="",D22="",D22="Keep"),0,MAX(0,C22-(E22)))</f>
         <v/>
       </c>
-      <c r="G22" s="23" t="n"/>
+      <c r="G22" s="24" t="n"/>
     </row>
     <row r="23">
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="37">
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="24" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="38">
         <f>IF(OR(C23="",D23="",D23="Keep"),0,MAX(0,C23-(E23)))</f>
         <v/>
       </c>
-      <c r="G23" s="23" t="n"/>
+      <c r="G23" s="24" t="n"/>
     </row>
     <row r="24">
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="37">
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="24" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="38">
         <f>IF(OR(C24="",D24="",D24="Keep"),0,MAX(0,C24-(E24)))</f>
         <v/>
       </c>
-      <c r="G24" s="23" t="n"/>
+      <c r="G24" s="24" t="n"/>
     </row>
     <row r="25">
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="27" t="n"/>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="37">
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="24" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="38">
         <f>IF(OR(C25="",D25="",D25="Keep"),0,MAX(0,C25-(E25)))</f>
         <v/>
       </c>
-      <c r="G25" s="23" t="n"/>
+      <c r="G25" s="24" t="n"/>
     </row>
     <row r="26">
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="37">
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="24" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="38">
         <f>IF(OR(C26="",D26="",D26="Keep"),0,MAX(0,C26-(E26)))</f>
         <v/>
       </c>
-      <c r="G26" s="23" t="n"/>
+      <c r="G26" s="24" t="n"/>
     </row>
     <row r="27">
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="27" t="n"/>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="27" t="n"/>
-      <c r="F27" s="37">
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="24" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="38">
         <f>IF(OR(C27="",D27="",D27="Keep"),0,MAX(0,C27-(E27)))</f>
         <v/>
       </c>
-      <c r="G27" s="23" t="n"/>
+      <c r="G27" s="24" t="n"/>
     </row>
     <row r="28">
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="23" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="37">
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="24" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="38">
         <f>IF(OR(C28="",D28="",D28="Keep"),0,MAX(0,C28-(E28)))</f>
         <v/>
       </c>
-      <c r="G28" s="23" t="n"/>
+      <c r="G28" s="24" t="n"/>
     </row>
     <row r="29">
-      <c r="B29" s="23" t="n"/>
-      <c r="C29" s="27" t="n"/>
-      <c r="D29" s="23" t="n"/>
-      <c r="E29" s="27" t="n"/>
-      <c r="F29" s="37">
+      <c r="B29" s="24" t="n"/>
+      <c r="C29" s="28" t="n"/>
+      <c r="D29" s="24" t="n"/>
+      <c r="E29" s="28" t="n"/>
+      <c r="F29" s="38">
         <f>IF(OR(C29="",D29="",D29="Keep"),0,MAX(0,C29-(E29)))</f>
         <v/>
       </c>
-      <c r="G29" s="23" t="n"/>
+      <c r="G29" s="24" t="n"/>
     </row>
     <row r="30">
-      <c r="B30" s="23" t="n"/>
-      <c r="C30" s="27" t="n"/>
-      <c r="D30" s="23" t="n"/>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="37">
+      <c r="B30" s="24" t="n"/>
+      <c r="C30" s="28" t="n"/>
+      <c r="D30" s="24" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="38">
         <f>IF(OR(C30="",D30="",D30="Keep"),0,MAX(0,C30-(E30)))</f>
         <v/>
       </c>
-      <c r="G30" s="23" t="n"/>
+      <c r="G30" s="24" t="n"/>
     </row>
     <row r="31"/>
     <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Reclaimable per month</t>
         </is>
       </c>
-      <c r="F32" s="35">
+      <c r="F32" s="36">
         <f>SUM(F6:F30)</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="17" t="inlineStr">
         <is>
           <t>Reclaimable per year</t>
         </is>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <f>F32*12</f>
         <v/>
       </c>
     </row>
     <row r="34"/>
     <row r="35" ht="30" customHeight="1">
-      <c r="B35" s="25" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>Rule: reclaimed money gets a job the same day. Move it to your buffer or debt before it disappears into everyday spending.</t>
         </is>
@@ -3892,11 +4050,20 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001A9E9E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3916,23 +4083,29 @@
     <col width="12" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>U · Understand</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="13" t="n"/>
-      <c r="H2" s="13" t="n"/>
-      <c r="I2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Roadmap stages 1–3 · Debt first: what you owe, what it costs you each month, and which one to attack first (highest interest = highest priority). Then: what is one hour of your working life really worth?</t>
         </is>
@@ -3940,296 +4113,296 @@
     </row>
     <row r="4"/>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Debt</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Balance €</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Interest % / year</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Minimum € / month</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>Extra € / month</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>Interest cost € / month</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>Months to clear</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>Priority</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Credit card</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>1500</v>
       </c>
-      <c r="D6" s="38" t="n">
+      <c r="D6" s="39" t="n">
         <v>0.199</v>
       </c>
-      <c r="E6" s="27" t="n">
+      <c r="E6" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="28" t="n">
         <v>40</v>
       </c>
-      <c r="G6" s="39">
+      <c r="G6" s="40">
         <f>IF((C6)&gt;0,C6*(D6)/12,0)</f>
         <v/>
       </c>
-      <c r="H6" s="40">
+      <c r="H6" s="41">
         <f>IF((C6)&lt;=0,"",IF((E6)+(F6)&lt;=G6,"Payment too low",ROUNDUP(IF((D6)=0,C6/((E6)+(F6)),NPER(D6/12,-((E6)+(F6)),C6)),0)))</f>
         <v/>
       </c>
-      <c r="I6" s="41">
+      <c r="I6" s="42">
         <f>IF((C6)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D6))+1)</f>
         <v/>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Overdraft</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="D7" s="38" t="n">
+      <c r="D7" s="39" t="n">
         <v>0.12</v>
       </c>
-      <c r="E7" s="27" t="n">
+      <c r="E7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="G7" s="39">
+      <c r="G7" s="40">
         <f>IF((C7)&gt;0,C7*(D7)/12,0)</f>
         <v/>
       </c>
-      <c r="H7" s="40">
+      <c r="H7" s="41">
         <f>IF((C7)&lt;=0,"",IF((E7)+(F7)&lt;=G7,"Payment too low",ROUNDUP(IF((D7)=0,C7/((E7)+(F7)),NPER(D7/12,-((E7)+(F7)),C7)),0)))</f>
         <v/>
       </c>
-      <c r="I7" s="41">
+      <c r="I7" s="42">
         <f>IF((C7)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D7))+1)</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="n"/>
-      <c r="C8" s="27" t="n"/>
-      <c r="D8" s="38" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="39">
+      <c r="B8" s="24" t="n"/>
+      <c r="C8" s="28" t="n"/>
+      <c r="D8" s="39" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="40">
         <f>IF((C8)&gt;0,C8*(D8)/12,0)</f>
         <v/>
       </c>
-      <c r="H8" s="40">
+      <c r="H8" s="41">
         <f>IF((C8)&lt;=0,"",IF((E8)+(F8)&lt;=G8,"Payment too low",ROUNDUP(IF((D8)=0,C8/((E8)+(F8)),NPER(D8/12,-((E8)+(F8)),C8)),0)))</f>
         <v/>
       </c>
-      <c r="I8" s="41">
+      <c r="I8" s="42">
         <f>IF((C8)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D8))+1)</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="27" t="n"/>
-      <c r="D9" s="38" t="n"/>
-      <c r="E9" s="27" t="n"/>
-      <c r="F9" s="27" t="n"/>
-      <c r="G9" s="39">
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="28" t="n"/>
+      <c r="D9" s="39" t="n"/>
+      <c r="E9" s="28" t="n"/>
+      <c r="F9" s="28" t="n"/>
+      <c r="G9" s="40">
         <f>IF((C9)&gt;0,C9*(D9)/12,0)</f>
         <v/>
       </c>
-      <c r="H9" s="40">
+      <c r="H9" s="41">
         <f>IF((C9)&lt;=0,"",IF((E9)+(F9)&lt;=G9,"Payment too low",ROUNDUP(IF((D9)=0,C9/((E9)+(F9)),NPER(D9/12,-((E9)+(F9)),C9)),0)))</f>
         <v/>
       </c>
-      <c r="I9" s="41">
+      <c r="I9" s="42">
         <f>IF((C9)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D9))+1)</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="27" t="n"/>
-      <c r="D10" s="38" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="39">
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="28" t="n"/>
+      <c r="D10" s="39" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="40">
         <f>IF((C10)&gt;0,C10*(D10)/12,0)</f>
         <v/>
       </c>
-      <c r="H10" s="40">
+      <c r="H10" s="41">
         <f>IF((C10)&lt;=0,"",IF((E10)+(F10)&lt;=G10,"Payment too low",ROUNDUP(IF((D10)=0,C10/((E10)+(F10)),NPER(D10/12,-((E10)+(F10)),C10)),0)))</f>
         <v/>
       </c>
-      <c r="I10" s="41">
+      <c r="I10" s="42">
         <f>IF((C10)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D10))+1)</f>
         <v/>
       </c>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="27" t="n"/>
-      <c r="D11" s="38" t="n"/>
-      <c r="E11" s="27" t="n"/>
-      <c r="F11" s="27" t="n"/>
-      <c r="G11" s="39">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="28" t="n"/>
+      <c r="D11" s="39" t="n"/>
+      <c r="E11" s="28" t="n"/>
+      <c r="F11" s="28" t="n"/>
+      <c r="G11" s="40">
         <f>IF((C11)&gt;0,C11*(D11)/12,0)</f>
         <v/>
       </c>
-      <c r="H11" s="40">
+      <c r="H11" s="41">
         <f>IF((C11)&lt;=0,"",IF((E11)+(F11)&lt;=G11,"Payment too low",ROUNDUP(IF((D11)=0,C11/((E11)+(F11)),NPER(D11/12,-((E11)+(F11)),C11)),0)))</f>
         <v/>
       </c>
-      <c r="I11" s="41">
+      <c r="I11" s="42">
         <f>IF((C11)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D11))+1)</f>
         <v/>
       </c>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="27" t="n"/>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="39">
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="28" t="n"/>
+      <c r="D12" s="39" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="40">
         <f>IF((C12)&gt;0,C12*(D12)/12,0)</f>
         <v/>
       </c>
-      <c r="H12" s="40">
+      <c r="H12" s="41">
         <f>IF((C12)&lt;=0,"",IF((E12)+(F12)&lt;=G12,"Payment too low",ROUNDUP(IF((D12)=0,C12/((E12)+(F12)),NPER(D12/12,-((E12)+(F12)),C12)),0)))</f>
         <v/>
       </c>
-      <c r="I12" s="41">
+      <c r="I12" s="42">
         <f>IF((C12)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D12))+1)</f>
         <v/>
       </c>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="27" t="n"/>
-      <c r="D13" s="38" t="n"/>
-      <c r="E13" s="27" t="n"/>
-      <c r="F13" s="27" t="n"/>
-      <c r="G13" s="39">
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="28" t="n"/>
+      <c r="D13" s="39" t="n"/>
+      <c r="E13" s="28" t="n"/>
+      <c r="F13" s="28" t="n"/>
+      <c r="G13" s="40">
         <f>IF((C13)&gt;0,C13*(D13)/12,0)</f>
         <v/>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="41">
         <f>IF((C13)&lt;=0,"",IF((E13)+(F13)&lt;=G13,"Payment too low",ROUNDUP(IF((D13)=0,C13/((E13)+(F13)),NPER(D13/12,-((E13)+(F13)),C13)),0)))</f>
         <v/>
       </c>
-      <c r="I13" s="41">
+      <c r="I13" s="42">
         <f>IF((C13)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D13))+1)</f>
         <v/>
       </c>
     </row>
     <row r="14">
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="27" t="n"/>
-      <c r="D14" s="38" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="39">
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="28" t="n"/>
+      <c r="D14" s="39" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="40">
         <f>IF((C14)&gt;0,C14*(D14)/12,0)</f>
         <v/>
       </c>
-      <c r="H14" s="40">
+      <c r="H14" s="41">
         <f>IF((C14)&lt;=0,"",IF((E14)+(F14)&lt;=G14,"Payment too low",ROUNDUP(IF((D14)=0,C14/((E14)+(F14)),NPER(D14/12,-((E14)+(F14)),C14)),0)))</f>
         <v/>
       </c>
-      <c r="I14" s="41">
+      <c r="I14" s="42">
         <f>IF((C14)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D14))+1)</f>
         <v/>
       </c>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="38" t="n"/>
-      <c r="E15" s="27" t="n"/>
-      <c r="F15" s="27" t="n"/>
-      <c r="G15" s="39">
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="28" t="n"/>
+      <c r="D15" s="39" t="n"/>
+      <c r="E15" s="28" t="n"/>
+      <c r="F15" s="28" t="n"/>
+      <c r="G15" s="40">
         <f>IF((C15)&gt;0,C15*(D15)/12,0)</f>
         <v/>
       </c>
-      <c r="H15" s="40">
+      <c r="H15" s="41">
         <f>IF((C15)&lt;=0,"",IF((E15)+(F15)&lt;=G15,"Payment too low",ROUNDUP(IF((D15)=0,C15/((E15)+(F15)),NPER(D15/12,-((E15)+(F15)),C15)),0)))</f>
         <v/>
       </c>
-      <c r="I15" s="41">
+      <c r="I15" s="42">
         <f>IF((C15)&lt;=0,"",COUNTIFS($C$6:$C$15,"&gt;0",$D$6:$D$15,"&gt;"&amp;(D15))+1)</f>
         <v/>
       </c>
     </row>
     <row r="16"/>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="17" t="inlineStr">
         <is>
           <t>Total debt</t>
         </is>
       </c>
-      <c r="C17" s="42">
+      <c r="C17" s="43">
         <f>SUM(C6:C15)</f>
         <v/>
       </c>
-      <c r="D17" s="25" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
         <is>
           <t>Priority 1 = highest interest rate. Send every extra euro there, pay minimums on the rest. Months to clear is an estimate with fixed payments.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="17" t="inlineStr">
         <is>
           <t>Interest you pay / month</t>
         </is>
       </c>
-      <c r="C18" s="43">
+      <c r="C18" s="44">
         <f>SUM(G6:G15)</f>
         <v/>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="17" t="inlineStr">
         <is>
           <t>Interest you pay / year</t>
         </is>
       </c>
-      <c r="C19" s="42">
+      <c r="C19" s="43">
         <f>C18*12</f>
         <v/>
       </c>
@@ -4237,114 +4410,114 @@
     <row r="20"/>
     <row r="21"/>
     <row r="22">
-      <c r="B22" s="26" t="inlineStr">
+      <c r="B22" s="27" t="inlineStr">
         <is>
           <t>WHAT ONE HOUR OF YOUR LIFE IS WORTH</t>
         </is>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="20" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C23" s="20" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Net money in / month</t>
         </is>
       </c>
-      <c r="C24" s="44">
+      <c r="C24" s="45">
         <f>'T · Track'!E7</f>
         <v/>
       </c>
-      <c r="D24" s="25" t="inlineStr">
+      <c r="D24" s="26" t="inlineStr">
         <is>
           <t>Keep your first hour: the first hour of every workday is paid to you, not to your bills. Set up a standing transfer for this amount on payday. If it's too much right now, start with a quarter of it.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="17" t="inlineStr">
+      <c r="B25" s="18" t="inlineStr">
         <is>
           <t>Contract hours / week</t>
         </is>
       </c>
-      <c r="C25" s="45" t="n">
+      <c r="C25" s="46" t="n">
         <v>39</v>
       </c>
     </row>
     <row r="26" ht="18" customHeight="1">
-      <c r="B26" s="17" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Unpaid overtime / week</t>
         </is>
       </c>
-      <c r="C26" s="45" t="n">
+      <c r="C26" s="46" t="n">
         <v>4</v>
       </c>
     </row>
     <row r="27" ht="18" customHeight="1">
-      <c r="B27" s="17" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Commute hours / week</t>
         </is>
       </c>
-      <c r="C27" s="45" t="n">
+      <c r="C27" s="46" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="46" t="inlineStr">
+      <c r="B28" s="47" t="inlineStr">
         <is>
           <t>Real hours / month</t>
         </is>
       </c>
-      <c r="C28" s="47">
+      <c r="C28" s="48">
         <f>((C25)+(C26)+(C27))*52/12</f>
         <v/>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="B29" s="34" t="inlineStr">
+      <c r="B29" s="35" t="inlineStr">
         <is>
           <t>Your real hourly value</t>
         </is>
       </c>
-      <c r="C29" s="48">
+      <c r="C29" s="49">
         <f>IF(C28&gt;0,C24/C28,0)</f>
         <v/>
       </c>
-      <c r="D29" s="25" t="inlineStr">
+      <c r="D29" s="26" t="inlineStr">
         <is>
           <t>Before any purchase over €50, divide the price by your real hourly value. That's how many hours of your life it costs.</t>
         </is>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="17" t="inlineStr">
+      <c r="B30" s="18" t="inlineStr">
         <is>
           <t>Workdays / month</t>
         </is>
       </c>
-      <c r="C30" s="49" t="n">
+      <c r="C30" s="50" t="n">
         <v>21</v>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1">
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Keep your first hour / month</t>
         </is>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <f>C29*(C30)</f>
         <v/>
       </c>
@@ -4358,12 +4531,21 @@
     <mergeCell ref="D24:I28"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001A9E9E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4381,21 +4563,27 @@
     <col width="14" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>S · Save</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Roadmap stages 3–4 · The order matters. First a 1-month buffer, then clear consumer debt, then a full emergency fund (3 months; 6 if you're a carer, self-employed or the only earner). Then goals.</t>
         </is>
@@ -4403,110 +4591,110 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>EMERGENCY FUND</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Monthly needs (baseline)</t>
         </is>
       </c>
-      <c r="C7" s="44">
+      <c r="C7" s="45">
         <f>'T · Track'!E58</f>
         <v/>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>Keep it separate from your everyday account, easy to reach within a day or two, and boring. This money is insurance, not an investment.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Months of safety you want</t>
         </is>
       </c>
-      <c r="C8" s="49" t="n">
+      <c r="C8" s="50" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="46" t="inlineStr">
+      <c r="B9" s="47" t="inlineStr">
         <is>
           <t>Starter buffer (1 month)</t>
         </is>
       </c>
-      <c r="C9" s="50">
+      <c r="C9" s="51">
         <f>C7</f>
         <v/>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
-      <c r="B10" s="46" t="inlineStr">
+      <c r="B10" s="47" t="inlineStr">
         <is>
           <t>Full emergency fund target</t>
         </is>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="30">
         <f>C7*(C8)</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Saved so far</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <v>1200</v>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="34" t="inlineStr">
+      <c r="B12" s="35" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
-      <c r="C12" s="36">
+      <c r="C12" s="37">
         <f>IF(C10&gt;0,MIN(1,(C11)/C10),0)</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="18" customHeight="1">
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr">
         <is>
           <t>Monthly transfer to it</t>
         </is>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="28" t="n">
         <v>250</v>
       </c>
     </row>
     <row r="14" ht="18" customHeight="1">
-      <c r="B14" s="46" t="inlineStr">
+      <c r="B14" s="47" t="inlineStr">
         <is>
           <t>Months until full fund</t>
         </is>
       </c>
-      <c r="C14" s="40">
+      <c r="C14" s="41">
         <f>IF((C11)&gt;=C10,"Done ✓",IF((C13)&gt;0,ROUNDUP((C10-(C11))/C13,0),"Add a transfer"))</f>
         <v/>
       </c>
@@ -4514,250 +4702,250 @@
     <row r="15"/>
     <row r="16"/>
     <row r="17">
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="27" t="inlineStr">
         <is>
           <t>GOAL POTS (sinking funds)</t>
         </is>
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="20" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>Goal</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>Target €</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>Saved €</t>
         </is>
       </c>
-      <c r="E18" s="20" t="inlineStr">
+      <c r="E18" s="21" t="inlineStr">
         <is>
           <t>€ / month</t>
         </is>
       </c>
-      <c r="F18" s="20" t="inlineStr">
+      <c r="F18" s="21" t="inlineStr">
         <is>
           <t>Months left</t>
         </is>
       </c>
-      <c r="G18" s="20" t="inlineStr">
+      <c r="G18" s="21" t="inlineStr">
         <is>
           <t>Progress</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="B19" s="23" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Care costs &amp; time off</t>
         </is>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C19" s="28" t="n">
         <v>1500</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="28" t="n">
         <v>300</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="28" t="n">
         <v>75</v>
       </c>
-      <c r="F19" s="40">
+      <c r="F19" s="41">
         <f>IF((C19)=0,"",IF((D19)&gt;=C19,"Done ✓",IF((E19)&gt;0,ROUNDUP((C19-(D19))/E19,0),"–")))</f>
         <v/>
       </c>
-      <c r="G19" s="51">
+      <c r="G19" s="52">
         <f>IF((C19)&gt;0,MIN(1,(D19)/C19),0)</f>
         <v/>
       </c>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Christmas &amp; birthdays</t>
         </is>
       </c>
-      <c r="C20" s="27" t="n">
+      <c r="C20" s="28" t="n">
         <v>600</v>
       </c>
-      <c r="D20" s="27" t="n">
+      <c r="D20" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="E20" s="27" t="n">
+      <c r="E20" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="F20" s="40">
+      <c r="F20" s="41">
         <f>IF((C20)=0,"",IF((D20)&gt;=C20,"Done ✓",IF((E20)&gt;0,ROUNDUP((C20-(D20))/E20,0),"–")))</f>
         <v/>
       </c>
-      <c r="G20" s="51">
+      <c r="G20" s="52">
         <f>IF((C20)&gt;0,MIN(1,(D20)/C20),0)</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Holiday with family</t>
         </is>
       </c>
-      <c r="C21" s="27" t="n">
+      <c r="C21" s="28" t="n">
         <v>1800</v>
       </c>
-      <c r="D21" s="27" t="n">
+      <c r="D21" s="28" t="n">
         <v>250</v>
       </c>
-      <c r="E21" s="27" t="n">
+      <c r="E21" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="F21" s="40">
+      <c r="F21" s="41">
         <f>IF((C21)=0,"",IF((D21)&gt;=C21,"Done ✓",IF((E21)&gt;0,ROUNDUP((C21-(D21))/E21,0),"–")))</f>
         <v/>
       </c>
-      <c r="G21" s="51">
+      <c r="G21" s="52">
         <f>IF((C21)&gt;0,MIN(1,(D21)/C21),0)</f>
         <v/>
       </c>
     </row>
     <row r="22">
-      <c r="B22" s="23" t="n"/>
-      <c r="C22" s="27" t="n"/>
-      <c r="D22" s="27" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="40">
+      <c r="B22" s="24" t="n"/>
+      <c r="C22" s="28" t="n"/>
+      <c r="D22" s="28" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="41">
         <f>IF((C22)=0,"",IF((D22)&gt;=C22,"Done ✓",IF((E22)&gt;0,ROUNDUP((C22-(D22))/E22,0),"–")))</f>
         <v/>
       </c>
-      <c r="G22" s="51">
+      <c r="G22" s="52">
         <f>IF((C22)&gt;0,MIN(1,(D22)/C22),0)</f>
         <v/>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="23" t="n"/>
-      <c r="C23" s="27" t="n"/>
-      <c r="D23" s="27" t="n"/>
-      <c r="E23" s="27" t="n"/>
-      <c r="F23" s="40">
+      <c r="B23" s="24" t="n"/>
+      <c r="C23" s="28" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
+      <c r="F23" s="41">
         <f>IF((C23)=0,"",IF((D23)&gt;=C23,"Done ✓",IF((E23)&gt;0,ROUNDUP((C23-(D23))/E23,0),"–")))</f>
         <v/>
       </c>
-      <c r="G23" s="51">
+      <c r="G23" s="52">
         <f>IF((C23)&gt;0,MIN(1,(D23)/C23),0)</f>
         <v/>
       </c>
     </row>
     <row r="24">
-      <c r="B24" s="23" t="n"/>
-      <c r="C24" s="27" t="n"/>
-      <c r="D24" s="27" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="40">
+      <c r="B24" s="24" t="n"/>
+      <c r="C24" s="28" t="n"/>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="41">
         <f>IF((C24)=0,"",IF((D24)&gt;=C24,"Done ✓",IF((E24)&gt;0,ROUNDUP((C24-(D24))/E24,0),"–")))</f>
         <v/>
       </c>
-      <c r="G24" s="51">
+      <c r="G24" s="52">
         <f>IF((C24)&gt;0,MIN(1,(D24)/C24),0)</f>
         <v/>
       </c>
     </row>
     <row r="25">
-      <c r="B25" s="23" t="n"/>
-      <c r="C25" s="27" t="n"/>
-      <c r="D25" s="27" t="n"/>
-      <c r="E25" s="27" t="n"/>
-      <c r="F25" s="40">
+      <c r="B25" s="24" t="n"/>
+      <c r="C25" s="28" t="n"/>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
+      <c r="F25" s="41">
         <f>IF((C25)=0,"",IF((D25)&gt;=C25,"Done ✓",IF((E25)&gt;0,ROUNDUP((C25-(D25))/E25,0),"–")))</f>
         <v/>
       </c>
-      <c r="G25" s="51">
+      <c r="G25" s="52">
         <f>IF((C25)&gt;0,MIN(1,(D25)/C25),0)</f>
         <v/>
       </c>
     </row>
     <row r="26">
-      <c r="B26" s="23" t="n"/>
-      <c r="C26" s="27" t="n"/>
-      <c r="D26" s="27" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="40">
+      <c r="B26" s="24" t="n"/>
+      <c r="C26" s="28" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="41">
         <f>IF((C26)=0,"",IF((D26)&gt;=C26,"Done ✓",IF((E26)&gt;0,ROUNDUP((C26-(D26))/E26,0),"–")))</f>
         <v/>
       </c>
-      <c r="G26" s="51">
+      <c r="G26" s="52">
         <f>IF((C26)&gt;0,MIN(1,(D26)/C26),0)</f>
         <v/>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="23" t="n"/>
-      <c r="C27" s="27" t="n"/>
-      <c r="D27" s="27" t="n"/>
-      <c r="E27" s="27" t="n"/>
-      <c r="F27" s="40">
+      <c r="B27" s="24" t="n"/>
+      <c r="C27" s="28" t="n"/>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
+      <c r="F27" s="41">
         <f>IF((C27)=0,"",IF((D27)&gt;=C27,"Done ✓",IF((E27)&gt;0,ROUNDUP((C27-(D27))/E27,0),"–")))</f>
         <v/>
       </c>
-      <c r="G27" s="51">
+      <c r="G27" s="52">
         <f>IF((C27)&gt;0,MIN(1,(D27)/C27),0)</f>
         <v/>
       </c>
     </row>
     <row r="28">
-      <c r="B28" s="23" t="n"/>
-      <c r="C28" s="27" t="n"/>
-      <c r="D28" s="27" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="40">
+      <c r="B28" s="24" t="n"/>
+      <c r="C28" s="28" t="n"/>
+      <c r="D28" s="28" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="41">
         <f>IF((C28)=0,"",IF((D28)&gt;=C28,"Done ✓",IF((E28)&gt;0,ROUNDUP((C28-(D28))/E28,0),"–")))</f>
         <v/>
       </c>
-      <c r="G28" s="51">
+      <c r="G28" s="52">
         <f>IF((C28)&gt;0,MIN(1,(D28)/C28),0)</f>
         <v/>
       </c>
     </row>
     <row r="29"/>
     <row r="30" ht="18" customHeight="1">
-      <c r="B30" s="46" t="inlineStr">
+      <c r="B30" s="47" t="inlineStr">
         <is>
           <t>Total monthly to goal pots</t>
         </is>
       </c>
-      <c r="E30" s="29">
+      <c r="E30" s="30">
         <f>SUM(E19:E28)</f>
         <v/>
       </c>
     </row>
     <row r="31" ht="31" customHeight="1">
-      <c r="B31" s="34" t="inlineStr">
+      <c r="B31" s="35" t="inlineStr">
         <is>
           <t>Total monthly saving (fund + pots)</t>
         </is>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <f>(C13)+E30</f>
         <v/>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="17" t="inlineStr">
         <is>
           <t>Still unassigned from KEEP</t>
         </is>
       </c>
-      <c r="E32" s="29">
+      <c r="E32" s="30">
         <f>'T · Track'!E62-E31</f>
         <v/>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
-      <c r="B33" s="25" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>If 'still unassigned' is negative, your plan spends more than you keep. Lower a transfer until it's zero or positive.</t>
         </is>
@@ -4771,11 +4959,20 @@
     <mergeCell ref="D7:G10"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F6E6E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4793,21 +4990,27 @@
     <col width="34" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Invest</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Roadmap stage 5 · Only after your full emergency fund, and only in what you understand. This tab is for learning and planning. It does not recommend any product, fund or provider.</t>
         </is>
@@ -4815,213 +5018,213 @@
     </row>
     <row r="4"/>
     <row r="5">
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="27" t="inlineStr">
         <is>
           <t>BEFORE YOU INVEST · CHECK</t>
         </is>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="21" t="inlineStr">
         <is>
           <t>Question</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>Answer</t>
         </is>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>Full emergency fund in place?</t>
         </is>
       </c>
-      <c r="C7" s="52">
+      <c r="C7" s="53">
         <f>IF('S · Save'!C12&gt;=1,"Yes ✓","Not yet")</f>
         <v/>
       </c>
-      <c r="D7" s="25" t="inlineStr">
+      <c r="D7" s="26" t="inlineStr">
         <is>
           <t>If any answer is not 'Yes', fix that first. Learning counts as progress.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Consumer debt cleared?</t>
         </is>
       </c>
-      <c r="C8" s="52">
+      <c r="C8" s="53">
         <f>IF(('U · Understand'!C17)&lt;=0,"Yes ✓","Not yet")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="18" t="inlineStr">
         <is>
           <t>Money not needed for 5+ years?</t>
         </is>
       </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="C9" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="10" ht="31" customHeight="1">
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="18" t="inlineStr">
         <is>
           <t>Can you explain it in two sentences?</t>
         </is>
       </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="C10" s="24" t="inlineStr">
         <is>
           <t>Not sure</t>
         </is>
       </c>
     </row>
     <row r="11" ht="31" customHeight="1">
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="18" t="inlineStr">
         <is>
           <t>Provider is regulated (e.g. BaFin register)?</t>
         </is>
       </c>
-      <c r="C11" s="23" t="inlineStr">
+      <c r="C11" s="24" t="inlineStr">
         <is>
           <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="12" ht="18" customHeight="1">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>Ready to start?</t>
         </is>
       </c>
-      <c r="C12" s="53">
+      <c r="C12" s="54">
         <f>IF(AND(C7="Yes ✓",C8="Yes ✓",C9="Yes",C10="Yes",C11="Yes"),"Ready ✓","Not yet: finish the checks")</f>
         <v/>
       </c>
     </row>
     <row r="13"/>
     <row r="14">
-      <c r="B14" s="26" t="inlineStr">
+      <c r="B14" s="27" t="inlineStr">
         <is>
           <t>WHAT TIME COULD DO · ILLUSTRATION ONLY</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="B15" s="20" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>Item</t>
         </is>
       </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>Value</t>
         </is>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="18" t="inlineStr">
         <is>
           <t>Monthly amount</t>
         </is>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="D16" s="25" t="inlineStr">
+      <c r="D16" s="26" t="inlineStr">
         <is>
           <t>Change the yellow cells to see how time, amount and fees change the result. Fixed growth is a simplification: real returns go up and down, aren't guaranteed, and you can lose money. Taxes and inflation are not included.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
-      <c r="B17" s="17" t="inlineStr">
+      <c r="B17" s="18" t="inlineStr">
         <is>
           <t>Starting amount</t>
         </is>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="28" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
-      <c r="B18" s="17" t="inlineStr">
+      <c r="B18" s="18" t="inlineStr">
         <is>
           <t>Years</t>
         </is>
       </c>
-      <c r="C18" s="49" t="n">
+      <c r="C18" s="50" t="n">
         <v>25</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
-      <c r="B19" s="17" t="inlineStr">
+      <c r="B19" s="18" t="inlineStr">
         <is>
           <t>Hypothetical yearly growth</t>
         </is>
       </c>
-      <c r="C19" s="38" t="n">
+      <c r="C19" s="39" t="n">
         <v>0.05</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
-      <c r="B20" s="17" t="inlineStr">
+      <c r="B20" s="18" t="inlineStr">
         <is>
           <t>Yearly costs (fees)</t>
         </is>
       </c>
-      <c r="C20" s="54" t="n">
+      <c r="C20" s="55" t="n">
         <v>0.005</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
-      <c r="B21" s="46" t="inlineStr">
+      <c r="B21" s="47" t="inlineStr">
         <is>
           <t>You pay in</t>
         </is>
       </c>
-      <c r="C21" s="50">
+      <c r="C21" s="51">
         <f>(C17)+(C16)*12*(C18)</f>
         <v/>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
-      <c r="B22" s="34" t="inlineStr">
+      <c r="B22" s="35" t="inlineStr">
         <is>
           <t>Value before fees</t>
         </is>
       </c>
-      <c r="C22" s="35">
+      <c r="C22" s="36">
         <f>IF((C19)=0,C21,FV((C19)/12,(C18)*12,-(C16),-(C17)))</f>
         <v/>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Value after fees</t>
         </is>
       </c>
-      <c r="C23" s="35">
+      <c r="C23" s="36">
         <f>IF((C19)-(C20)=0,C21,FV(((C19)-(C20))/12,(C18)*12,-(C16),-(C17)))</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
-      <c r="B24" s="19" t="inlineStr">
+      <c r="B24" s="20" t="inlineStr">
         <is>
           <t>What the fees cost you</t>
         </is>
       </c>
-      <c r="C24" s="42">
+      <c r="C24" s="43">
         <f>C22-C23</f>
         <v/>
       </c>
@@ -5029,170 +5232,170 @@
     <row r="25"/>
     <row r="26"/>
     <row r="27">
-      <c r="B27" s="26" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>WHAT YOU ALREADY INVEST</t>
         </is>
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="B28" s="20" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>Account / plan</t>
         </is>
       </c>
-      <c r="C28" s="20" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
+      <c r="D28" s="21" t="inlineStr">
         <is>
           <t>€ / month</t>
         </is>
       </c>
-      <c r="E28" s="20" t="inlineStr">
+      <c r="E28" s="21" t="inlineStr">
         <is>
           <t>Value now €</t>
         </is>
       </c>
-      <c r="F28" s="20" t="inlineStr">
+      <c r="F28" s="21" t="inlineStr">
         <is>
           <t>Yearly costs %</t>
         </is>
       </c>
-      <c r="G28" s="20" t="inlineStr">
+      <c r="G28" s="21" t="inlineStr">
         <is>
           <t>Note</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="B29" s="23" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Workplace pension</t>
         </is>
       </c>
-      <c r="C29" s="23" t="inlineStr">
+      <c r="C29" s="24" t="inlineStr">
         <is>
           <t>Employer plan</t>
         </is>
       </c>
-      <c r="D29" s="27" t="n">
+      <c r="D29" s="28" t="n">
         <v>100</v>
       </c>
-      <c r="E29" s="27" t="n">
+      <c r="E29" s="28" t="n">
         <v>2400</v>
       </c>
-      <c r="F29" s="54" t="n">
+      <c r="F29" s="55" t="n">
         <v>0.006</v>
       </c>
-      <c r="G29" s="23" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>Employer adds €50 a month</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="B30" s="23" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Long-term plan</t>
         </is>
       </c>
-      <c r="C30" s="23" t="inlineStr">
+      <c r="C30" s="24" t="inlineStr">
         <is>
           <t>Monthly savings plan</t>
         </is>
       </c>
-      <c r="D30" s="27" t="n">
+      <c r="D30" s="28" t="n">
         <v>50</v>
       </c>
-      <c r="E30" s="27" t="n">
+      <c r="E30" s="28" t="n">
         <v>600</v>
       </c>
-      <c r="F30" s="54" t="n">
+      <c r="F30" s="55" t="n">
         <v>0.002</v>
       </c>
-      <c r="G30" s="23" t="inlineStr">
+      <c r="G30" s="24" t="inlineStr">
         <is>
           <t>Example rows: overwrite with yours</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="B31" s="23" t="n"/>
-      <c r="C31" s="23" t="n"/>
-      <c r="D31" s="27" t="n"/>
-      <c r="E31" s="27" t="n"/>
-      <c r="F31" s="54" t="n"/>
-      <c r="G31" s="23" t="n"/>
+      <c r="B31" s="24" t="n"/>
+      <c r="C31" s="24" t="n"/>
+      <c r="D31" s="28" t="n"/>
+      <c r="E31" s="28" t="n"/>
+      <c r="F31" s="55" t="n"/>
+      <c r="G31" s="24" t="n"/>
     </row>
     <row r="32">
-      <c r="B32" s="23" t="n"/>
-      <c r="C32" s="23" t="n"/>
-      <c r="D32" s="27" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="54" t="n"/>
-      <c r="G32" s="23" t="n"/>
+      <c r="B32" s="24" t="n"/>
+      <c r="C32" s="24" t="n"/>
+      <c r="D32" s="28" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="55" t="n"/>
+      <c r="G32" s="24" t="n"/>
     </row>
     <row r="33">
-      <c r="B33" s="23" t="n"/>
-      <c r="C33" s="23" t="n"/>
-      <c r="D33" s="27" t="n"/>
-      <c r="E33" s="27" t="n"/>
-      <c r="F33" s="54" t="n"/>
-      <c r="G33" s="23" t="n"/>
+      <c r="B33" s="24" t="n"/>
+      <c r="C33" s="24" t="n"/>
+      <c r="D33" s="28" t="n"/>
+      <c r="E33" s="28" t="n"/>
+      <c r="F33" s="55" t="n"/>
+      <c r="G33" s="24" t="n"/>
     </row>
     <row r="34">
-      <c r="B34" s="23" t="n"/>
-      <c r="C34" s="23" t="n"/>
-      <c r="D34" s="27" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="54" t="n"/>
-      <c r="G34" s="23" t="n"/>
+      <c r="B34" s="24" t="n"/>
+      <c r="C34" s="24" t="n"/>
+      <c r="D34" s="28" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="55" t="n"/>
+      <c r="G34" s="24" t="n"/>
     </row>
     <row r="35">
-      <c r="B35" s="23" t="n"/>
-      <c r="C35" s="23" t="n"/>
-      <c r="D35" s="27" t="n"/>
-      <c r="E35" s="27" t="n"/>
-      <c r="F35" s="54" t="n"/>
-      <c r="G35" s="23" t="n"/>
+      <c r="B35" s="24" t="n"/>
+      <c r="C35" s="24" t="n"/>
+      <c r="D35" s="28" t="n"/>
+      <c r="E35" s="28" t="n"/>
+      <c r="F35" s="55" t="n"/>
+      <c r="G35" s="24" t="n"/>
     </row>
     <row r="36">
-      <c r="B36" s="23" t="n"/>
-      <c r="C36" s="23" t="n"/>
-      <c r="D36" s="27" t="n"/>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="54" t="n"/>
-      <c r="G36" s="23" t="n"/>
+      <c r="B36" s="24" t="n"/>
+      <c r="C36" s="24" t="n"/>
+      <c r="D36" s="28" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="55" t="n"/>
+      <c r="G36" s="24" t="n"/>
     </row>
     <row r="37"/>
     <row r="38" ht="18" customHeight="1">
-      <c r="B38" s="34" t="inlineStr">
+      <c r="B38" s="35" t="inlineStr">
         <is>
           <t>Invested / month</t>
         </is>
       </c>
-      <c r="D38" s="35">
+      <c r="D38" s="36">
         <f>SUM(D29:D36)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
-      <c r="B39" s="34" t="inlineStr">
+      <c r="B39" s="35" t="inlineStr">
         <is>
           <t>Invested so far</t>
         </is>
       </c>
-      <c r="E39" s="35">
+      <c r="E39" s="36">
         <f>SUM(E29:E36)</f>
         <v/>
       </c>
     </row>
     <row r="40"/>
     <row r="41" ht="18" customHeight="1">
-      <c r="B41" s="25" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Rule: automate a fixed amount on payday, review once a year, and never invest money you might need within 5 years.</t>
         </is>
@@ -5212,11 +5415,20 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="000F6E6E"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5236,23 +5448,29 @@
     <col width="30" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
-    <row r="1"/>
+    <row r="1" ht="16" customHeight="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>© 2026 iCyber · For the purchaser's personal use only · Copying or reselling is not permitted</t>
+        </is>
+      </c>
+    </row>
     <row r="2" ht="40" customHeight="1">
-      <c r="B2" s="12" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>Income Streams</t>
         </is>
       </c>
-      <c r="C2" s="13" t="n"/>
-      <c r="D2" s="13" t="n"/>
-      <c r="E2" s="13" t="n"/>
-      <c r="F2" s="13" t="n"/>
-      <c r="G2" s="13" t="n"/>
-      <c r="H2" s="13" t="n"/>
-      <c r="I2" s="13" t="n"/>
+      <c r="C2" s="14" t="n"/>
+      <c r="D2" s="14" t="n"/>
+      <c r="E2" s="14" t="n"/>
+      <c r="F2" s="14" t="n"/>
+      <c r="G2" s="14" t="n"/>
+      <c r="H2" s="14" t="n"/>
+      <c r="I2" s="14" t="n"/>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Roadmap stages 2 + 6 · Build one stream at a time, beside your career. Log every stream here, including a raise you negotiated. Watch € per hour: a stream that pays less than your job per hour must be buying you something else (skills, assets, freedom later).</t>
         </is>
@@ -5260,371 +5478,371 @@
     </row>
     <row r="4"/>
     <row r="5" ht="30" customHeight="1">
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t>Stream</t>
         </is>
       </c>
-      <c r="C5" s="20" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D5" s="20" t="inlineStr">
+      <c r="D5" s="21" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="E5" s="20" t="inlineStr">
+      <c r="E5" s="21" t="inlineStr">
         <is>
           <t>Hours / week</t>
         </is>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F5" s="21" t="inlineStr">
         <is>
           <t>Started (month)</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr">
+      <c r="G5" s="21" t="inlineStr">
         <is>
           <t>€ / month (net)</t>
         </is>
       </c>
-      <c r="H5" s="20" t="inlineStr">
+      <c r="H5" s="21" t="inlineStr">
         <is>
           <t>€ per hour</t>
         </is>
       </c>
-      <c r="I5" s="20" t="inlineStr">
+      <c r="I5" s="21" t="inlineStr">
         <is>
           <t>Next small step</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="23" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Salary raise negotiated</t>
         </is>
       </c>
-      <c r="C6" s="23" t="inlineStr">
+      <c r="C6" s="24" t="inlineStr">
         <is>
           <t>Career (raise/promotion)</t>
         </is>
       </c>
-      <c r="D6" s="23" t="inlineStr">
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>Earning</t>
         </is>
       </c>
-      <c r="E6" s="45" t="n">
+      <c r="E6" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="inlineStr">
+      <c r="F6" s="24" t="inlineStr">
         <is>
           <t>2026-03</t>
         </is>
       </c>
-      <c r="G6" s="27" t="n">
+      <c r="G6" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="H6" s="55">
+      <c r="H6" s="56">
         <f>IF((E6)&gt;0,(G6)/(E6*52/12),IF((G6)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I6" s="23" t="inlineStr">
+      <c r="I6" s="24" t="inlineStr">
         <is>
           <t>Prepare next review in March</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="B7" s="23" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Cybersecurity starter guide</t>
         </is>
       </c>
-      <c r="C7" s="23" t="inlineStr">
+      <c r="C7" s="24" t="inlineStr">
         <is>
           <t>Digital product</t>
         </is>
       </c>
-      <c r="D7" s="23" t="inlineStr">
+      <c r="D7" s="24" t="inlineStr">
         <is>
           <t>Testing</t>
         </is>
       </c>
-      <c r="E7" s="45" t="n">
+      <c r="E7" s="46" t="n">
         <v>3</v>
       </c>
-      <c r="F7" s="23" t="inlineStr">
+      <c r="F7" s="24" t="inlineStr">
         <is>
           <t>2026-08</t>
         </is>
       </c>
-      <c r="G7" s="27" t="n">
+      <c r="G7" s="28" t="n">
         <v>60</v>
       </c>
-      <c r="H7" s="55">
+      <c r="H7" s="56">
         <f>IF((E7)&gt;0,(G7)/(E7*52/12),IF((G7)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I7" s="23" t="inlineStr">
+      <c r="I7" s="24" t="inlineStr">
         <is>
           <t>Post 3 reels pointing to it</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="B8" s="23" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>UGC for a skincare brand</t>
         </is>
       </c>
-      <c r="C8" s="23" t="inlineStr">
+      <c r="C8" s="24" t="inlineStr">
         <is>
           <t>UGC</t>
         </is>
       </c>
-      <c r="D8" s="23" t="inlineStr">
+      <c r="D8" s="24" t="inlineStr">
         <is>
           <t>Idea</t>
         </is>
       </c>
-      <c r="E8" s="45" t="n">
+      <c r="E8" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="23" t="inlineStr"/>
-      <c r="G8" s="27" t="n">
+      <c r="F8" s="24" t="inlineStr"/>
+      <c r="G8" s="28" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="55">
+      <c r="H8" s="56">
         <f>IF((E8)&gt;0,(G8)/(E8*52/12),IF((G8)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I8" s="23" t="inlineStr">
+      <c r="I8" s="24" t="inlineStr">
         <is>
           <t>Make 2 sample videos</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="B9" s="23" t="n"/>
-      <c r="C9" s="23" t="n"/>
-      <c r="D9" s="23" t="n"/>
-      <c r="E9" s="45" t="n"/>
-      <c r="F9" s="23" t="n"/>
-      <c r="G9" s="27" t="n"/>
-      <c r="H9" s="55">
+      <c r="B9" s="24" t="n"/>
+      <c r="C9" s="24" t="n"/>
+      <c r="D9" s="24" t="n"/>
+      <c r="E9" s="46" t="n"/>
+      <c r="F9" s="24" t="n"/>
+      <c r="G9" s="28" t="n"/>
+      <c r="H9" s="56">
         <f>IF((E9)&gt;0,(G9)/(E9*52/12),IF((G9)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I9" s="23" t="n"/>
+      <c r="I9" s="24" t="n"/>
     </row>
     <row r="10">
-      <c r="B10" s="23" t="n"/>
-      <c r="C10" s="23" t="n"/>
-      <c r="D10" s="23" t="n"/>
-      <c r="E10" s="45" t="n"/>
-      <c r="F10" s="23" t="n"/>
-      <c r="G10" s="27" t="n"/>
-      <c r="H10" s="55">
+      <c r="B10" s="24" t="n"/>
+      <c r="C10" s="24" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="46" t="n"/>
+      <c r="F10" s="24" t="n"/>
+      <c r="G10" s="28" t="n"/>
+      <c r="H10" s="56">
         <f>IF((E10)&gt;0,(G10)/(E10*52/12),IF((G10)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I10" s="23" t="n"/>
+      <c r="I10" s="24" t="n"/>
     </row>
     <row r="11">
-      <c r="B11" s="23" t="n"/>
-      <c r="C11" s="23" t="n"/>
-      <c r="D11" s="23" t="n"/>
-      <c r="E11" s="45" t="n"/>
-      <c r="F11" s="23" t="n"/>
-      <c r="G11" s="27" t="n"/>
-      <c r="H11" s="55">
+      <c r="B11" s="24" t="n"/>
+      <c r="C11" s="24" t="n"/>
+      <c r="D11" s="24" t="n"/>
+      <c r="E11" s="46" t="n"/>
+      <c r="F11" s="24" t="n"/>
+      <c r="G11" s="28" t="n"/>
+      <c r="H11" s="56">
         <f>IF((E11)&gt;0,(G11)/(E11*52/12),IF((G11)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I11" s="23" t="n"/>
+      <c r="I11" s="24" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="23" t="n"/>
-      <c r="C12" s="23" t="n"/>
-      <c r="D12" s="23" t="n"/>
-      <c r="E12" s="45" t="n"/>
-      <c r="F12" s="23" t="n"/>
-      <c r="G12" s="27" t="n"/>
-      <c r="H12" s="55">
+      <c r="B12" s="24" t="n"/>
+      <c r="C12" s="24" t="n"/>
+      <c r="D12" s="24" t="n"/>
+      <c r="E12" s="46" t="n"/>
+      <c r="F12" s="24" t="n"/>
+      <c r="G12" s="28" t="n"/>
+      <c r="H12" s="56">
         <f>IF((E12)&gt;0,(G12)/(E12*52/12),IF((G12)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I12" s="23" t="n"/>
+      <c r="I12" s="24" t="n"/>
     </row>
     <row r="13">
-      <c r="B13" s="23" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="23" t="n"/>
-      <c r="E13" s="45" t="n"/>
-      <c r="F13" s="23" t="n"/>
-      <c r="G13" s="27" t="n"/>
-      <c r="H13" s="55">
+      <c r="B13" s="24" t="n"/>
+      <c r="C13" s="24" t="n"/>
+      <c r="D13" s="24" t="n"/>
+      <c r="E13" s="46" t="n"/>
+      <c r="F13" s="24" t="n"/>
+      <c r="G13" s="28" t="n"/>
+      <c r="H13" s="56">
         <f>IF((E13)&gt;0,(G13)/(E13*52/12),IF((G13)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I13" s="23" t="n"/>
+      <c r="I13" s="24" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="23" t="n"/>
-      <c r="C14" s="23" t="n"/>
-      <c r="D14" s="23" t="n"/>
-      <c r="E14" s="45" t="n"/>
-      <c r="F14" s="23" t="n"/>
-      <c r="G14" s="27" t="n"/>
-      <c r="H14" s="55">
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="24" t="n"/>
+      <c r="D14" s="24" t="n"/>
+      <c r="E14" s="46" t="n"/>
+      <c r="F14" s="24" t="n"/>
+      <c r="G14" s="28" t="n"/>
+      <c r="H14" s="56">
         <f>IF((E14)&gt;0,(G14)/(E14*52/12),IF((G14)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I14" s="23" t="n"/>
+      <c r="I14" s="24" t="n"/>
     </row>
     <row r="15">
-      <c r="B15" s="23" t="n"/>
-      <c r="C15" s="23" t="n"/>
-      <c r="D15" s="23" t="n"/>
-      <c r="E15" s="45" t="n"/>
-      <c r="F15" s="23" t="n"/>
-      <c r="G15" s="27" t="n"/>
-      <c r="H15" s="55">
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="24" t="n"/>
+      <c r="D15" s="24" t="n"/>
+      <c r="E15" s="46" t="n"/>
+      <c r="F15" s="24" t="n"/>
+      <c r="G15" s="28" t="n"/>
+      <c r="H15" s="56">
         <f>IF((E15)&gt;0,(G15)/(E15*52/12),IF((G15)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I15" s="23" t="n"/>
+      <c r="I15" s="24" t="n"/>
     </row>
     <row r="16">
-      <c r="B16" s="23" t="n"/>
-      <c r="C16" s="23" t="n"/>
-      <c r="D16" s="23" t="n"/>
-      <c r="E16" s="45" t="n"/>
-      <c r="F16" s="23" t="n"/>
-      <c r="G16" s="27" t="n"/>
-      <c r="H16" s="55">
+      <c r="B16" s="24" t="n"/>
+      <c r="C16" s="24" t="n"/>
+      <c r="D16" s="24" t="n"/>
+      <c r="E16" s="46" t="n"/>
+      <c r="F16" s="24" t="n"/>
+      <c r="G16" s="28" t="n"/>
+      <c r="H16" s="56">
         <f>IF((E16)&gt;0,(G16)/(E16*52/12),IF((G16)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I16" s="23" t="n"/>
+      <c r="I16" s="24" t="n"/>
     </row>
     <row r="17">
-      <c r="B17" s="23" t="n"/>
-      <c r="C17" s="23" t="n"/>
-      <c r="D17" s="23" t="n"/>
-      <c r="E17" s="45" t="n"/>
-      <c r="F17" s="23" t="n"/>
-      <c r="G17" s="27" t="n"/>
-      <c r="H17" s="55">
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="24" t="n"/>
+      <c r="D17" s="24" t="n"/>
+      <c r="E17" s="46" t="n"/>
+      <c r="F17" s="24" t="n"/>
+      <c r="G17" s="28" t="n"/>
+      <c r="H17" s="56">
         <f>IF((E17)&gt;0,(G17)/(E17*52/12),IF((G17)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I17" s="23" t="n"/>
+      <c r="I17" s="24" t="n"/>
     </row>
     <row r="18">
-      <c r="B18" s="23" t="n"/>
-      <c r="C18" s="23" t="n"/>
-      <c r="D18" s="23" t="n"/>
-      <c r="E18" s="45" t="n"/>
-      <c r="F18" s="23" t="n"/>
-      <c r="G18" s="27" t="n"/>
-      <c r="H18" s="55">
+      <c r="B18" s="24" t="n"/>
+      <c r="C18" s="24" t="n"/>
+      <c r="D18" s="24" t="n"/>
+      <c r="E18" s="46" t="n"/>
+      <c r="F18" s="24" t="n"/>
+      <c r="G18" s="28" t="n"/>
+      <c r="H18" s="56">
         <f>IF((E18)&gt;0,(G18)/(E18*52/12),IF((G18)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I18" s="23" t="n"/>
+      <c r="I18" s="24" t="n"/>
     </row>
     <row r="19">
-      <c r="B19" s="23" t="n"/>
-      <c r="C19" s="23" t="n"/>
-      <c r="D19" s="23" t="n"/>
-      <c r="E19" s="45" t="n"/>
-      <c r="F19" s="23" t="n"/>
-      <c r="G19" s="27" t="n"/>
-      <c r="H19" s="55">
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="24" t="n"/>
+      <c r="D19" s="24" t="n"/>
+      <c r="E19" s="46" t="n"/>
+      <c r="F19" s="24" t="n"/>
+      <c r="G19" s="28" t="n"/>
+      <c r="H19" s="56">
         <f>IF((E19)&gt;0,(G19)/(E19*52/12),IF((G19)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I19" s="23" t="n"/>
+      <c r="I19" s="24" t="n"/>
     </row>
     <row r="20">
-      <c r="B20" s="23" t="n"/>
-      <c r="C20" s="23" t="n"/>
-      <c r="D20" s="23" t="n"/>
-      <c r="E20" s="45" t="n"/>
-      <c r="F20" s="23" t="n"/>
-      <c r="G20" s="27" t="n"/>
-      <c r="H20" s="55">
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="24" t="n"/>
+      <c r="D20" s="24" t="n"/>
+      <c r="E20" s="46" t="n"/>
+      <c r="F20" s="24" t="n"/>
+      <c r="G20" s="28" t="n"/>
+      <c r="H20" s="56">
         <f>IF((E20)&gt;0,(G20)/(E20*52/12),IF((G20)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I20" s="23" t="n"/>
+      <c r="I20" s="24" t="n"/>
     </row>
     <row r="21">
-      <c r="B21" s="23" t="n"/>
-      <c r="C21" s="23" t="n"/>
-      <c r="D21" s="23" t="n"/>
-      <c r="E21" s="45" t="n"/>
-      <c r="F21" s="23" t="n"/>
-      <c r="G21" s="27" t="n"/>
-      <c r="H21" s="55">
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="24" t="n"/>
+      <c r="D21" s="24" t="n"/>
+      <c r="E21" s="46" t="n"/>
+      <c r="F21" s="24" t="n"/>
+      <c r="G21" s="28" t="n"/>
+      <c r="H21" s="56">
         <f>IF((E21)&gt;0,(G21)/(E21*52/12),IF((G21)&gt;0,"no time logged",""))</f>
         <v/>
       </c>
-      <c r="I21" s="23" t="n"/>
+      <c r="I21" s="24" t="n"/>
     </row>
     <row r="22"/>
     <row r="23" ht="18" customHeight="1">
-      <c r="B23" s="34" t="inlineStr">
+      <c r="B23" s="35" t="inlineStr">
         <is>
           <t>Total extra income / month</t>
         </is>
       </c>
-      <c r="G23" s="35">
+      <c r="G23" s="36">
         <f>SUMIF(C6:C21,"&lt;&gt;Career (raise/promotion)",G6:G21)</f>
         <v/>
       </c>
     </row>
     <row r="24" ht="31" customHeight="1">
-      <c r="B24" s="46" t="inlineStr">
+      <c r="B24" s="47" t="inlineStr">
         <is>
           <t>Career growth / month (in salary)</t>
         </is>
       </c>
-      <c r="G24" s="29">
+      <c r="G24" s="30">
         <f>SUMIF(C6:C21,"Career (raise/promotion)",G6:G21)</f>
         <v/>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
-      <c r="B25" s="46" t="inlineStr">
+      <c r="B25" s="47" t="inlineStr">
         <is>
           <t>Hours / week on streams</t>
         </is>
       </c>
-      <c r="E25" s="56">
+      <c r="E25" s="57">
         <f>SUM(E6:E21)</f>
         <v/>
       </c>
     </row>
     <row r="26" ht="31" customHeight="1">
-      <c r="B26" s="19" t="inlineStr">
+      <c r="B26" s="20" t="inlineStr">
         <is>
           <t>Share of your needs covered by extra income</t>
         </is>
       </c>
-      <c r="G26" s="57">
+      <c r="G26" s="58">
         <f>IF('T · Track'!E58&gt;0,G23/'T · Track'!E58,0)</f>
         <v/>
       </c>
     </row>
     <row r="27"/>
     <row r="28" ht="18" customHeight="1">
-      <c r="B28" s="25" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>A raise already shows up in your net salary on T · Track, so it is counted separately and not added to side income twice.</t>
         </is>
@@ -5645,5 +5863,14 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;9 iCyber</oddHeader>
+    <oddFooter>&amp;C&amp;8 © 2026 iCyber · Personal use only · Copying or reselling is not permitted</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <picture r:id="rIdWm"/>
 </worksheet>
 </file>